--- a/accretech/dist/20261028_東京精密個股模型_v0.1.2.xlsx
+++ b/accretech/dist/20261028_東京精密個股模型_v0.1.2.xlsx
@@ -41536,7 +41536,7 @@
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="str">
         <f aca="false">"重點觀察 1：目標價 ¥"&amp;TEXT(Val!$B$40,"#,##0")&amp;"（DCF "&amp;TEXT(Val!$B$24,"#,##0")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0")&amp;"（2026-10-23）"&amp;IF(Val!$B$43&gt;=0,"高 "&amp;TEXT(Val!$B$43,"0.0%"),"低 "&amp;TEXT(-Val!$B$43,"0.0%"))&amp;"，級距 "&amp;Val!$B$115&amp;"、投資建議 "&amp;Val!$B$116&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$24+(1-tp_w_dcf)*Val!$B$36)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$44,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：主因是 Comparable 的倍數：同業（Disco、東京威力科創、Advantest、Lasertec、Kokusai Electric）前瞻 P/E 中位數 34.0 倍，東京精密自身前瞻 P/E 只有 21.9 倍、現價隱含 18.3 倍 12 個月後前瞻 EPS（849），Comparable 未扣本公司長期低於同"&amp;"業的折價；EPS 只比共識前瞻 EPS 801 高 5.9%。DCF 反而比現價低 34.3%（ROE 13.9%、再投資率 28.7%）。"</f>
-        <v>重點觀察 1：目標價 ¥13,021（DCF 10,189、Comparable（相對倍數調整後）15,853；DCF 權重 50%），比現價 15,520（2026-10-23）低 16.1%，級距 0%～−25%、投資建議 中立。相對倍數調整係數 0.55（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 +25.8%；Comparable 單獨（市場主流同業法、未調整）為 +86.0%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：主因是 Comparable 的倍數：同業（Disco、東京威力科創、Advantest、Lasertec、Kokusai Electric）前瞻 P/E 中位數 34.0 倍，東京精密自身前瞻 P/E 只有 21.9 倍、現價隱含 18.3 倍 12 個月後前瞻 EPS（849），Comparable 未扣本公司長期低於同業的折價；EPS 只比共識前瞻 EPS 801 高 5.9%。DCF 反而比現價低 34.3%（ROE 13.9%、再投資率 28.7%）。</v>
+        <v>重點觀察 1：目標價 ¥13,008（DCF 10,180、Comparable（相對倍數調整後）15,837；DCF 權重 50%），比現價 15,520（2026-10-23）低 16.2%，級距 0%～−25%、投資建議 中立。相對倍數調整係數 0.55（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 +25.7%；Comparable 單獨（市場主流同業法、未調整）為 +85.8%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：主因是 Comparable 的倍數：同業（Disco、東京威力科創、Advantest、Lasertec、Kokusai Electric）前瞻 P/E 中位數 34.0 倍，東京精密自身前瞻 P/E 只有 21.9 倍、現價隱含 18.3 倍 12 個月後前瞻 EPS（849），Comparable 未扣本公司長期低於同業的折價；EPS 只比共識前瞻 EPS 801 高 5.9%。DCF 反而比現價低 34.3%（ROE 13.9%、再投資率 28.7%）。</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42580,7 +42580,7 @@
         <v>161</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="G48" s="8" t="s">
         <v>92</v>
@@ -42880,7 +42880,7 @@
         <v>161</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>92</v>
@@ -43180,7 +43180,7 @@
         <v>161</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="G78" s="8" t="s">
         <v>92</v>
@@ -44221,7 +44221,7 @@
         <v>161</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="G127" s="8" t="s">
         <v>92</v>
@@ -44321,7 +44321,7 @@
         <v>161</v>
       </c>
       <c r="E132" s="7" t="n">
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="G132" s="8" t="s">
         <v>92</v>
@@ -44421,7 +44421,7 @@
         <v>161</v>
       </c>
       <c r="E137" s="7" t="n">
-        <v>178.157050570127</v>
+        <v>182.0450143593</v>
       </c>
       <c r="G137" s="8" t="s">
         <v>92</v>
@@ -45708,15 +45708,15 @@
       </c>
       <c r="E5" s="16" t="n">
         <f aca="false">E76</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="F5" s="16" t="n">
         <f aca="false">F76</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G5" s="16" t="n">
         <f aca="false">G76</f>
-        <v>272.551816268834</v>
+        <v>272.335194976389</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45764,15 +45764,15 @@
       </c>
       <c r="E7" s="16" t="n">
         <f aca="false">E73</f>
-        <v>48.7843396554535</v>
+        <v>48.6070476070838</v>
       </c>
       <c r="F7" s="16" t="n">
         <f aca="false">F73</f>
-        <v>56.061461770453</v>
+        <v>55.8596083876428</v>
       </c>
       <c r="G7" s="16" t="n">
         <f aca="false">G73</f>
-        <v>60.9370262140963</v>
+        <v>60.7204049216519</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45820,15 +45820,15 @@
       </c>
       <c r="E9" s="16" t="n">
         <f aca="false">E81</f>
-        <v>53.0753690197811</v>
+        <v>53.0220425089314</v>
       </c>
       <c r="F9" s="16" t="n">
         <f aca="false">F81</f>
-        <v>62.4623992867873</v>
+        <v>62.4016851334598</v>
       </c>
       <c r="G9" s="16" t="n">
         <f aca="false">G81</f>
-        <v>68.6542815761198</v>
+        <v>68.5891254802428</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45848,15 +45848,15 @@
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">E83</f>
-        <v>0.24161379230609</v>
+        <v>0.241565998948899</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">F83</f>
-        <v>0.248451716122154</v>
+        <v>0.248409665426728</v>
       </c>
       <c r="G10" s="11" t="n">
         <f aca="false">G83</f>
-        <v>0.251894419622587</v>
+        <v>0.251855532246537</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45876,15 +45876,15 @@
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">E82</f>
-        <v>0.262343965317397</v>
+        <v>0.262305134001743</v>
       </c>
       <c r="F11" s="11" t="n">
         <f aca="false">F82</f>
-        <v>0.267805852212157</v>
+        <v>0.267773313411736</v>
       </c>
       <c r="G11" s="11" t="n">
         <f aca="false">G82</f>
-        <v>0.270517586789836</v>
+        <v>0.270488174540448</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45904,15 +45904,15 @@
       </c>
       <c r="E12" s="16" t="n">
         <f aca="false">E84</f>
-        <v>37.1527583138467</v>
+        <v>37.115429756252</v>
       </c>
       <c r="F12" s="16" t="n">
         <f aca="false">F84</f>
-        <v>43.7236795007511</v>
+        <v>43.6811795934219</v>
       </c>
       <c r="G12" s="16" t="n">
         <f aca="false">G84</f>
-        <v>48.0579971032839</v>
+        <v>48.01238783617</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45932,15 +45932,15 @@
       </c>
       <c r="E13" s="13" t="n">
         <f aca="false">E85</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="F13" s="13" t="n">
         <f aca="false">F85</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="G13" s="13" t="n">
         <f aca="false">G85</f>
-        <v>1184.03163815322</v>
+        <v>1182.90793723952</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45965,15 +45965,15 @@
       </c>
       <c r="E16" s="16" t="n">
         <f aca="false">E105</f>
-        <v>205.629490035978</v>
+        <v>205.464400326542</v>
       </c>
       <c r="F16" s="16" t="n">
         <f aca="false">F105</f>
-        <v>203.499550370459</v>
+        <v>203.338379193634</v>
       </c>
       <c r="G16" s="16" t="n">
         <f aca="false">G105</f>
-        <v>199.271722179176</v>
+        <v>199.116671426787</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46021,15 +46021,15 @@
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">E102</f>
-        <v>45.345616559068</v>
+        <v>45.1805268496326</v>
       </c>
       <c r="F18" s="16" t="n">
         <f aca="false">F102</f>
-        <v>44.269303093965</v>
+        <v>44.1081319171397</v>
       </c>
       <c r="G18" s="16" t="n">
         <f aca="false">G102</f>
-        <v>42.5881903182448</v>
+        <v>42.433139565856</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46077,15 +46077,15 @@
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">E110</f>
-        <v>48.9020466997887</v>
+        <v>48.8523904503273</v>
       </c>
       <c r="F20" s="16" t="n">
         <f aca="false">F110</f>
-        <v>48.1575746079894</v>
+        <v>48.1090969882165</v>
       </c>
       <c r="G20" s="16" t="n">
         <f aca="false">G110</f>
-        <v>46.7779395434393</v>
+        <v>46.7313028459363</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46105,15 +46105,15 @@
       </c>
       <c r="E21" s="11" t="n">
         <f aca="false">E112</f>
-        <v>0.237816310740413</v>
+        <v>0.237765716945061</v>
       </c>
       <c r="F21" s="11" t="n">
         <f aca="false">F112</f>
-        <v>0.236647081137631</v>
+        <v>0.23659624503254</v>
       </c>
       <c r="G21" s="11" t="n">
         <f aca="false">G112</f>
-        <v>0.234744493759023</v>
+        <v>0.234693069701694</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46133,15 +46133,15 @@
       </c>
       <c r="E22" s="11" t="n">
         <f aca="false">E111</f>
-        <v>0.259218358999536</v>
+        <v>0.259176080627046</v>
       </c>
       <c r="F22" s="11" t="n">
         <f aca="false">F111</f>
-        <v>0.258207793097768</v>
+        <v>0.258164486817033</v>
       </c>
       <c r="G22" s="11" t="n">
         <f aca="false">G111</f>
-        <v>0.25652717575605</v>
+        <v>0.256482160016865</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46161,15 +46161,15 @@
       </c>
       <c r="E23" s="16" t="n">
         <f aca="false">E113</f>
-        <v>34.2314326898521</v>
+        <v>34.1966733152291</v>
       </c>
       <c r="F23" s="16" t="n">
         <f aca="false">F113</f>
-        <v>33.7103022255926</v>
+        <v>33.6763678917516</v>
       </c>
       <c r="G23" s="16" t="n">
         <f aca="false">G113</f>
-        <v>32.7445576804075</v>
+        <v>32.7119119921554</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46189,15 +46189,15 @@
       </c>
       <c r="E24" s="13" t="n">
         <f aca="false">E114</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="F24" s="13" t="n">
         <f aca="false">F114</f>
-        <v>830.539489213988</v>
+        <v>829.703430133101</v>
       </c>
       <c r="G24" s="13" t="n">
         <f aca="false">G114</f>
-        <v>806.745903030704</v>
+        <v>805.941593028838</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46222,15 +46222,15 @@
       </c>
       <c r="E27" s="16" t="n">
         <f aca="false">E134</f>
-        <v>186.520240445094</v>
+        <v>186.373303090132</v>
       </c>
       <c r="F27" s="16" t="n">
         <f aca="false">F134</f>
-        <v>154.887951700422</v>
+        <v>154.773582692342</v>
       </c>
       <c r="G27" s="16" t="n">
         <f aca="false">G134</f>
-        <v>151.934679149409</v>
+        <v>151.823741211572</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46278,15 +46278,15 @@
       </c>
       <c r="E29" s="16" t="n">
         <f aca="false">E131</f>
-        <v>40.35966250773</v>
+        <v>40.2127251527679</v>
       </c>
       <c r="F29" s="16" t="n">
         <f aca="false">F131</f>
-        <v>31.4140306161021</v>
+        <v>31.2996616080227</v>
       </c>
       <c r="G29" s="16" t="n">
         <f aca="false">G131</f>
-        <v>30.471609697619</v>
+        <v>30.3606717597821</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46334,15 +46334,15 @@
       </c>
       <c r="E31" s="16" t="n">
         <f aca="false">E139</f>
-        <v>43.2291723113338</v>
+        <v>43.1849759893574</v>
       </c>
       <c r="F31" s="16" t="n">
         <f aca="false">F139</f>
-        <v>32.563959241222</v>
+        <v>32.5307026284901</v>
       </c>
       <c r="G31" s="16" t="n">
         <f aca="false">G139</f>
-        <v>31.6839711911279</v>
+        <v>31.6517122767779</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46362,15 +46362,15 @@
       </c>
       <c r="E32" s="11" t="n">
         <f aca="false">E141</f>
-        <v>0.231766655501708</v>
+        <v>0.231712242436744</v>
       </c>
       <c r="F32" s="11" t="n">
         <f aca="false">F141</f>
-        <v>0.210242041964671</v>
+        <v>0.210182526388592</v>
       </c>
       <c r="G32" s="11" t="n">
         <f aca="false">G141</f>
-        <v>0.208536796000146</v>
+        <v>0.208476698204071</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46390,15 +46390,15 @@
       </c>
       <c r="E33" s="11" t="n">
         <f aca="false">E140</f>
-        <v>0.254083490833043</v>
+        <v>0.254035989472809</v>
       </c>
       <c r="F33" s="11" t="n">
         <f aca="false">F140</f>
-        <v>0.2307849589791</v>
+        <v>0.230723930870638</v>
       </c>
       <c r="G33" s="11" t="n">
         <f aca="false">G140</f>
-        <v>0.228929336089136</v>
+        <v>0.228866420513401</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46418,15 +46418,15 @@
       </c>
       <c r="E34" s="16" t="n">
         <f aca="false">E142</f>
-        <v>30.2604206179337</v>
+        <v>30.2294831925502</v>
       </c>
       <c r="F34" s="16" t="n">
         <f aca="false">F142</f>
-        <v>22.7947714688554</v>
+        <v>22.7714918399431</v>
       </c>
       <c r="G34" s="16" t="n">
         <f aca="false">G142</f>
-        <v>22.1787798337895</v>
+        <v>22.1561985937445</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46446,15 +46446,15 @@
       </c>
       <c r="E35" s="13" t="n">
         <f aca="false">E143</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
       <c r="F35" s="13" t="n">
         <f aca="false">F143</f>
-        <v>561.607479096399</v>
+        <v>561.03392591445</v>
       </c>
       <c r="G35" s="13" t="n">
         <f aca="false">G143</f>
-        <v>546.430950137269</v>
+        <v>545.874603550778</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46599,7 +46599,7 @@
       </c>
       <c r="D65" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E65" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -46660,7 +46660,7 @@
       </c>
       <c r="C68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C65+0.25*D65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*C64+0.25*D64)/(0.75*D64+0.25*E64)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D65+0.25*E65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*D64+0.25*E64)/(0.75*D64+0.25*E64)</f>
@@ -46668,15 +46668,15 @@
       </c>
       <c r="E68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E65+0.25*F65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*E64+0.25*F64)/(0.75*D64+0.25*E64)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F65+0.25*G65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*F64+0.25*G64)/(0.75*D64+0.25*E64)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G65+0.25*H65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*G64+0.25*H64)/(0.75*D64+0.25*E64)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46780,15 +46780,15 @@
       </c>
       <c r="E73" s="16" t="n">
         <f aca="false">$D73*E68*E69*E70</f>
-        <v>48.7843396554535</v>
+        <v>48.6070476070838</v>
       </c>
       <c r="F73" s="16" t="n">
         <f aca="false">$D73*F68*F69*F70</f>
-        <v>56.061461770453</v>
+        <v>55.8596083876428</v>
       </c>
       <c r="G73" s="16" t="n">
         <f aca="false">$D73*G68*G69*G70</f>
-        <v>60.9370262140963</v>
+        <v>60.7204049216519</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46808,15 +46808,15 @@
       </c>
       <c r="E74" s="16" t="n">
         <f aca="false">E72+E73</f>
-        <v>175.680278394298</v>
+        <v>175.502986345929</v>
       </c>
       <c r="F74" s="16" t="n">
         <f aca="false">F72+F73</f>
-        <v>204.777192241356</v>
+        <v>204.575338858545</v>
       </c>
       <c r="G74" s="16" t="n">
         <f aca="false">G72+G73</f>
-        <v>223.124652268834</v>
+        <v>222.908030976389</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46864,15 +46864,15 @@
       </c>
       <c r="E76" s="16" t="n">
         <f aca="false">E74+E75</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="F76" s="16" t="n">
         <f aca="false">F74+F75</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G76" s="16" t="n">
         <f aca="false">G74+G75</f>
-        <v>272.551816268834</v>
+        <v>272.335194976389</v>
       </c>
       <c r="J76" s="8" t="s">
         <v>557</v>
@@ -46895,15 +46895,15 @@
       </c>
       <c r="E77" s="11" t="n">
         <f aca="false">E74/E76</f>
-        <v>0.799745325942366</v>
+        <v>0.799583573341746</v>
       </c>
       <c r="F77" s="11" t="n">
         <f aca="false">F74/F76</f>
-        <v>0.814525945464331</v>
+        <v>0.814376909401151</v>
       </c>
       <c r="G77" s="11" t="n">
         <f aca="false">G74/G76</f>
-        <v>0.818650395815939</v>
+        <v>0.818506146426336</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46928,15 +46928,15 @@
       </c>
       <c r="E79" s="16" t="n">
         <f aca="false">$D79+v_s*(E74-$D74)</f>
-        <v>46.0886608620245</v>
+        <v>46.0353343511749</v>
       </c>
       <c r="F79" s="16" t="n">
         <f aca="false">$D79+v_s*(F74-$D74)+0*F74</f>
-        <v>54.8405304818089</v>
+        <v>54.7798163284814</v>
       </c>
       <c r="G79" s="16" t="n">
         <f aca="false">$D79+v_s*(G74-$D74)+0*G74</f>
-        <v>60.3591424850862</v>
+        <v>60.2939863892092</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>560</v>
@@ -46990,15 +46990,15 @@
       </c>
       <c r="E81" s="16" t="n">
         <f aca="false">E79+E80</f>
-        <v>53.0753690197811</v>
+        <v>53.0220425089314</v>
       </c>
       <c r="F81" s="16" t="n">
         <f aca="false">F79+F80</f>
-        <v>62.4623992867873</v>
+        <v>62.4016851334598</v>
       </c>
       <c r="G81" s="16" t="n">
         <f aca="false">G79+G80</f>
-        <v>68.6542815761198</v>
+        <v>68.5891254802428</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47018,15 +47018,15 @@
       </c>
       <c r="E82" s="11" t="n">
         <f aca="false">E79/E74</f>
-        <v>0.262343965317397</v>
+        <v>0.262305134001743</v>
       </c>
       <c r="F82" s="11" t="n">
         <f aca="false">F79/F74</f>
-        <v>0.267805852212157</v>
+        <v>0.267773313411736</v>
       </c>
       <c r="G82" s="11" t="n">
         <f aca="false">G79/G74</f>
-        <v>0.270517586789836</v>
+        <v>0.270488174540448</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47046,15 +47046,15 @@
       </c>
       <c r="E83" s="11" t="n">
         <f aca="false">E81/E76</f>
-        <v>0.24161379230609</v>
+        <v>0.241565998948899</v>
       </c>
       <c r="F83" s="11" t="n">
         <f aca="false">F81/F76</f>
-        <v>0.248451716122154</v>
+        <v>0.248409665426728</v>
       </c>
       <c r="G83" s="11" t="n">
         <f aca="false">G81/G76</f>
-        <v>0.251894419622587</v>
+        <v>0.251855532246537</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47074,15 +47074,15 @@
       </c>
       <c r="E84" s="16" t="n">
         <f aca="false">E81*nioi</f>
-        <v>37.1527583138467</v>
+        <v>37.115429756252</v>
       </c>
       <c r="F84" s="16" t="n">
         <f aca="false">F81*nioi</f>
-        <v>43.7236795007511</v>
+        <v>43.6811795934219</v>
       </c>
       <c r="G84" s="16" t="n">
         <f aca="false">G81*nioi</f>
-        <v>48.0579971032839</v>
+        <v>48.01238783617</v>
       </c>
       <c r="J84" s="8" t="s">
         <v>563</v>
@@ -47105,15 +47105,15 @@
       </c>
       <c r="E85" s="16" t="n">
         <f aca="false">E84*1000/shares</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="F85" s="16" t="n">
         <f aca="false">F84*1000/shares</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="G85" s="16" t="n">
         <f aca="false">G84*1000/shares</f>
-        <v>1184.03163815322</v>
+        <v>1182.90793723952</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47248,7 +47248,7 @@
       </c>
       <c r="D94" s="16" t="n">
         <f aca="false">wfeB_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E94" s="16" t="n">
         <f aca="false">wfeB_27</f>
@@ -47309,7 +47309,7 @@
       </c>
       <c r="C97" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C94+0.25*D94)/(0.75*D94+0.25*E94)+(1-w_cmp)*(0.75*C93+0.25*D93)/(0.75*D93+0.25*E93)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D97" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D94+0.25*E94)/(0.75*D94+0.25*E94)+(1-w_cmp)*(0.75*D93+0.25*E93)/(0.75*D93+0.25*E93)</f>
@@ -47317,15 +47317,15 @@
       </c>
       <c r="E97" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E94+0.25*F94)/(0.75*D94+0.25*E94)+(1-w_cmp)*(0.75*E93+0.25*F93)/(0.75*D93+0.25*E93)</f>
-        <v>1.11044937285547</v>
+        <v>1.10640656170373</v>
       </c>
       <c r="F97" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F94+0.25*G94)/(0.75*D94+0.25*E94)+(1-w_cmp)*(0.75*F93+0.25*G93)/(0.75*D93+0.25*E93)</f>
-        <v>1.09656875569478</v>
+        <v>1.09257647968244</v>
       </c>
       <c r="G97" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G94+0.25*H94)/(0.75*D94+0.25*E94)+(1-w_cmp)*(0.75*G93+0.25*H93)/(0.75*D93+0.25*E93)</f>
-        <v>1.0549269042127</v>
+        <v>1.05108623361855</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47429,15 +47429,15 @@
       </c>
       <c r="E102" s="16" t="n">
         <f aca="false">$D102*E97*E98*E99</f>
-        <v>45.345616559068</v>
+        <v>45.1805268496326</v>
       </c>
       <c r="F102" s="16" t="n">
         <f aca="false">$D102*F97*F98*F99</f>
-        <v>44.269303093965</v>
+        <v>44.1081319171397</v>
       </c>
       <c r="G102" s="16" t="n">
         <f aca="false">$D102*G97*G98*G99</f>
-        <v>42.5881903182448</v>
+        <v>42.433139565856</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47457,15 +47457,15 @@
       </c>
       <c r="E103" s="16" t="n">
         <f aca="false">E101+E102</f>
-        <v>162.469490035978</v>
+        <v>162.304400326542</v>
       </c>
       <c r="F103" s="16" t="n">
         <f aca="false">F101+F102</f>
-        <v>158.613150370459</v>
+        <v>158.451979193634</v>
       </c>
       <c r="G103" s="16" t="n">
         <f aca="false">G101+G102</f>
-        <v>152.589866179176</v>
+        <v>152.434815426787</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47513,15 +47513,15 @@
       </c>
       <c r="E105" s="16" t="n">
         <f aca="false">E103+E104</f>
-        <v>205.629490035978</v>
+        <v>205.464400326542</v>
       </c>
       <c r="F105" s="16" t="n">
         <f aca="false">F103+F104</f>
-        <v>203.499550370459</v>
+        <v>203.338379193634</v>
       </c>
       <c r="G105" s="16" t="n">
         <f aca="false">G103+G104</f>
-        <v>199.271722179176</v>
+        <v>199.116671426787</v>
       </c>
       <c r="J105" s="8" t="s">
         <v>557</v>
@@ -47544,15 +47544,15 @@
       </c>
       <c r="E106" s="11" t="n">
         <f aca="false">E103/E105</f>
-        <v>0.790107926677013</v>
+        <v>0.7899392793525</v>
       </c>
       <c r="F106" s="11" t="n">
         <f aca="false">F103/F105</f>
-        <v>0.779427522477141</v>
+        <v>0.779252691115159</v>
       </c>
       <c r="G106" s="11" t="n">
         <f aca="false">G103/G105</f>
-        <v>0.765737679739497</v>
+        <v>0.765555261317411</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47577,15 +47577,15 @@
       </c>
       <c r="E108" s="16" t="n">
         <f aca="false">$D108+v_s*(E103-$D103)</f>
-        <v>42.1150745946177</v>
+        <v>42.0654183451563</v>
       </c>
       <c r="F108" s="16" t="n">
         <f aca="false">$D108+v_s*(F103-$D103)+0*F103</f>
-        <v>40.9551515134405</v>
+        <v>40.9066738936677</v>
       </c>
       <c r="G108" s="16" t="n">
         <f aca="false">$D108+v_s*(G103-$D103)+0*G103</f>
-        <v>39.1434474199375</v>
+        <v>39.0968107224345</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>560</v>
@@ -47639,15 +47639,15 @@
       </c>
       <c r="E110" s="16" t="n">
         <f aca="false">E108+E109</f>
-        <v>48.9020466997887</v>
+        <v>48.8523904503273</v>
       </c>
       <c r="F110" s="16" t="n">
         <f aca="false">F108+F109</f>
-        <v>48.1575746079894</v>
+        <v>48.1090969882165</v>
       </c>
       <c r="G110" s="16" t="n">
         <f aca="false">G108+G109</f>
-        <v>46.7779395434393</v>
+        <v>46.7313028459363</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47667,15 +47667,15 @@
       </c>
       <c r="E111" s="11" t="n">
         <f aca="false">E108/E103</f>
-        <v>0.259218358999536</v>
+        <v>0.259176080627046</v>
       </c>
       <c r="F111" s="11" t="n">
         <f aca="false">F108/F103</f>
-        <v>0.258207793097768</v>
+        <v>0.258164486817033</v>
       </c>
       <c r="G111" s="11" t="n">
         <f aca="false">G108/G103</f>
-        <v>0.25652717575605</v>
+        <v>0.256482160016865</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47695,15 +47695,15 @@
       </c>
       <c r="E112" s="11" t="n">
         <f aca="false">E110/E105</f>
-        <v>0.237816310740413</v>
+        <v>0.237765716945061</v>
       </c>
       <c r="F112" s="11" t="n">
         <f aca="false">F110/F105</f>
-        <v>0.236647081137631</v>
+        <v>0.23659624503254</v>
       </c>
       <c r="G112" s="11" t="n">
         <f aca="false">G110/G105</f>
-        <v>0.234744493759023</v>
+        <v>0.234693069701694</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47723,15 +47723,15 @@
       </c>
       <c r="E113" s="16" t="n">
         <f aca="false">E110*nioi</f>
-        <v>34.2314326898521</v>
+        <v>34.1966733152291</v>
       </c>
       <c r="F113" s="16" t="n">
         <f aca="false">F110*nioi</f>
-        <v>33.7103022255926</v>
+        <v>33.6763678917516</v>
       </c>
       <c r="G113" s="16" t="n">
         <f aca="false">G110*nioi</f>
-        <v>32.7445576804075</v>
+        <v>32.7119119921554</v>
       </c>
       <c r="J113" s="8" t="s">
         <v>563</v>
@@ -47754,15 +47754,15 @@
       </c>
       <c r="E114" s="16" t="n">
         <f aca="false">E113*1000/shares</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="F114" s="16" t="n">
         <f aca="false">F113*1000/shares</f>
-        <v>830.539489213988</v>
+        <v>829.703430133101</v>
       </c>
       <c r="G114" s="16" t="n">
         <f aca="false">G113*1000/shares</f>
-        <v>806.745903030704</v>
+        <v>805.941593028838</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47897,7 +47897,7 @@
       </c>
       <c r="D123" s="16" t="n">
         <f aca="false">wfeC_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E123" s="16" t="n">
         <f aca="false">wfeC_27</f>
@@ -47958,7 +47958,7 @@
       </c>
       <c r="C126" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C123+0.25*D123)/(0.75*D123+0.25*E123)+(1-w_cmp)*(0.75*C122+0.25*D122)/(0.75*D122+0.25*E122)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D126" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D123+0.25*E123)/(0.75*D123+0.25*E123)+(1-w_cmp)*(0.75*D122+0.25*E122)/(0.75*D122+0.25*E122)</f>
@@ -47966,15 +47966,15 @@
       </c>
       <c r="E126" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E123+0.25*F123)/(0.75*D123+0.25*E123)+(1-w_cmp)*(0.75*E122+0.25*F122)/(0.75*D122+0.25*E122)</f>
-        <v>1.0549269042127</v>
+        <v>1.05108623361855</v>
       </c>
       <c r="F126" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F123+0.25*G123)/(0.75*D123+0.25*E123)+(1-w_cmp)*(0.75*F122+0.25*G122)/(0.75*D122+0.25*E122)</f>
-        <v>0.888359498284378</v>
+        <v>0.885125249362988</v>
       </c>
       <c r="G126" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G123+0.25*H123)/(0.75*D123+0.25*E123)+(1-w_cmp)*(0.75*G122+0.25*H122)/(0.75*D122+0.25*E122)</f>
-        <v>0.888359498284378</v>
+        <v>0.885125249362988</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48078,15 +48078,15 @@
       </c>
       <c r="E131" s="16" t="n">
         <f aca="false">$D131*E126*E127*E128</f>
-        <v>40.35966250773</v>
+        <v>40.2127251527679</v>
       </c>
       <c r="F131" s="16" t="n">
         <f aca="false">$D131*F126*F127*F128</f>
-        <v>31.4140306161021</v>
+        <v>31.2996616080227</v>
       </c>
       <c r="G131" s="16" t="n">
         <f aca="false">$D131*G126*G127*G128</f>
-        <v>30.471609697619</v>
+        <v>30.3606717597821</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48106,15 +48106,15 @@
       </c>
       <c r="E132" s="16" t="n">
         <f aca="false">E130+E131</f>
-        <v>144.605240445094</v>
+        <v>144.458303090132</v>
       </c>
       <c r="F132" s="16" t="n">
         <f aca="false">F130+F131</f>
-        <v>112.553801700422</v>
+        <v>112.439432692342</v>
       </c>
       <c r="G132" s="16" t="n">
         <f aca="false">G130+G131</f>
-        <v>109.177187649409</v>
+        <v>109.066249711572</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48162,15 +48162,15 @@
       </c>
       <c r="E134" s="16" t="n">
         <f aca="false">E132+E133</f>
-        <v>186.520240445094</v>
+        <v>186.373303090132</v>
       </c>
       <c r="F134" s="16" t="n">
         <f aca="false">F132+F133</f>
-        <v>154.887951700422</v>
+        <v>154.773582692342</v>
       </c>
       <c r="G134" s="16" t="n">
         <f aca="false">G132+G133</f>
-        <v>151.934679149409</v>
+        <v>151.823741211572</v>
       </c>
       <c r="J134" s="8" t="s">
         <v>557</v>
@@ -48193,15 +48193,15 @@
       </c>
       <c r="E135" s="11" t="n">
         <f aca="false">E132/E134</f>
-        <v>0.775279080168575</v>
+        <v>0.775101909420313</v>
       </c>
       <c r="F135" s="11" t="n">
         <f aca="false">F132/F134</f>
-        <v>0.726678869884721</v>
+        <v>0.726476900879451</v>
       </c>
       <c r="G135" s="11" t="n">
         <f aca="false">G132/G134</f>
-        <v>0.718579775602427</v>
+        <v>0.718374141232524</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48226,15 +48226,15 @@
       </c>
       <c r="E137" s="16" t="n">
         <f aca="false">$D137+v_s*(E132-$D132)</f>
-        <v>36.741804285041</v>
+        <v>36.6976079630647</v>
       </c>
       <c r="F137" s="16" t="n">
         <f aca="false">$D137+v_s*(F132-$D132)+madjC*F132</f>
-        <v>25.9757245083736</v>
+        <v>25.9424678956417</v>
       </c>
       <c r="G137" s="16" t="n">
         <f aca="false">$D137+v_s*(G132-$D132)+madjC*G132</f>
-        <v>24.9938610846582</v>
+        <v>24.9616021703082</v>
       </c>
       <c r="J137" s="4" t="s">
         <v>560</v>
@@ -48288,15 +48288,15 @@
       </c>
       <c r="E139" s="16" t="n">
         <f aca="false">E137+E138</f>
-        <v>43.2291723113338</v>
+        <v>43.1849759893574</v>
       </c>
       <c r="F139" s="16" t="n">
         <f aca="false">F137+F138</f>
-        <v>32.563959241222</v>
+        <v>32.5307026284901</v>
       </c>
       <c r="G139" s="16" t="n">
         <f aca="false">G137+G138</f>
-        <v>31.6839711911279</v>
+        <v>31.6517122767779</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48316,15 +48316,15 @@
       </c>
       <c r="E140" s="11" t="n">
         <f aca="false">E137/E132</f>
-        <v>0.254083490833043</v>
+        <v>0.254035989472809</v>
       </c>
       <c r="F140" s="11" t="n">
         <f aca="false">F137/F132</f>
-        <v>0.2307849589791</v>
+        <v>0.230723930870638</v>
       </c>
       <c r="G140" s="11" t="n">
         <f aca="false">G137/G132</f>
-        <v>0.228929336089136</v>
+        <v>0.228866420513401</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48344,15 +48344,15 @@
       </c>
       <c r="E141" s="11" t="n">
         <f aca="false">E139/E134</f>
-        <v>0.231766655501708</v>
+        <v>0.231712242436744</v>
       </c>
       <c r="F141" s="11" t="n">
         <f aca="false">F139/F134</f>
-        <v>0.210242041964671</v>
+        <v>0.210182526388592</v>
       </c>
       <c r="G141" s="11" t="n">
         <f aca="false">G139/G134</f>
-        <v>0.208536796000146</v>
+        <v>0.208476698204071</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48372,15 +48372,15 @@
       </c>
       <c r="E142" s="16" t="n">
         <f aca="false">E139*nioi</f>
-        <v>30.2604206179337</v>
+        <v>30.2294831925502</v>
       </c>
       <c r="F142" s="16" t="n">
         <f aca="false">F139*nioi</f>
-        <v>22.7947714688554</v>
+        <v>22.7714918399431</v>
       </c>
       <c r="G142" s="16" t="n">
         <f aca="false">G139*nioi</f>
-        <v>22.1787798337895</v>
+        <v>22.1561985937445</v>
       </c>
       <c r="J142" s="8" t="s">
         <v>563</v>
@@ -48403,15 +48403,15 @@
       </c>
       <c r="E143" s="16" t="n">
         <f aca="false">E142*1000/shares</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
       <c r="F143" s="16" t="n">
         <f aca="false">F142*1000/shares</f>
-        <v>561.607479096399</v>
+        <v>561.03392591445</v>
       </c>
       <c r="G143" s="16" t="n">
         <f aca="false">G142*1000/shares</f>
-        <v>546.430950137269</v>
+        <v>545.874603550778</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48493,27 +48493,27 @@
       </c>
       <c r="E152" s="16" t="n">
         <f aca="false">E5</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="F152" s="16" t="n">
         <f aca="false">F5</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G152" s="16" t="n">
         <f aca="false">G5</f>
-        <v>272.551816268834</v>
+        <v>272.335194976389</v>
       </c>
       <c r="H152" s="22" t="n">
         <f aca="false">G152*(1+H153)</f>
-        <v>293.285319036903</v>
+        <v>293.053815886563</v>
       </c>
       <c r="I152" s="22" t="n">
         <f aca="false">H152*(1+I153)</f>
-        <v>313.239247259247</v>
+        <v>312.992852785297</v>
       </c>
       <c r="J152" s="22" t="n">
         <f aca="false">I152*(1+J153)</f>
-        <v>332.033602094802</v>
+        <v>331.772423952415</v>
       </c>
       <c r="K152" s="8" t="s">
         <v>575</v>
@@ -48532,23 +48532,23 @@
       </c>
       <c r="E153" s="11" t="n">
         <f aca="false">E152/D152-1</f>
-        <v>0.162276605260838</v>
+        <v>0.16133855209486</v>
       </c>
       <c r="F153" s="11" t="n">
         <f aca="false">F152/E152-1</f>
-        <v>0.144472497959382</v>
+        <v>0.14447729305864</v>
       </c>
       <c r="G153" s="11" t="n">
         <f aca="false">G152/F152-1</f>
-        <v>0.0841076752958736</v>
+        <v>0.0841164709466031</v>
       </c>
       <c r="H153" s="23" t="n">
         <f aca="false">$G153+((tp_g+0.02)-$G153)*1/3</f>
-        <v>0.0760717835305824</v>
+        <v>0.0760776472977354</v>
       </c>
       <c r="I153" s="23" t="n">
         <f aca="false">$G153+((tp_g+0.02)-$G153)*2/3</f>
-        <v>0.0680358917652912</v>
+        <v>0.0680388236488677</v>
       </c>
       <c r="J153" s="23" t="n">
         <f aca="false">$G153+((tp_g+0.02)-$G153)*3/3</f>
@@ -48572,27 +48572,27 @@
       </c>
       <c r="E154" s="11" t="n">
         <f aca="false">E155/E152</f>
-        <v>0.169129654614263</v>
+        <v>0.16909619926423</v>
       </c>
       <c r="F154" s="11" t="n">
         <f aca="false">F155/F152</f>
-        <v>0.173916201285508</v>
+        <v>0.17388676579871</v>
       </c>
       <c r="G154" s="11" t="n">
         <f aca="false">G155/G152</f>
-        <v>0.176326093735811</v>
+        <v>0.176298872572576</v>
       </c>
       <c r="H154" s="23" t="n">
         <f aca="false">$G154+($G154-$G154)*1/3</f>
-        <v>0.176326093735811</v>
+        <v>0.176298872572576</v>
       </c>
       <c r="I154" s="23" t="n">
         <f aca="false">$G154+($G154-$G154)*2/3</f>
-        <v>0.176326093735811</v>
+        <v>0.176298872572576</v>
       </c>
       <c r="J154" s="23" t="n">
         <f aca="false">$G154+($G154-$G154)*3/3</f>
-        <v>0.176326093735811</v>
+        <v>0.176298872572576</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48612,27 +48612,27 @@
       </c>
       <c r="E155" s="16" t="n">
         <f aca="false">E12</f>
-        <v>37.1527583138467</v>
+        <v>37.115429756252</v>
       </c>
       <c r="F155" s="16" t="n">
         <f aca="false">F12</f>
-        <v>43.7236795007511</v>
+        <v>43.6811795934219</v>
       </c>
       <c r="G155" s="16" t="n">
         <f aca="false">G12</f>
-        <v>48.0579971032839</v>
+        <v>48.01238783617</v>
       </c>
       <c r="H155" s="22" t="n">
         <f aca="false">H152*H154</f>
-        <v>51.7138546558382</v>
+        <v>51.6650573438922</v>
       </c>
       <c r="I155" s="22" t="n">
         <f aca="false">I152*I154</f>
-        <v>55.2322528739688</v>
+        <v>55.1802870693219</v>
       </c>
       <c r="J155" s="22" t="n">
         <f aca="false">J152*J154</f>
-        <v>58.546188046407</v>
+        <v>58.4911042934813</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48652,27 +48652,27 @@
       </c>
       <c r="E156" s="13" t="n">
         <f aca="false">E13</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="F156" s="13" t="n">
         <f aca="false">F13</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="G156" s="13" t="n">
         <f aca="false">G13</f>
-        <v>1184.03163815322</v>
+        <v>1182.90793723952</v>
       </c>
       <c r="H156" s="24" t="n">
         <f aca="false">$G156*H155/$G155</f>
-        <v>1274.10303662418</v>
+        <v>1272.90079007452</v>
       </c>
       <c r="I156" s="24" t="n">
         <f aca="false">$G156*I155/$G155</f>
-        <v>1360.78777292177</v>
+        <v>1359.5074624529</v>
       </c>
       <c r="J156" s="24" t="n">
         <f aca="false">$G156*J155/$G155</f>
-        <v>1442.43503929707</v>
+        <v>1441.07791020008</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48697,27 +48697,27 @@
       </c>
       <c r="E159" s="16" t="n">
         <f aca="false">E16</f>
-        <v>205.629490035978</v>
+        <v>205.464400326542</v>
       </c>
       <c r="F159" s="16" t="n">
         <f aca="false">F16</f>
-        <v>203.499550370459</v>
+        <v>203.338379193634</v>
       </c>
       <c r="G159" s="16" t="n">
         <f aca="false">G16</f>
-        <v>199.271722179176</v>
+        <v>199.116671426787</v>
       </c>
       <c r="H159" s="22" t="n">
         <f aca="false">G159*(1+H160)</f>
-        <v>199.168683499574</v>
+        <v>199.01552254833</v>
       </c>
       <c r="I159" s="22" t="n">
         <f aca="false">H159*(1+I160)</f>
-        <v>203.100564469193</v>
+        <v>202.945284251276</v>
       </c>
       <c r="J159" s="22" t="n">
         <f aca="false">I159*(1+J160)</f>
-        <v>211.224587047961</v>
+        <v>211.063095621327</v>
       </c>
       <c r="K159" s="8" t="s">
         <v>575</v>
@@ -48736,23 +48736,23 @@
       </c>
       <c r="E160" s="11" t="n">
         <f aca="false">E159/D159-1</f>
-        <v>0.0879867197670787</v>
+        <v>0.0871132292409653</v>
       </c>
       <c r="F160" s="11" t="n">
         <f aca="false">F159/E159-1</f>
-        <v>-0.0103581430131752</v>
+        <v>-0.0103473941448246</v>
       </c>
       <c r="G160" s="11" t="n">
         <f aca="false">G159/F159-1</f>
-        <v>-0.0207756144108756</v>
+        <v>-0.0207619819907515</v>
       </c>
       <c r="H160" s="23" t="n">
         <f aca="false">$G160+((tp_g)-$G160)*1/3</f>
-        <v>-0.000517076273917071</v>
+        <v>-0.000507987993834346</v>
       </c>
       <c r="I160" s="23" t="n">
         <f aca="false">$G160+((tp_g)-$G160)*2/3</f>
-        <v>0.0197414618630415</v>
+        <v>0.0197460060030828</v>
       </c>
       <c r="J160" s="23" t="n">
         <f aca="false">$G160+((tp_g)-$G160)*3/3</f>
@@ -48776,27 +48776,27 @@
       </c>
       <c r="E161" s="11" t="n">
         <f aca="false">E162/E159</f>
-        <v>0.166471417518289</v>
+        <v>0.166436001861542</v>
       </c>
       <c r="F161" s="11" t="n">
         <f aca="false">F162/F159</f>
-        <v>0.165652956796342</v>
+        <v>0.165617371522778</v>
       </c>
       <c r="G161" s="11" t="n">
         <f aca="false">G162/G159</f>
-        <v>0.164321145631316</v>
+        <v>0.164285148791186</v>
       </c>
       <c r="H161" s="23" t="n">
         <f aca="false">$G161+(($G161+nim10)/2-$G161)*1/3</f>
-        <v>0.160424156905418</v>
+        <v>0.160394159538643</v>
       </c>
       <c r="I161" s="23" t="n">
         <f aca="false">$G161+(($G161+nim10)/2-$G161)*2/3</f>
-        <v>0.156527168179519</v>
+        <v>0.156503170286099</v>
       </c>
       <c r="J161" s="23" t="n">
         <f aca="false">$G161+(($G161+nim10)/2-$G161)*3/3</f>
-        <v>0.152630179453621</v>
+        <v>0.152612181033556</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48816,27 +48816,27 @@
       </c>
       <c r="E162" s="16" t="n">
         <f aca="false">E23</f>
-        <v>34.2314326898521</v>
+        <v>34.1966733152291</v>
       </c>
       <c r="F162" s="16" t="n">
         <f aca="false">F23</f>
-        <v>33.7103022255926</v>
+        <v>33.6763678917516</v>
       </c>
       <c r="G162" s="16" t="n">
         <f aca="false">G23</f>
-        <v>32.7445576804075</v>
+        <v>32.7119119921554</v>
       </c>
       <c r="H162" s="22" t="n">
         <f aca="false">H159*H161</f>
-        <v>31.9514681323812</v>
+        <v>31.9209274742832</v>
       </c>
       <c r="I162" s="22" t="n">
         <f aca="false">I159*I161</f>
-        <v>31.7907562120248</v>
+        <v>31.7615803799383</v>
       </c>
       <c r="J162" s="22" t="n">
         <f aca="false">J159*J161</f>
-        <v>32.2392466261473</v>
+        <v>32.2107993584647</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48856,27 +48856,27 @@
       </c>
       <c r="E163" s="13" t="n">
         <f aca="false">E24</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="F163" s="13" t="n">
         <f aca="false">F24</f>
-        <v>830.539489213988</v>
+        <v>829.703430133101</v>
       </c>
       <c r="G163" s="13" t="n">
         <f aca="false">G24</f>
-        <v>806.745903030704</v>
+        <v>805.941593028838</v>
       </c>
       <c r="H163" s="24" t="n">
         <f aca="false">$G163*H162/$G162</f>
-        <v>787.206114164063</v>
+        <v>786.453666962396</v>
       </c>
       <c r="I163" s="24" t="n">
         <f aca="false">$G163*I162/$G162</f>
-        <v>783.246565081702</v>
+        <v>782.527743858553</v>
       </c>
       <c r="J163" s="24" t="n">
         <f aca="false">$G163*J162/$G162</f>
-        <v>794.296273178947</v>
+        <v>793.595402002754</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48901,27 +48901,27 @@
       </c>
       <c r="E166" s="16" t="n">
         <f aca="false">E27</f>
-        <v>186.520240445094</v>
+        <v>186.373303090132</v>
       </c>
       <c r="F166" s="16" t="n">
         <f aca="false">F27</f>
-        <v>154.887951700422</v>
+        <v>154.773582692342</v>
       </c>
       <c r="G166" s="16" t="n">
         <f aca="false">G27</f>
-        <v>151.934679149409</v>
+        <v>151.823741211572</v>
       </c>
       <c r="H166" s="22" t="n">
         <f aca="false">G166*(1+H167)</f>
-        <v>151.016268979652</v>
+        <v>150.906819334518</v>
       </c>
       <c r="I166" s="22" t="n">
         <f aca="false">H166*(1+I167)</f>
-        <v>152.070002373628</v>
+        <v>151.960195411004</v>
       </c>
       <c r="J166" s="22" t="n">
         <f aca="false">I166*(1+J167)</f>
-        <v>155.111402421101</v>
+        <v>154.999399319224</v>
       </c>
       <c r="K166" s="8" t="s">
         <v>575</v>
@@ -48940,23 +48940,23 @@
       </c>
       <c r="E167" s="11" t="n">
         <f aca="false">E166/D166-1</f>
-        <v>-0.0131204209254289</v>
+        <v>-0.0138978672479793</v>
       </c>
       <c r="F167" s="11" t="n">
         <f aca="false">F166/E166-1</f>
-        <v>-0.169591721891351</v>
+        <v>-0.16955068067076</v>
       </c>
       <c r="G167" s="11" t="n">
         <f aca="false">G166/F166-1</f>
-        <v>-0.019067154795389</v>
+        <v>-0.0190590760351782</v>
       </c>
       <c r="H167" s="23" t="n">
         <f aca="false">$G167+((tp_g-0.02)-$G167)*1/3</f>
-        <v>-0.00604476986359267</v>
+        <v>-0.00603938402345213</v>
       </c>
       <c r="I167" s="23" t="n">
         <f aca="false">$G167+((tp_g-0.02)-$G167)*2/3</f>
-        <v>0.00697761506820367</v>
+        <v>0.00698030798827394</v>
       </c>
       <c r="J167" s="23" t="n">
         <f aca="false">$G167+((tp_g-0.02)-$G167)*3/3</f>
@@ -48980,23 +48980,23 @@
       </c>
       <c r="E168" s="11" t="n">
         <f aca="false">E169/E166</f>
-        <v>0.162236658851195</v>
+        <v>0.162198569705721</v>
       </c>
       <c r="F168" s="11" t="n">
         <f aca="false">F169/F166</f>
-        <v>0.14716942937527</v>
+        <v>0.147127768472014</v>
       </c>
       <c r="G168" s="11" t="n">
         <f aca="false">G169/G166</f>
-        <v>0.145975757200102</v>
+        <v>0.14593368874285</v>
       </c>
       <c r="H168" s="23" t="n">
         <f aca="false">$G168+(nim10-$G168)*1/3</f>
-        <v>0.144296909225377</v>
+        <v>0.144268863587209</v>
       </c>
       <c r="I168" s="23" t="n">
         <f aca="false">$G168+(nim10-$G168)*2/3</f>
-        <v>0.142618061250651</v>
+        <v>0.142604038431567</v>
       </c>
       <c r="J168" s="23" t="n">
         <f aca="false">$G168+(nim10-$G168)*3/3</f>
@@ -49020,27 +49020,27 @@
       </c>
       <c r="E169" s="16" t="n">
         <f aca="false">E34</f>
-        <v>30.2604206179337</v>
+        <v>30.2294831925502</v>
       </c>
       <c r="F169" s="16" t="n">
         <f aca="false">F34</f>
-        <v>22.7947714688554</v>
+        <v>22.7714918399431</v>
       </c>
       <c r="G169" s="16" t="n">
         <f aca="false">G34</f>
-        <v>22.1787798337895</v>
+        <v>22.1561985937445</v>
       </c>
       <c r="H169" s="22" t="n">
         <f aca="false">H166*H168</f>
-        <v>21.7911808565119</v>
+        <v>21.7711553329511</v>
       </c>
       <c r="I169" s="22" t="n">
         <f aca="false">I166*I168</f>
-        <v>21.6879289129088</v>
+        <v>21.6701375464593</v>
       </c>
       <c r="J169" s="22" t="n">
         <f aca="false">J166*J168</f>
-        <v>21.8612790273555</v>
+        <v>21.8454933982925</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49060,27 +49060,27 @@
       </c>
       <c r="E170" s="13" t="n">
         <f aca="false">E35</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
       <c r="F170" s="13" t="n">
         <f aca="false">F35</f>
-        <v>561.607479096399</v>
+        <v>561.03392591445</v>
       </c>
       <c r="G170" s="13" t="n">
         <f aca="false">G35</f>
-        <v>546.430950137269</v>
+        <v>545.874603550778</v>
       </c>
       <c r="H170" s="24" t="n">
         <f aca="false">$G170*H169/$G169</f>
-        <v>536.88145828004</v>
+        <v>536.38807830385</v>
       </c>
       <c r="I170" s="24" t="n">
         <f aca="false">$G170*I169/$G169</f>
-        <v>534.337582644438</v>
+        <v>533.8992468412</v>
       </c>
       <c r="J170" s="24" t="n">
         <f aca="false">$G170*J169/$G169</f>
-        <v>538.608505952816</v>
+        <v>538.219586618567</v>
       </c>
     </row>
   </sheetData>
@@ -49160,15 +49160,15 @@
       </c>
       <c r="B8" s="13" t="n">
         <f aca="false">PL!E156</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">PL!E163</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="D8" s="13" t="n">
         <f aca="false">PL!E170</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49177,15 +49177,15 @@
       </c>
       <c r="B9" s="13" t="n">
         <f aca="false">PL!F156</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">PL!F163</f>
-        <v>830.539489213988</v>
+        <v>829.703430133101</v>
       </c>
       <c r="D9" s="13" t="n">
         <f aca="false">PL!F170</f>
-        <v>561.607479096399</v>
+        <v>561.03392591445</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49194,15 +49194,15 @@
       </c>
       <c r="B10" s="13" t="n">
         <f aca="false">PL!G156</f>
-        <v>1184.03163815322</v>
+        <v>1182.90793723952</v>
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">PL!G163</f>
-        <v>806.745903030704</v>
+        <v>805.941593028838</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">PL!G170</f>
-        <v>546.430950137269</v>
+        <v>545.874603550778</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49211,15 +49211,15 @@
       </c>
       <c r="B11" s="13" t="n">
         <f aca="false">PL!H156</f>
-        <v>1274.10303662418</v>
+        <v>1272.90079007452</v>
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">PL!H163</f>
-        <v>787.206114164063</v>
+        <v>786.453666962396</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">PL!H170</f>
-        <v>536.88145828004</v>
+        <v>536.38807830385</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49228,15 +49228,15 @@
       </c>
       <c r="B12" s="13" t="n">
         <f aca="false">PL!I156</f>
-        <v>1360.78777292177</v>
+        <v>1359.5074624529</v>
       </c>
       <c r="C12" s="13" t="n">
         <f aca="false">PL!I163</f>
-        <v>783.246565081702</v>
+        <v>782.527743858553</v>
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">PL!I170</f>
-        <v>534.337582644438</v>
+        <v>533.8992468412</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49245,15 +49245,15 @@
       </c>
       <c r="B13" s="13" t="n">
         <f aca="false">PL!J156</f>
-        <v>1442.43503929707</v>
+        <v>1441.07791020008</v>
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">PL!J163</f>
-        <v>794.296273178947</v>
+        <v>793.595402002754</v>
       </c>
       <c r="D13" s="13" t="n">
         <f aca="false">PL!J170</f>
-        <v>538.608505952816</v>
+        <v>538.219586618567</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49282,15 +49282,15 @@
       </c>
       <c r="B16" s="13" t="n">
         <f aca="false">B8*(1-$B$15)</f>
-        <v>652.572374870218</v>
+        <v>651.916714655859</v>
       </c>
       <c r="C16" s="13" t="n">
         <f aca="false">C8*(1-$B$15)</f>
-        <v>601.260534599427</v>
+        <v>600.650000989644</v>
       </c>
       <c r="D16" s="13" t="n">
         <f aca="false">D8*(1-$B$15)</f>
-        <v>531.511398976182</v>
+        <v>530.967996276864</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49299,15 +49299,15 @@
       </c>
       <c r="B17" s="13" t="n">
         <f aca="false">B9*(1-$B$15)</f>
-        <v>767.98780668824</v>
+        <v>767.241313918489</v>
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">C9*(1-$B$15)</f>
-        <v>592.107099965953</v>
+        <v>591.511057846087</v>
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">D9*(1-$B$15)</f>
-        <v>400.38045160461</v>
+        <v>399.971554838531</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49316,15 +49316,15 @@
       </c>
       <c r="B18" s="13" t="n">
         <f aca="false">B10*(1-$B$15)</f>
-        <v>844.118249209715</v>
+        <v>843.317141859753</v>
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">C10*(1-$B$15)</f>
-        <v>575.144208380741</v>
+        <v>574.570800771755</v>
       </c>
       <c r="D18" s="13" t="n">
         <f aca="false">D10*(1-$B$15)</f>
-        <v>389.560820911258</v>
+        <v>389.164191048162</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49333,15 +49333,15 @@
       </c>
       <c r="B19" s="13" t="n">
         <f aca="false">B11*(1-$B$15)</f>
-        <v>908.331829937811</v>
+        <v>907.474725938294</v>
       </c>
       <c r="C19" s="13" t="n">
         <f aca="false">C11*(1-$B$15)</f>
-        <v>561.213928279643</v>
+        <v>560.677494628694</v>
       </c>
       <c r="D19" s="13" t="n">
         <f aca="false">D11*(1-$B$15)</f>
-        <v>382.752809969981</v>
+        <v>382.401070178343</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49350,15 +49350,15 @@
       </c>
       <c r="B20" s="13" t="n">
         <f aca="false">B12*(1-$B$15)</f>
-        <v>970.130996006429</v>
+        <v>969.218238782214</v>
       </c>
       <c r="C20" s="13" t="n">
         <f aca="false">C12*(1-$B$15)</f>
-        <v>558.391091852505</v>
+        <v>557.878630789112</v>
       </c>
       <c r="D20" s="13" t="n">
         <f aca="false">D12*(1-$B$15)</f>
-        <v>380.93923355991</v>
+        <v>380.62673578631</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49367,15 +49367,15 @@
       </c>
       <c r="B21" s="13" t="n">
         <f aca="false">B13*(1-$B$15)</f>
-        <v>1028.33885576681</v>
+        <v>1027.37133310915</v>
       </c>
       <c r="C21" s="13" t="n">
         <f aca="false">C13*(1-$B$15)</f>
-        <v>566.268634945757</v>
+        <v>565.768970805791</v>
       </c>
       <c r="D21" s="13" t="n">
         <f aca="false">D13*(1-$B$15)</f>
-        <v>383.984054483108</v>
+        <v>383.706786632375</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49384,15 +49384,15 @@
       </c>
       <c r="B22" s="13" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(B16:B21,1/(1+tp_r)^{1;2;3;4;5;6})+B21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>13726.883412508</v>
+        <v>13713.9037829861</v>
       </c>
       <c r="C22" s="13" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(C16:C21,1/(1+tp_r)^{1;2;3;4;5;6})+C21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>8058.23098663888</v>
+        <v>8050.89709161679</v>
       </c>
       <c r="D22" s="13" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(D16:D21,1/(1+tp_r)^{1;2;3;4;5;6})+D21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>5578.45799128314</v>
+        <v>5574.0244255108</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>600</v>
@@ -49404,15 +49404,15 @@
       </c>
       <c r="B23" s="13" t="n">
         <f aca="false">B22*(1+tp_r)</f>
-        <v>15099.5717537588</v>
+        <v>15085.2941612847</v>
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">C22*(1+tp_r)</f>
-        <v>8864.05408530277</v>
+        <v>8855.98680077847</v>
       </c>
       <c r="D23" s="13" t="n">
         <f aca="false">D22*(1+tp_r)</f>
-        <v>6136.30379041145</v>
+        <v>6131.42686806188</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49421,7 +49421,7 @@
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">tp_wA*B23+tp_wB*C23+tp_wC*D23</f>
-        <v>10189.1593268613</v>
+        <v>10179.867022387</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>603</v>
@@ -49585,7 +49585,7 @@
       </c>
       <c r="B35" s="13" t="n">
         <f aca="false">tp_wA*(5/12*B8+7/12*B9)+tp_wB*(5/12*C8+7/12*C9)+tp_wC*(5/12*D8+7/12*D9)</f>
-        <v>848.53101977411</v>
+        <v>847.680120370557</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>631</v>
@@ -49597,7 +49597,7 @@
       </c>
       <c r="B36" s="25" t="n">
         <f aca="false">B34*B35</f>
-        <v>28867.0252927152</v>
+        <v>28838.0776950064</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>633</v>
@@ -49627,7 +49627,7 @@
       </c>
       <c r="B40" s="25" t="n">
         <f aca="false">tp_w_dcf*B24+(1-tp_w_dcf)*tp_comp_adj</f>
-        <v>13020.9578674506</v>
+        <v>13008.3632132389</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>637</v>
@@ -49639,7 +49639,7 @@
       </c>
       <c r="B41" s="13" t="n">
         <f aca="false">B36</f>
-        <v>28867.0252927152</v>
+        <v>28838.0776950064</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>639</v>
@@ -49663,7 +49663,7 @@
       </c>
       <c r="B43" s="11" t="n">
         <f aca="false">B40/px-1</f>
-        <v>-0.161020755963233</v>
+        <v>-0.161832267188213</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>643</v>
@@ -49675,7 +49675,7 @@
       </c>
       <c r="B44" s="11" t="n">
         <f aca="false">B41/px-1</f>
-        <v>0.85998874308732</v>
+        <v>0.858123562822575</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49684,7 +49684,7 @@
       </c>
       <c r="B45" s="11" t="n">
         <f aca="false">B35/cons_feps-1</f>
-        <v>0.0587315895666778</v>
+        <v>0.0576699028904215</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>646</v>
@@ -49709,7 +49709,7 @@
       </c>
       <c r="B47" s="28" t="str">
         <f aca="false">TEXT(D23,"#,##0")&amp;"～"&amp;TEXT(B23,"#,##0")</f>
-        <v>6,136～15,100</v>
+        <v>6,131～15,085</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>649</v>
@@ -49803,15 +49803,15 @@
       </c>
       <c r="B55" s="27" t="n">
         <f aca="false">px/PL!E13</f>
-        <v>16.9552037961398</v>
+        <v>16.9722563617599</v>
       </c>
       <c r="C55" s="27" t="n">
         <f aca="false">px/PL!E24</f>
-        <v>18.4021683961461</v>
+        <v>18.4208733695586</v>
       </c>
       <c r="D55" s="27" t="n">
         <f aca="false">px/PL!E35</f>
-        <v>20.8170466879325</v>
+        <v>20.8383512476072</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49820,15 +49820,15 @@
       </c>
       <c r="B56" s="27" t="n">
         <f aca="false">px/PL!F13</f>
-        <v>14.4071266643782</v>
+        <v>14.4211441784155</v>
       </c>
       <c r="C56" s="27" t="n">
         <f aca="false">px/PL!F24</f>
-        <v>18.6866491016435</v>
+        <v>18.7054788932357</v>
       </c>
       <c r="D56" s="27" t="n">
         <f aca="false">px/PL!F35</f>
-        <v>27.6349596073239</v>
+        <v>27.6632112304143</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49837,15 +49837,15 @@
       </c>
       <c r="B57" s="27" t="n">
         <f aca="false">px/PL!G13</f>
-        <v>13.1077578502945</v>
+        <v>13.1202095373695</v>
       </c>
       <c r="C57" s="27" t="n">
         <f aca="false">px/PL!G24</f>
-        <v>19.2377797540663</v>
+        <v>19.2569785878326</v>
       </c>
       <c r="D57" s="27" t="n">
         <f aca="false">px/PL!G35</f>
-        <v>28.4024907375785</v>
+        <v>28.4314380977724</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50388,7 +50388,7 @@
       </c>
       <c r="C93" s="25" t="n">
         <f aca="false">PL!E13</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="D93" s="31" t="str">
         <f aca="false">"規則值："&amp;D87</f>
@@ -50400,11 +50400,11 @@
       </c>
       <c r="F93" s="25" t="n">
         <f aca="false">C93*E93</f>
-        <v>13288.7605257011</v>
+        <v>13275.4088854687</v>
       </c>
       <c r="G93" s="33" t="n">
         <f aca="false">F93/px-1</f>
-        <v>-0.143765430045035</v>
+        <v>-0.144625716142482</v>
       </c>
       <c r="H93" s="31"/>
     </row>
@@ -50417,7 +50417,7 @@
       </c>
       <c r="C94" s="13" t="n">
         <f aca="false">PL!E13</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>716</v>
@@ -50428,11 +50428,11 @@
       </c>
       <c r="F94" s="13" t="n">
         <f aca="false">C94*E94</f>
-        <v>9357.16472365637</v>
+        <v>9347.76328273616</v>
       </c>
       <c r="G94" s="29" t="n">
         <f aca="false">F94/px-1</f>
-        <v>-0.397089901826265</v>
+        <v>-0.397695664772155</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50444,7 +50444,7 @@
       </c>
       <c r="C95" s="13" t="n">
         <f aca="false">PL!E13</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>717</v>
@@ -50455,11 +50455,11 @@
       </c>
       <c r="F95" s="13" t="n">
         <f aca="false">C95*E95</f>
-        <v>13288.7605257011</v>
+        <v>13275.4088854687</v>
       </c>
       <c r="G95" s="29" t="n">
         <f aca="false">F95/px-1</f>
-        <v>-0.143765430045035</v>
+        <v>-0.144625716142482</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50471,7 +50471,7 @@
       </c>
       <c r="C96" s="13" t="n">
         <f aca="false">PL!E13</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>718</v>
@@ -50482,11 +50482,11 @@
       </c>
       <c r="F96" s="13" t="n">
         <f aca="false">C96*E96</f>
-        <v>16166.196210648</v>
+        <v>16149.9535192914</v>
       </c>
       <c r="G96" s="29" t="n">
         <f aca="false">F96/px-1</f>
-        <v>0.0416363537788662</v>
+        <v>0.040589788614138</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50498,7 +50498,7 @@
       </c>
       <c r="C97" s="13" t="n">
         <f aca="false">PL!F13</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>719</v>
@@ -50509,11 +50509,11 @@
       </c>
       <c r="F97" s="13" t="n">
         <f aca="false">C97*E97</f>
-        <v>15639.0408830409</v>
+        <v>15623.8395597342</v>
       </c>
       <c r="G97" s="29" t="n">
         <f aca="false">F97/px-1</f>
-        <v>0.00767015998974774</v>
+        <v>0.00669069328184468</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50525,7 +50525,7 @@
       </c>
       <c r="C98" s="25" t="n">
         <f aca="false">PL!E24</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="D98" s="31" t="str">
         <f aca="false">"規則值："&amp;D88</f>
@@ -50537,11 +50537,11 @@
       </c>
       <c r="F98" s="25" t="n">
         <f aca="false">C98*E98</f>
-        <v>12243.8637698015</v>
+        <v>12231.431072302</v>
       </c>
       <c r="G98" s="33" t="n">
         <f aca="false">F98/px-1</f>
-        <v>-0.21109125194578</v>
+        <v>-0.211892327815593</v>
       </c>
       <c r="H98" s="31"/>
     </row>
@@ -50554,7 +50554,7 @@
       </c>
       <c r="C99" s="13" t="n">
         <f aca="false">PL!E24</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>716</v>
@@ -50565,11 +50565,11 @@
       </c>
       <c r="F99" s="13" t="n">
         <f aca="false">C99*E99</f>
-        <v>8621.4097941235</v>
+        <v>8612.65541870698</v>
       </c>
       <c r="G99" s="29" t="n">
         <f aca="false">F99/px-1</f>
-        <v>-0.444496791615754</v>
+        <v>-0.445060862196715</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50581,7 +50581,7 @@
       </c>
       <c r="C100" s="13" t="n">
         <f aca="false">PL!E24</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>717</v>
@@ -50592,11 +50592,11 @@
       </c>
       <c r="F100" s="13" t="n">
         <f aca="false">C100*E100</f>
-        <v>12243.8637698015</v>
+        <v>12231.431072302</v>
       </c>
       <c r="G100" s="29" t="n">
         <f aca="false">F100/px-1</f>
-        <v>-0.21109125194578</v>
+        <v>-0.211892327815593</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50608,7 +50608,7 @@
       </c>
       <c r="C101" s="13" t="n">
         <f aca="false">PL!E24</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>718</v>
@@ -50619,11 +50619,11 @@
       </c>
       <c r="F101" s="13" t="n">
         <f aca="false">C101*E101</f>
-        <v>14895.0463586304</v>
+        <v>14879.9215900852</v>
       </c>
       <c r="G101" s="29" t="n">
         <f aca="false">F101/px-1</f>
-        <v>-0.0402676315315448</v>
+        <v>-0.0412421655872959</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50635,7 +50635,7 @@
       </c>
       <c r="C102" s="13" t="n">
         <f aca="false">PL!F24</f>
-        <v>830.539489213988</v>
+        <v>829.703430133101</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>719</v>
@@ -50646,11 +50646,11 @@
       </c>
       <c r="F102" s="13" t="n">
         <f aca="false">C102*E102</f>
-        <v>12057.4663593134</v>
+        <v>12045.3287615554</v>
       </c>
       <c r="G102" s="29" t="n">
         <f aca="false">F102/px-1</f>
-        <v>-0.223101394374139</v>
+        <v>-0.223883456085348</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50662,7 +50662,7 @@
       </c>
       <c r="C103" s="25" t="n">
         <f aca="false">PL!E35</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
       <c r="D103" s="31" t="str">
         <f aca="false">"規則值："&amp;D89</f>
@@ -50674,11 +50674,11 @@
       </c>
       <c r="F103" s="25" t="n">
         <f aca="false">C103*E103</f>
-        <v>7621.28448007056</v>
+        <v>7613.49268752064</v>
       </c>
       <c r="G103" s="33" t="n">
         <f aca="false">F103/px-1</f>
-        <v>-0.508937855665557</v>
+        <v>-0.509439904154598</v>
       </c>
       <c r="H103" s="31"/>
     </row>
@@ -50691,7 +50691,7 @@
       </c>
       <c r="C104" s="13" t="n">
         <f aca="false">PL!E35</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>716</v>
@@ -50702,11 +50702,11 @@
       </c>
       <c r="F104" s="13" t="n">
         <f aca="false">C104*E104</f>
-        <v>7621.28448007056</v>
+        <v>7613.49268752064</v>
       </c>
       <c r="G104" s="29" t="n">
         <f aca="false">F104/px-1</f>
-        <v>-0.508937855665557</v>
+        <v>-0.509439904154598</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50718,7 +50718,7 @@
       </c>
       <c r="C105" s="13" t="n">
         <f aca="false">PL!E35</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>717</v>
@@ -50729,11 +50729,11 @@
       </c>
       <c r="F105" s="13" t="n">
         <f aca="false">C105*E105</f>
-        <v>10823.5162407534</v>
+        <v>10812.4505741418</v>
       </c>
       <c r="G105" s="29" t="n">
         <f aca="false">F105/px-1</f>
-        <v>-0.302608489642176</v>
+        <v>-0.303321483624883</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50745,7 +50745,7 @@
       </c>
       <c r="C106" s="13" t="n">
         <f aca="false">PL!E35</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>718</v>
@@ -50756,11 +50756,11 @@
       </c>
       <c r="F106" s="13" t="n">
         <f aca="false">C106*E106</f>
-        <v>13167.1488020832</v>
+        <v>13153.6870697193</v>
       </c>
       <c r="G106" s="29" t="n">
         <f aca="false">F106/px-1</f>
-        <v>-0.151601236979175</v>
+        <v>-0.152468616641797</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50772,7 +50772,7 @@
       </c>
       <c r="C107" s="13" t="n">
         <f aca="false">PL!F35</f>
-        <v>561.607479096399</v>
+        <v>561.03392591445</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>719</v>
@@ -50783,11 +50783,11 @@
       </c>
       <c r="F107" s="13" t="n">
         <f aca="false">C107*E107</f>
-        <v>8153.21050267235</v>
+        <v>8144.88386885609</v>
       </c>
       <c r="G107" s="29" t="n">
         <f aca="false">F107/px-1</f>
-        <v>-0.474664271735029</v>
+        <v>-0.47520078164587</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50814,7 +50814,7 @@
       </c>
       <c r="B111" s="13" t="n">
         <f aca="false">tp_wA*F93+tp_wB*F98+tp_wC*F103</f>
-        <v>11632.8169386252</v>
+        <v>11621.0367392957</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50823,7 +50823,7 @@
       </c>
       <c r="B112" s="11" t="n">
         <f aca="false">B111/px-1</f>
-        <v>-0.250462826119512</v>
+        <v>-0.251221859581461</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51318,7 +51318,7 @@
       </c>
       <c r="B136" s="25" t="n">
         <f aca="false">Val!$B$36*B135</f>
-        <v>15852.7564080399</v>
+        <v>15836.8594040909</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>769</v>
@@ -51750,27 +51750,27 @@
       </c>
       <c r="C16" s="13" t="n">
         <f aca="false">PL!E13</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="D16" s="11" t="n">
         <f aca="false">C16/B16-1</f>
-        <v>0.121481495914736</v>
+        <v>0.120354707796931</v>
       </c>
       <c r="E16" s="13" t="n">
         <f aca="false">PL!E24</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="F16" s="11" t="n">
         <f aca="false">E16/B16-1</f>
-        <v>0.0332992779707582</v>
+        <v>0.0322500424033756</v>
       </c>
       <c r="G16" s="13" t="n">
         <f aca="false">PL!E35</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
       <c r="H16" s="11" t="n">
         <f aca="false">G16/B16-1</f>
-        <v>-0.0865684454722894</v>
+        <v>-0.0875023128800794</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>806</v>
@@ -51789,27 +51789,27 @@
       </c>
       <c r="C17" s="16" t="n">
         <f aca="false">PL!E5</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="D17" s="11" t="n">
         <f aca="false">C17/B17-1</f>
-        <v>0.187406910239451</v>
+        <v>0.186448574842857</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">PL!E16</f>
-        <v>205.629490035978</v>
+        <v>205.464400326542</v>
       </c>
       <c r="F17" s="11" t="n">
         <f aca="false">E17/B17-1</f>
-        <v>0.111510756951232</v>
+        <v>0.110618380143473</v>
       </c>
       <c r="G17" s="16" t="n">
         <f aca="false">PL!E27</f>
-        <v>186.520240445094</v>
+        <v>186.373303090132</v>
       </c>
       <c r="H17" s="11" t="n">
         <f aca="false">G17/B17-1</f>
-        <v>0.00821751591942665</v>
+        <v>0.00742325994665904</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>809</v>
@@ -51828,27 +51828,27 @@
       </c>
       <c r="C18" s="16" t="n">
         <f aca="false">PL!E9</f>
-        <v>53.0753690197811</v>
+        <v>53.0220425089314</v>
       </c>
       <c r="D18" s="11" t="n">
         <f aca="false">C18/B18-1</f>
-        <v>0.179452644884023</v>
+        <v>0.178267611309586</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">PL!E20</f>
-        <v>48.9020466997887</v>
+        <v>48.8523904503273</v>
       </c>
       <c r="F18" s="11" t="n">
         <f aca="false">E18/B18-1</f>
-        <v>0.0867121488841935</v>
+        <v>0.0856086766739399</v>
       </c>
       <c r="G18" s="16" t="n">
         <f aca="false">PL!E31</f>
-        <v>43.2291723113338</v>
+        <v>43.1849759893574</v>
       </c>
       <c r="H18" s="11" t="n">
         <f aca="false">G18/B18-1</f>
-        <v>-0.0393517264148047</v>
+        <v>-0.0403338669031688</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>166</v>
@@ -51908,27 +51908,27 @@
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">PL!F74/PL!D74-1-(tot_A_28/tot_A_26-1)</f>
-        <v>0.0073550879021187</v>
+        <v>0.0354800724665145</v>
       </c>
       <c r="D21" s="11" t="n">
         <f aca="false">C21-B21</f>
-        <v>0.0073550879021187</v>
+        <v>0.0354800724665145</v>
       </c>
       <c r="E21" s="11" t="n">
         <f aca="false">PL!F103/PL!D103-1-(tot_B_28/tot_B_26-1)</f>
-        <v>-0.149562021514558</v>
+        <v>-0.124494211325816</v>
       </c>
       <c r="F21" s="11" t="n">
         <f aca="false">E21-B21</f>
-        <v>-0.149562021514558</v>
+        <v>-0.124494211325816</v>
       </c>
       <c r="G21" s="11" t="n">
         <f aca="false">PL!F132/PL!D132-1-(tot_C_28/tot_C_26-1)</f>
-        <v>-0.216847709387551</v>
+        <v>-0.196694695586517</v>
       </c>
       <c r="H21" s="11" t="n">
         <f aca="false">G21-B21</f>
-        <v>-0.216847709387551</v>
+        <v>-0.196694695586517</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>817</v>
@@ -52018,11 +52018,11 @@
       </c>
       <c r="C4" s="13" t="n">
         <f aca="false">PL!E76</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="D4" s="13" t="n">
         <f aca="false">PL!E85</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="E4" s="11" t="n">
         <f aca="false">D4/D$4-1</f>
@@ -52030,11 +52030,11 @@
       </c>
       <c r="F4" s="13" t="n">
         <f aca="false">PL!F76</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G4" s="13" t="n">
         <f aca="false">PL!F85</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="H4" s="11" t="n">
         <f aca="false">G4/G$4-1</f>
@@ -52058,27 +52058,27 @@
       </c>
       <c r="C5" s="13" t="n">
         <f aca="false">E76</f>
-        <v>216.259010852662</v>
+        <v>216.085161368338</v>
       </c>
       <c r="D5" s="13" t="n">
         <f aca="false">E85</f>
-        <v>897.657593684067</v>
+        <v>896.755767173028</v>
       </c>
       <c r="E5" s="11" t="n">
         <f aca="false">D5/D$4-1</f>
-        <v>-0.0193319948411186</v>
+        <v>-0.0193319088693749</v>
       </c>
       <c r="F5" s="13" t="n">
         <f aca="false">F76</f>
-        <v>243.531288778779</v>
+        <v>243.337198255823</v>
       </c>
       <c r="G5" s="13" t="n">
         <f aca="false">F85</f>
-        <v>1036.39230618294</v>
+        <v>1035.38548134349</v>
       </c>
       <c r="H5" s="11" t="n">
         <f aca="false">G5/G$4-1</f>
-        <v>-0.0379229878115498</v>
+        <v>-0.037922467352279</v>
       </c>
       <c r="I5" s="13" t="n">
         <f aca="false">D85</f>
@@ -52098,27 +52098,27 @@
       </c>
       <c r="C6" s="13" t="n">
         <f aca="false">E116</f>
-        <v>223.081545935935</v>
+        <v>222.900811323519</v>
       </c>
       <c r="D6" s="13" t="n">
         <f aca="false">E125</f>
-        <v>933.048800247148</v>
+        <v>932.111257834682</v>
       </c>
       <c r="E6" s="11" t="n">
         <f aca="false">D6/D$4-1</f>
-        <v>0.0193319948411184</v>
+        <v>0.0193319088693746</v>
       </c>
       <c r="F6" s="13" t="n">
         <f aca="false">F116</f>
-        <v>259.436313418885</v>
+        <v>259.226544963282</v>
       </c>
       <c r="G6" s="13" t="n">
         <f aca="false">F125</f>
-        <v>1118.89800319414</v>
+        <v>1117.80985067429</v>
       </c>
       <c r="H6" s="11" t="n">
         <f aca="false">G6/G$4-1</f>
-        <v>0.0386665758078548</v>
+        <v>0.0386660451435004</v>
       </c>
       <c r="I6" s="13" t="n">
         <f aca="false">D125</f>
@@ -52138,27 +52138,27 @@
       </c>
       <c r="C7" s="13" t="n">
         <f aca="false">E156</f>
-        <v>214.553377081843</v>
+        <v>214.381248879542</v>
       </c>
       <c r="D7" s="13" t="n">
         <f aca="false">E165</f>
-        <v>888.809792043297</v>
+        <v>887.916894507615</v>
       </c>
       <c r="E7" s="11" t="n">
         <f aca="false">D7/D$4-1</f>
-        <v>-0.0289979922616777</v>
+        <v>-0.0289978633040621</v>
       </c>
       <c r="F7" s="13" t="n">
         <f aca="false">F156</f>
-        <v>239.651543690598</v>
+        <v>239.461277517717</v>
       </c>
       <c r="G7" s="13" t="n">
         <f aca="false">F165</f>
-        <v>1016.2665232955</v>
+        <v>1015.27953688294</v>
       </c>
       <c r="H7" s="11" t="n">
         <f aca="false">G7/G$4-1</f>
-        <v>-0.0566056362187102</v>
+        <v>-0.0566048593567103</v>
       </c>
       <c r="I7" s="13" t="n">
         <f aca="false">D165</f>
@@ -52178,27 +52178,27 @@
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">E196</f>
-        <v>211.764665866555</v>
+        <v>211.595351960362</v>
       </c>
       <c r="D8" s="13" t="n">
         <f aca="false">E205</f>
-        <v>874.343636360638</v>
+        <v>873.465337699664</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">D8/D$4-1</f>
-        <v>-0.044801898044292</v>
+        <v>-0.0448016988047759</v>
       </c>
       <c r="F8" s="13" t="n">
         <f aca="false">F196</f>
-        <v>232.976644939634</v>
+        <v>232.792958361276</v>
       </c>
       <c r="G8" s="13" t="n">
         <f aca="false">F205</f>
-        <v>981.641165184529</v>
+        <v>980.6883097491</v>
       </c>
       <c r="H8" s="11" t="n">
         <f aca="false">G8/G$4-1</f>
-        <v>-0.0887481568439847</v>
+        <v>-0.0887469388544843</v>
       </c>
       <c r="I8" s="13" t="n">
         <f aca="false">D205</f>
@@ -52218,27 +52218,27 @@
       </c>
       <c r="C9" s="13" t="n">
         <f aca="false">E236</f>
-        <v>212.643067258526</v>
+        <v>212.472866892091</v>
       </c>
       <c r="D9" s="13" t="n">
         <f aca="false">E245</f>
-        <v>878.900254205634</v>
+        <v>878.017357122352</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">D9/D$4-1</f>
-        <v>-0.039823909372704</v>
+        <v>-0.0398237322709121</v>
       </c>
       <c r="F9" s="13" t="n">
         <f aca="false">F236</f>
-        <v>235.024416862047</v>
+        <v>234.838711749862</v>
       </c>
       <c r="G9" s="13" t="n">
         <f aca="false">F245</f>
-        <v>992.263773674721</v>
+        <v>991.30044730044</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">G9/G$4-1</f>
-        <v>-0.0788872505279866</v>
+        <v>-0.0788861678706527</v>
       </c>
       <c r="I9" s="13" t="n">
         <f aca="false">D245</f>
@@ -52258,27 +52258,27 @@
       </c>
       <c r="C10" s="13" t="n">
         <f aca="false">E276</f>
-        <v>210.886264474583</v>
+        <v>210.717837028632</v>
       </c>
       <c r="D10" s="13" t="n">
         <f aca="false">E285</f>
-        <v>869.787018515641</v>
+        <v>868.913318276976</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">D10/D$4-1</f>
-        <v>-0.0497798867158801</v>
+        <v>-0.04977966533864</v>
       </c>
       <c r="F10" s="13" t="n">
         <f aca="false">F276</f>
-        <v>230.92887301722</v>
+        <v>230.747204972691</v>
       </c>
       <c r="G10" s="13" t="n">
         <f aca="false">F285</f>
-        <v>971.018556694338</v>
+        <v>970.076172197759</v>
       </c>
       <c r="H10" s="11" t="n">
         <f aca="false">G10/G$4-1</f>
-        <v>-0.0986090631599832</v>
+        <v>-0.0986077098383156</v>
       </c>
       <c r="I10" s="13" t="n">
         <f aca="false">D285</f>
@@ -52298,27 +52298,27 @@
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">E316</f>
-        <v>219.629986896784</v>
+        <v>219.440031130673</v>
       </c>
       <c r="D11" s="13" t="n">
         <f aca="false">E325</f>
-        <v>915.144188921841</v>
+        <v>914.15881271282</v>
       </c>
       <c r="E11" s="11" t="n">
         <f aca="false">D11/D$4-1</f>
-        <v>-0.000228335952132452</v>
+        <v>-0.000300404334791615</v>
       </c>
       <c r="F11" s="13" t="n">
         <f aca="false">F316</f>
-        <v>251.279989854736</v>
+        <v>251.063718373154</v>
       </c>
       <c r="G11" s="13" t="n">
         <f aca="false">F325</f>
-        <v>1076.58790459725</v>
+        <v>1075.46601829179</v>
       </c>
       <c r="H11" s="11" t="n">
         <f aca="false">G11/G$4-1</f>
-        <v>-0.000609645175897788</v>
+        <v>-0.000679735259507264</v>
       </c>
       <c r="I11" s="13" t="n">
         <f aca="false">D325</f>
@@ -52338,27 +52338,27 @@
       </c>
       <c r="C12" s="13" t="n">
         <f aca="false">E356</f>
-        <v>219.710569891813</v>
+        <v>219.545941561184</v>
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">E365</f>
-        <v>915.562205009374</v>
+        <v>914.70821229489</v>
       </c>
       <c r="E12" s="11" t="n">
         <f aca="false">D12/D$4-1</f>
-        <v>0.000228335952132452</v>
+        <v>0.000300404334791171</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">F356</f>
-        <v>251.533194627975</v>
+        <v>251.345759343937</v>
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">F365</f>
-        <v>1077.90137859527</v>
+        <v>1076.92907713054</v>
       </c>
       <c r="H12" s="11" t="n">
         <f aca="false">G12/G$4-1</f>
-        <v>0.000609645175898121</v>
+        <v>0.000679735259507153</v>
       </c>
       <c r="I12" s="13" t="n">
         <f aca="false">D365</f>
@@ -52378,27 +52378,27 @@
       </c>
       <c r="C13" s="13" t="n">
         <f aca="false">E396</f>
-        <v>219.375448545338</v>
+        <v>219.286802521153</v>
       </c>
       <c r="D13" s="13" t="n">
         <f aca="false">E405</f>
-        <v>913.823797122562</v>
+        <v>913.363954891686</v>
       </c>
       <c r="E13" s="11" t="n">
         <f aca="false">D13/D$4-1</f>
-        <v>-0.00167083028509119</v>
+        <v>-0.00116963956104421</v>
       </c>
       <c r="F13" s="13" t="n">
         <f aca="false">F396</f>
-        <v>251.135759582624</v>
+        <v>251.034832891219</v>
       </c>
       <c r="G13" s="13" t="n">
         <f aca="false">F405</f>
-        <v>1075.83972473585</v>
+        <v>1075.31617779331</v>
       </c>
       <c r="H13" s="11" t="n">
         <f aca="false">G13/G$4-1</f>
-        <v>-0.00130417623458445</v>
+        <v>-0.000818966666235155</v>
       </c>
       <c r="I13" s="13" t="n">
         <f aca="false">D405</f>
@@ -52418,27 +52418,27 @@
       </c>
       <c r="C14" s="13" t="n">
         <f aca="false">E436</f>
-        <v>220.112523167739</v>
+        <v>219.802262083092</v>
       </c>
       <c r="D14" s="13" t="n">
         <f aca="false">E445</f>
-        <v>917.647296730175</v>
+        <v>916.037848922109</v>
       </c>
       <c r="E14" s="11" t="n">
         <f aca="false">D14/D$4-1</f>
-        <v>0.00250624542763656</v>
+        <v>0.00175445934156615</v>
       </c>
       <c r="F14" s="13" t="n">
         <f aca="false">F436</f>
-        <v>251.812841229452</v>
+        <v>251.459597809535</v>
       </c>
       <c r="G14" s="13" t="n">
         <f aca="false">F445</f>
-        <v>1079.35201688686</v>
+        <v>1077.51960258796</v>
       </c>
       <c r="H14" s="11" t="n">
         <f aca="false">G14/G$4-1</f>
-        <v>0.00195626435187646</v>
+        <v>0.00122844999935268</v>
       </c>
       <c r="I14" s="13" t="n">
         <f aca="false">D445</f>
@@ -52458,11 +52458,11 @@
       </c>
       <c r="C15" s="13" t="n">
         <f aca="false">E476</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="D15" s="13" t="n">
         <f aca="false">E485</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="E15" s="11" t="n">
         <f aca="false">D15/D$4-1</f>
@@ -52470,11 +52470,11 @@
       </c>
       <c r="F15" s="13" t="n">
         <f aca="false">F476</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G15" s="13" t="n">
         <f aca="false">F485</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="H15" s="11" t="n">
         <f aca="false">G15/G$4-1</f>
@@ -52498,11 +52498,11 @@
       </c>
       <c r="C16" s="13" t="n">
         <f aca="false">E516</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="D16" s="13" t="n">
         <f aca="false">E525</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="E16" s="11" t="n">
         <f aca="false">D16/D$4-1</f>
@@ -52510,11 +52510,11 @@
       </c>
       <c r="F16" s="13" t="n">
         <f aca="false">F516</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G16" s="13" t="n">
         <f aca="false">F525</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="H16" s="11" t="n">
         <f aca="false">G16/G$4-1</f>
@@ -52538,27 +52538,27 @@
       </c>
       <c r="C17" s="13" t="n">
         <f aca="false">E556</f>
-        <v>218.840278394298</v>
+        <v>218.662986345929</v>
       </c>
       <c r="D17" s="13" t="n">
         <f aca="false">E565</f>
-        <v>911.908491113157</v>
+        <v>910.988806651404</v>
       </c>
       <c r="E17" s="11" t="n">
         <f aca="false">D17/D$4-1</f>
-        <v>-0.00376325320528759</v>
+        <v>-0.00376703806821199</v>
       </c>
       <c r="F17" s="13" t="n">
         <f aca="false">F556</f>
-        <v>249.663592241356</v>
+        <v>249.461738858545</v>
       </c>
       <c r="G17" s="13" t="n">
         <f aca="false">F565</f>
-        <v>1070.01075930611</v>
+        <v>1068.96366542102</v>
       </c>
       <c r="H17" s="11" t="n">
         <f aca="false">G17/G$4-1</f>
-        <v>-0.00671517129055088</v>
+        <v>-0.00672170486313772</v>
       </c>
       <c r="I17" s="13" t="n">
         <f aca="false">D565</f>
@@ -52578,27 +52578,27 @@
       </c>
       <c r="C18" s="13" t="n">
         <f aca="false">E596</f>
-        <v>220.500278394298</v>
+        <v>220.322986345929</v>
       </c>
       <c r="D18" s="13" t="n">
         <f aca="false">E605</f>
-        <v>918.797902818058</v>
+        <v>917.878218356306</v>
       </c>
       <c r="E18" s="11" t="n">
         <f aca="false">D18/D$4-1</f>
-        <v>0.00376325320528714</v>
+        <v>0.00376703806821221</v>
       </c>
       <c r="F18" s="13" t="n">
         <f aca="false">F596</f>
-        <v>253.182792241356</v>
+        <v>252.980938858545</v>
       </c>
       <c r="G18" s="13" t="n">
         <f aca="false">F605</f>
-        <v>1084.6163121205</v>
+        <v>1083.56921823541</v>
       </c>
       <c r="H18" s="11" t="n">
         <f aca="false">G18/G$4-1</f>
-        <v>0.00684307931513284</v>
+        <v>0.00684973733672134</v>
       </c>
       <c r="I18" s="13" t="n">
         <f aca="false">D605</f>
@@ -52618,27 +52618,27 @@
       </c>
       <c r="C19" s="13" t="n">
         <f aca="false">E636</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="D19" s="13" t="n">
         <f aca="false">E645</f>
-        <v>884.738249255683</v>
+        <v>884.011174203756</v>
       </c>
       <c r="E19" s="11" t="n">
         <f aca="false">D19/D$4-1</f>
-        <v>-0.0334460488163614</v>
+        <v>-0.033269054429992</v>
       </c>
       <c r="F19" s="13" t="n">
         <f aca="false">F636</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G19" s="13" t="n">
         <f aca="false">F645</f>
-        <v>1015.01891689244</v>
+        <v>1014.19111575789</v>
       </c>
       <c r="H19" s="11" t="n">
         <f aca="false">G19/G$4-1</f>
-        <v>-0.0577637820612464</v>
+        <v>-0.0576162174734134</v>
       </c>
       <c r="I19" s="13" t="n">
         <f aca="false">D645</f>
@@ -52658,27 +52658,27 @@
       </c>
       <c r="C20" s="13" t="n">
         <f aca="false">E676</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="D20" s="13" t="n">
         <f aca="false">E685</f>
-        <v>889.200248480876</v>
+        <v>888.306840718031</v>
       </c>
       <c r="E20" s="11" t="n">
         <f aca="false">D20/D$4-1</f>
-        <v>-0.0285714285714287</v>
+        <v>-0.0285714285714286</v>
       </c>
       <c r="F20" s="13" t="n">
         <f aca="false">F676</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G20" s="13" t="n">
         <f aca="false">F685</f>
-        <v>1046.46622326493</v>
+        <v>1045.44904634799</v>
       </c>
       <c r="H20" s="11" t="n">
         <f aca="false">G20/G$4-1</f>
-        <v>-0.0285714285714285</v>
+        <v>-0.0285714285714286</v>
       </c>
       <c r="I20" s="13" t="n">
         <f aca="false">D685</f>
@@ -52698,11 +52698,11 @@
       </c>
       <c r="C21" s="13" t="n">
         <f aca="false">E716</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="D21" s="13" t="n">
         <f aca="false">E725</f>
-        <v>958.85617488259</v>
+        <v>957.892781595694</v>
       </c>
       <c r="E21" s="11" t="n">
         <f aca="false">D21/D$4-1</f>
@@ -52710,15 +52710,15 @@
       </c>
       <c r="F21" s="13" t="n">
         <f aca="false">F716</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G21" s="13" t="n">
         <f aca="false">F725</f>
-        <v>1128.44165495667</v>
+        <v>1127.34479699985</v>
       </c>
       <c r="H21" s="11" t="n">
         <f aca="false">G21/G$4-1</f>
-        <v>0.0475258928042139</v>
+        <v>0.0475258928042137</v>
       </c>
       <c r="I21" s="13" t="n">
         <f aca="false">D725</f>
@@ -52738,27 +52738,27 @@
       </c>
       <c r="C22" s="13" t="n">
         <f aca="false">E756</f>
-        <v>213.080170042469</v>
+        <v>212.908196755551</v>
       </c>
       <c r="D22" s="13" t="n">
         <f aca="false">E765</f>
-        <v>882.53640759023</v>
+        <v>881.644313662331</v>
       </c>
       <c r="E22" s="11" t="n">
         <f aca="false">D22/D$4-1</f>
-        <v>-0.0358515046259355</v>
+        <v>-0.0358573897316412</v>
       </c>
       <c r="F22" s="13" t="n">
         <f aca="false">F756</f>
-        <v>243.864394474115</v>
+        <v>243.668596692789</v>
       </c>
       <c r="G22" s="13" t="n">
         <f aca="false">F765</f>
-        <v>1039.57110888196</v>
+        <v>1038.55542781342</v>
       </c>
       <c r="H22" s="11" t="n">
         <f aca="false">G22/G$4-1</f>
-        <v>-0.0349721235637543</v>
+        <v>-0.0349769612259385</v>
       </c>
       <c r="I22" s="13" t="n">
         <f aca="false">D765</f>
@@ -52778,27 +52778,27 @@
       </c>
       <c r="C23" s="13" t="n">
         <f aca="false">E796</f>
-        <v>230.653792314013</v>
+        <v>230.467635663225</v>
       </c>
       <c r="D23" s="13" t="n">
         <f aca="false">E805</f>
-        <v>970.047845924569</v>
+        <v>969.082177239729</v>
       </c>
       <c r="E23" s="11" t="n">
         <f aca="false">D23/D$4-1</f>
-        <v>0.0597525077098915</v>
+        <v>0.0597623162194019</v>
       </c>
       <c r="F23" s="13" t="n">
         <f aca="false">F796</f>
-        <v>263.976921853423</v>
+        <v>263.764975801473</v>
       </c>
       <c r="G23" s="13" t="n">
         <f aca="false">F805</f>
-        <v>1140.03386278675</v>
+        <v>1138.93441420741</v>
       </c>
       <c r="H23" s="11" t="n">
         <f aca="false">G23/G$4-1</f>
-        <v>0.0582868726062571</v>
+        <v>0.0582949353765645</v>
       </c>
       <c r="I23" s="13" t="n">
         <f aca="false">D805</f>
@@ -52818,27 +52818,27 @@
       </c>
       <c r="C24" s="13" t="n">
         <f aca="false">PL!E105</f>
-        <v>205.629490035978</v>
+        <v>205.464400326542</v>
       </c>
       <c r="D24" s="13" t="n">
         <f aca="false">PL!E114</f>
-        <v>843.378870679733</v>
+        <v>842.522484609635</v>
       </c>
       <c r="E24" s="11" t="n">
         <f aca="false">D24/D$4-1</f>
-        <v>-0.0786301140635869</v>
+        <v>-0.0786399742692248</v>
       </c>
       <c r="F24" s="13" t="n">
         <f aca="false">PL!F105</f>
-        <v>203.499550370459</v>
+        <v>203.338379193634</v>
       </c>
       <c r="G24" s="13" t="n">
         <f aca="false">PL!F114</f>
-        <v>830.539489213988</v>
+        <v>829.703430133101</v>
       </c>
       <c r="H24" s="11" t="n">
         <f aca="false">G24/G$4-1</f>
-        <v>-0.229014972881835</v>
+        <v>-0.229041701593081</v>
       </c>
       <c r="I24" s="13" t="n">
         <f aca="false">PL!D114</f>
@@ -52858,27 +52858,27 @@
       </c>
       <c r="C25" s="13" t="n">
         <f aca="false">PL!E134</f>
-        <v>186.520240445094</v>
+        <v>186.373303090132</v>
       </c>
       <c r="D25" s="13" t="n">
         <f aca="false">PL!E143</f>
-        <v>745.542834805518</v>
+        <v>744.780612227279</v>
       </c>
       <c r="E25" s="11" t="n">
         <f aca="false">D25/D$4-1</f>
-        <v>-0.185513485639216</v>
+        <v>-0.185527868299622</v>
       </c>
       <c r="F25" s="13" t="n">
         <f aca="false">PL!F134</f>
-        <v>154.887951700422</v>
+        <v>154.773582692342</v>
       </c>
       <c r="G25" s="13" t="n">
         <f aca="false">PL!F143</f>
-        <v>561.607479096399</v>
+        <v>561.03392591445</v>
       </c>
       <c r="H25" s="11" t="n">
         <f aca="false">G25/G$4-1</f>
-        <v>-0.478663009857992</v>
+        <v>-0.47868871555446</v>
       </c>
       <c r="I25" s="13" t="n">
         <f aca="false">PL!D143</f>
@@ -53014,7 +53014,7 @@
       </c>
       <c r="D65" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E65" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="C68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C65+0.25*D65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*C64+0.25*D64)/(0.75*D64+0.25*E64)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D65+0.25*E65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*D64+0.25*E64)/(0.75*D64+0.25*E64)</f>
@@ -53083,15 +53083,15 @@
       </c>
       <c r="E68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E65+0.25*F65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*E64+0.25*F64)/(0.75*D64+0.25*E64)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F65+0.25*G65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*F64+0.25*G64)/(0.75*D64+0.25*E64)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G68" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G65+0.25*H65)/(0.75*D65+0.25*E65)+(1-w_cmp)*(0.75*G64+0.25*H64)/(0.75*D64+0.25*E64)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53195,15 +53195,15 @@
       </c>
       <c r="E73" s="16" t="n">
         <f aca="false">$D73*E68*E69*E70</f>
-        <v>47.8370709242797</v>
+        <v>47.6632214399559</v>
       </c>
       <c r="F73" s="16" t="n">
         <f aca="false">$D73*F68*F69*F70</f>
-        <v>53.9054549458376</v>
+        <v>53.7113644228809</v>
       </c>
       <c r="G73" s="16" t="n">
         <f aca="false">$D73*G68*G69*G70</f>
-        <v>57.4557771935805</v>
+        <v>57.2515311795013</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53223,15 +53223,15 @@
       </c>
       <c r="E74" s="16" t="n">
         <f aca="false">E72+E73</f>
-        <v>172.269010852662</v>
+        <v>172.095161368338</v>
       </c>
       <c r="F74" s="16" t="n">
         <f aca="false">F72+F73</f>
-        <v>196.901888778779</v>
+        <v>196.707798255823</v>
       </c>
       <c r="G74" s="16" t="n">
         <f aca="false">G72+G73</f>
-        <v>210.377845845515</v>
+        <v>210.173599831435</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53279,15 +53279,15 @@
       </c>
       <c r="E76" s="16" t="n">
         <f aca="false">E74+E75</f>
-        <v>216.259010852662</v>
+        <v>216.085161368338</v>
       </c>
       <c r="F76" s="16" t="n">
         <f aca="false">F74+F75</f>
-        <v>243.531288778779</v>
+        <v>243.337198255823</v>
       </c>
       <c r="G76" s="16" t="n">
         <f aca="false">G74+G75</f>
-        <v>259.805009845515</v>
+        <v>259.600763831435</v>
       </c>
       <c r="J76" s="8" t="s">
         <v>557</v>
@@ -53310,15 +53310,15 @@
       </c>
       <c r="E77" s="11" t="n">
         <f aca="false">E74/E76</f>
-        <v>0.796586510654251</v>
+        <v>0.796422856056206</v>
       </c>
       <c r="F77" s="11" t="n">
         <f aca="false">F74/F76</f>
-        <v>0.808528094135955</v>
+        <v>0.808375372387669</v>
       </c>
       <c r="G77" s="11" t="n">
         <f aca="false">G74/G76</f>
-        <v>0.809752844914767</v>
+        <v>0.809603164218368</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53343,15 +53343,15 @@
       </c>
       <c r="E79" s="16" t="n">
         <f aca="false">$D79+v_s*(E74-$D74)</f>
-        <v>45.0626081019437</v>
+        <v>45.0103170573241</v>
       </c>
       <c r="F79" s="16" t="n">
         <f aca="false">$D79+v_s*(F74-$D74)+0*F74</f>
-        <v>52.4717696749759</v>
+        <v>52.4133904612806</v>
       </c>
       <c r="G79" s="16" t="n">
         <f aca="false">$D79+v_s*(G74-$D74)+0*G74</f>
-        <v>56.5251142966705</v>
+        <v>56.4636804794974</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>560</v>
@@ -53405,15 +53405,15 @@
       </c>
       <c r="E81" s="16" t="n">
         <f aca="false">E79+E80</f>
-        <v>52.0493162597002</v>
+        <v>51.9970252150806</v>
       </c>
       <c r="F81" s="16" t="n">
         <f aca="false">F79+F80</f>
-        <v>60.0936384799544</v>
+        <v>60.035259266259</v>
       </c>
       <c r="G81" s="16" t="n">
         <f aca="false">G79+G80</f>
-        <v>64.8202533877042</v>
+        <v>64.7588195705311</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53433,15 +53433,15 @@
       </c>
       <c r="E82" s="11" t="n">
         <f aca="false">E79/E74</f>
-        <v>0.261582787750984</v>
+        <v>0.261543187498386</v>
       </c>
       <c r="F82" s="11" t="n">
         <f aca="false">F79/F74</f>
-        <v>0.266486878314958</v>
+        <v>0.266453038090111</v>
       </c>
       <c r="G82" s="11" t="n">
         <f aca="false">G79/G74</f>
-        <v>0.268683777369687</v>
+        <v>0.268652583030327</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53461,15 +53461,15 @@
       </c>
       <c r="E83" s="11" t="n">
         <f aca="false">E81/E76</f>
-        <v>0.240680450976268</v>
+        <v>0.240632095632179</v>
       </c>
       <c r="F83" s="11" t="n">
         <f aca="false">F81/F76</f>
-        <v>0.246759415520289</v>
+        <v>0.246716324904602</v>
       </c>
       <c r="G83" s="11" t="n">
         <f aca="false">G81/G76</f>
-        <v>0.249495779262485</v>
+        <v>0.249455427691193</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53489,15 +53489,15 @@
       </c>
       <c r="E84" s="16" t="n">
         <f aca="false">E81*nioi</f>
-        <v>36.4345213817901</v>
+        <v>36.3979176505564</v>
       </c>
       <c r="F84" s="16" t="n">
         <f aca="false">F81*nioi</f>
-        <v>42.0655469359681</v>
+        <v>42.0246814863813</v>
       </c>
       <c r="G84" s="16" t="n">
         <f aca="false">G81*nioi</f>
-        <v>45.3741773713929</v>
+        <v>45.3311736993717</v>
       </c>
       <c r="J84" s="8" t="s">
         <v>563</v>
@@ -53520,15 +53520,15 @@
       </c>
       <c r="E85" s="16" t="n">
         <f aca="false">E84*1000/shares</f>
-        <v>897.657593684067</v>
+        <v>896.755767173028</v>
       </c>
       <c r="F85" s="16" t="n">
         <f aca="false">F84*1000/shares</f>
-        <v>1036.39230618294</v>
+        <v>1035.38548134349</v>
       </c>
       <c r="G85" s="16" t="n">
         <f aca="false">G84*1000/shares</f>
-        <v>1117.90887679824</v>
+        <v>1116.84937138189</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53663,7 +53663,7 @@
       </c>
       <c r="D105" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E105" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -53724,7 +53724,7 @@
       </c>
       <c r="C108" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C105+0.25*D105)/(0.75*D105+0.25*E105)+(1-w_cmp)*(0.75*C104+0.25*D104)/(0.75*D104+0.25*E104)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D108" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D105+0.25*E105)/(0.75*D105+0.25*E105)+(1-w_cmp)*(0.75*D104+0.25*E104)/(0.75*D104+0.25*E104)</f>
@@ -53732,15 +53732,15 @@
       </c>
       <c r="E108" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E105+0.25*F105)/(0.75*D105+0.25*E105)+(1-w_cmp)*(0.75*E104+0.25*F104)/(0.75*D104+0.25*E104)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F108" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F105+0.25*G105)/(0.75*D105+0.25*E105)+(1-w_cmp)*(0.75*F104+0.25*G104)/(0.75*D104+0.25*E104)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G108" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G105+0.25*H105)/(0.75*D105+0.25*E105)+(1-w_cmp)*(0.75*G104+0.25*H104)/(0.75*D104+0.25*E104)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53844,15 +53844,15 @@
       </c>
       <c r="E113" s="16" t="n">
         <f aca="false">$D113*E108*E109*E110</f>
-        <v>49.7316083866274</v>
+        <v>49.5508737742116</v>
       </c>
       <c r="F113" s="16" t="n">
         <f aca="false">$D113*F108*F109*F110</f>
-        <v>58.2597432386883</v>
+        <v>58.0499747830862</v>
       </c>
       <c r="G113" s="16" t="n">
         <f aca="false">$D113*G108*G109*G110</f>
-        <v>64.5561288145101</v>
+        <v>64.3266421964748</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53872,15 +53872,15 @@
       </c>
       <c r="E114" s="16" t="n">
         <f aca="false">E112+E113</f>
-        <v>179.091545935935</v>
+        <v>178.910811323519</v>
       </c>
       <c r="F114" s="16" t="n">
         <f aca="false">F112+F113</f>
-        <v>212.806913418885</v>
+        <v>212.597144963282</v>
       </c>
       <c r="G114" s="16" t="n">
         <f aca="false">G112+G113</f>
-        <v>236.376218014846</v>
+        <v>236.146731396811</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53928,15 +53928,15 @@
       </c>
       <c r="E116" s="16" t="n">
         <f aca="false">E114+E115</f>
-        <v>223.081545935935</v>
+        <v>222.900811323519</v>
       </c>
       <c r="F116" s="16" t="n">
         <f aca="false">F114+F115</f>
-        <v>259.436313418885</v>
+        <v>259.226544963282</v>
       </c>
       <c r="G116" s="16" t="n">
         <f aca="false">G114+G115</f>
-        <v>285.803382014846</v>
+        <v>285.573895396811</v>
       </c>
       <c r="J116" s="8" t="s">
         <v>557</v>
@@ -53959,15 +53959,15 @@
       </c>
       <c r="E117" s="11" t="n">
         <f aca="false">E114/E116</f>
-        <v>0.802807534727085</v>
+        <v>0.802647645206851</v>
       </c>
       <c r="F117" s="11" t="n">
         <f aca="false">F114/F116</f>
-        <v>0.820266487040646</v>
+        <v>0.820121045062709</v>
       </c>
       <c r="G117" s="11" t="n">
         <f aca="false">G114/G116</f>
-        <v>0.827058855456677</v>
+        <v>0.826919880294661</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53992,15 +53992,15 @@
       </c>
       <c r="E119" s="16" t="n">
         <f aca="false">$D119+v_s*(E114-$D114)</f>
-        <v>47.1147136221054</v>
+        <v>47.0603516450257</v>
       </c>
       <c r="F119" s="16" t="n">
         <f aca="false">$D119+v_s*(F114-$D114)+0*F114</f>
-        <v>57.255737578972</v>
+        <v>57.1926427028823</v>
       </c>
       <c r="G119" s="16" t="n">
         <f aca="false">$D119+v_s*(G114-$D114)+0*G114</f>
-        <v>64.3449939151281</v>
+        <v>64.2759681424607</v>
       </c>
       <c r="J119" s="4" t="s">
         <v>560</v>
@@ -54054,15 +54054,15 @@
       </c>
       <c r="E121" s="16" t="n">
         <f aca="false">E119+E120</f>
-        <v>54.1014217798619</v>
+        <v>54.0470598027822</v>
       </c>
       <c r="F121" s="16" t="n">
         <f aca="false">F119+F120</f>
-        <v>64.8776063839504</v>
+        <v>64.8145115078607</v>
       </c>
       <c r="G121" s="16" t="n">
         <f aca="false">G119+G120</f>
-        <v>72.6401330061617</v>
+        <v>72.5711072334943</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54082,15 +54082,15 @@
       </c>
       <c r="E122" s="11" t="n">
         <f aca="false">E119/E114</f>
-        <v>0.263076145643186</v>
+        <v>0.263038053971639</v>
       </c>
       <c r="F122" s="11" t="n">
         <f aca="false">F119/F114</f>
-        <v>0.269050176327077</v>
+        <v>0.269018865294546</v>
       </c>
       <c r="G122" s="11" t="n">
         <f aca="false">G119/G114</f>
-        <v>0.272214330424251</v>
+        <v>0.272186567064755</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54110,15 +54110,15 @@
       </c>
       <c r="E123" s="11" t="n">
         <f aca="false">E121/E116</f>
-        <v>0.242518589123454</v>
+        <v>0.242471346254267</v>
       </c>
       <c r="F123" s="11" t="n">
         <f aca="false">F121/F116</f>
-        <v>0.250071416483626</v>
+        <v>0.250030379863456</v>
       </c>
       <c r="G123" s="11" t="n">
         <f aca="false">G121/G116</f>
-        <v>0.254161208639541</v>
+        <v>0.254123743112638</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54138,15 +54138,15 @@
       </c>
       <c r="E124" s="16" t="n">
         <f aca="false">E121*nioi</f>
-        <v>37.8709952459033</v>
+        <v>37.8329418619475</v>
       </c>
       <c r="F124" s="16" t="n">
         <f aca="false">F121*nioi</f>
-        <v>45.4143244687653</v>
+        <v>45.3701580555025</v>
       </c>
       <c r="G124" s="16" t="n">
         <f aca="false">G121*nioi</f>
-        <v>50.8480931043132</v>
+        <v>50.799775063446</v>
       </c>
       <c r="J124" s="8" t="s">
         <v>563</v>
@@ -54169,15 +54169,15 @@
       </c>
       <c r="E125" s="16" t="n">
         <f aca="false">E124*1000/shares</f>
-        <v>933.048800247148</v>
+        <v>932.111257834682</v>
       </c>
       <c r="F125" s="16" t="n">
         <f aca="false">F124*1000/shares</f>
-        <v>1118.89800319414</v>
+        <v>1117.80985067429</v>
       </c>
       <c r="G125" s="16" t="n">
         <f aca="false">G124*1000/shares</f>
-        <v>1252.77278713627</v>
+        <v>1251.58234865509</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54312,7 +54312,7 @@
       </c>
       <c r="D145" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E145" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -54373,7 +54373,7 @@
       </c>
       <c r="C148" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C145+0.25*D145)/(0.75*D145+0.25*E145)+(1-w_cmp)*(0.75*C144+0.25*D144)/(0.75*D144+0.25*E144)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D148" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D145+0.25*E145)/(0.75*D145+0.25*E145)+(1-w_cmp)*(0.75*D144+0.25*E144)/(0.75*D144+0.25*E144)</f>
@@ -54381,15 +54381,15 @@
       </c>
       <c r="E148" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E145+0.25*F145)/(0.75*D145+0.25*E145)+(1-w_cmp)*(0.75*E144+0.25*F144)/(0.75*D144+0.25*E144)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F148" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F145+0.25*G145)/(0.75*D145+0.25*E145)+(1-w_cmp)*(0.75*F144+0.25*G144)/(0.75*D144+0.25*E144)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G148" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G145+0.25*H145)/(0.75*D145+0.25*E145)+(1-w_cmp)*(0.75*G144+0.25*H144)/(0.75*D144+0.25*E144)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54493,15 +54493,15 @@
       </c>
       <c r="E153" s="16" t="n">
         <f aca="false">$D153*E148*E149*E150</f>
-        <v>47.3634365586928</v>
+        <v>47.191308356392</v>
       </c>
       <c r="F153" s="16" t="n">
         <f aca="false">$D153*F148*F149*F150</f>
-        <v>52.8433045248873</v>
+        <v>52.6530383520056</v>
       </c>
       <c r="G153" s="16" t="n">
         <f aca="false">$D153*G148*G149*G150</f>
-        <v>55.766011285615</v>
+        <v>55.5677721165963</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54521,15 +54521,15 @@
       </c>
       <c r="E154" s="16" t="n">
         <f aca="false">E152+E153</f>
-        <v>170.563377081843</v>
+        <v>170.391248879542</v>
       </c>
       <c r="F154" s="16" t="n">
         <f aca="false">F152+F153</f>
-        <v>193.022143690598</v>
+        <v>192.831877517717</v>
       </c>
       <c r="G154" s="16" t="n">
         <f aca="false">G152+G153</f>
-        <v>204.190664519897</v>
+        <v>203.992425350878</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54577,15 +54577,15 @@
       </c>
       <c r="E156" s="16" t="n">
         <f aca="false">E154+E155</f>
-        <v>214.553377081843</v>
+        <v>214.381248879542</v>
       </c>
       <c r="F156" s="16" t="n">
         <f aca="false">F154+F155</f>
-        <v>239.651543690598</v>
+        <v>239.461277517717</v>
       </c>
       <c r="G156" s="16" t="n">
         <f aca="false">G154+G155</f>
-        <v>253.617828519897</v>
+        <v>253.419589350878</v>
       </c>
       <c r="J156" s="8" t="s">
         <v>557</v>
@@ -54608,15 +54608,15 @@
       </c>
       <c r="E157" s="11" t="n">
         <f aca="false">E154/E156</f>
-        <v>0.794969435586094</v>
+        <v>0.79480481511367</v>
       </c>
       <c r="F157" s="11" t="n">
         <f aca="false">F154/F156</f>
-        <v>0.80542833448133</v>
+        <v>0.805273735764856</v>
       </c>
       <c r="G157" s="11" t="n">
         <f aca="false">G154/G156</f>
-        <v>0.805111634744076</v>
+        <v>0.80495918201665</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54641,15 +54641,15 @@
       </c>
       <c r="E159" s="16" t="n">
         <f aca="false">$D159+v_s*(E154-$D154)</f>
-        <v>44.5495817219032</v>
+        <v>44.4978084103987</v>
       </c>
       <c r="F159" s="16" t="n">
         <f aca="false">$D159+v_s*(F154-$D154)+0*F154</f>
-        <v>51.3048066304332</v>
+        <v>51.2475777178802</v>
       </c>
       <c r="G159" s="16" t="n">
         <f aca="false">$D159+v_s*(G154-$D154)+0*G154</f>
-        <v>54.6641126605384</v>
+        <v>54.6044856028406</v>
       </c>
       <c r="J159" s="4" t="s">
         <v>560</v>
@@ -54703,15 +54703,15 @@
       </c>
       <c r="E161" s="16" t="n">
         <f aca="false">E159+E160</f>
-        <v>51.5362898796598</v>
+        <v>51.4845165681552</v>
       </c>
       <c r="F161" s="16" t="n">
         <f aca="false">F159+F160</f>
-        <v>58.9266754354116</v>
+        <v>58.8694465228586</v>
       </c>
       <c r="G161" s="16" t="n">
         <f aca="false">G159+G160</f>
-        <v>62.959251751572</v>
+        <v>62.8996246938742</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54731,15 +54731,15 @@
       </c>
       <c r="E162" s="11" t="n">
         <f aca="false">E159/E154</f>
-        <v>0.261190781304281</v>
+        <v>0.261150785049157</v>
       </c>
       <c r="F162" s="11" t="n">
         <f aca="false">F159/F154</f>
-        <v>0.265797517577421</v>
+        <v>0.265762997164055</v>
       </c>
       <c r="G162" s="11" t="n">
         <f aca="false">G159/G154</f>
-        <v>0.267711125721968</v>
+        <v>0.267678986162931</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54759,15 +54759,15 @@
       </c>
       <c r="E163" s="11" t="n">
         <f aca="false">E161/E156</f>
-        <v>0.240202650643904</v>
+        <v>0.240154009911024</v>
       </c>
       <c r="F163" s="11" t="n">
         <f aca="false">F161/F156</f>
-        <v>0.245884814793803</v>
+        <v>0.245841194589397</v>
       </c>
       <c r="G163" s="11" t="n">
         <f aca="false">G161/G156</f>
-        <v>0.248244581696009</v>
+        <v>0.248203482828571</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54787,15 +54787,15 @@
       </c>
       <c r="E164" s="16" t="n">
         <f aca="false">E161*nioi</f>
-        <v>36.0754029157618</v>
+        <v>36.0391615977087</v>
       </c>
       <c r="F164" s="16" t="n">
         <f aca="false">F161*nioi</f>
-        <v>41.2486728047882</v>
+        <v>41.208612566001</v>
       </c>
       <c r="G164" s="16" t="n">
         <f aca="false">G161*nioi</f>
-        <v>44.0714762261004</v>
+        <v>44.029737285712</v>
       </c>
       <c r="J164" s="8" t="s">
         <v>563</v>
@@ -54818,15 +54818,15 @@
       </c>
       <c r="E165" s="16" t="n">
         <f aca="false">E164*1000/shares</f>
-        <v>888.809792043297</v>
+        <v>887.916894507615</v>
       </c>
       <c r="F165" s="16" t="n">
         <f aca="false">F164*1000/shares</f>
-        <v>1016.2665232955</v>
+        <v>1015.27953688294</v>
       </c>
       <c r="G165" s="16" t="n">
         <f aca="false">G164*1000/shares</f>
-        <v>1085.81350320684</v>
+        <v>1084.78515768805</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54961,7 +54961,7 @@
       </c>
       <c r="D185" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E185" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -55022,7 +55022,7 @@
       </c>
       <c r="C188" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C185+0.25*D185)/(0.75*D185+0.25*E185)+(1-w_cmp)*(0.75*C184+0.25*D184)/(0.75*D184+0.25*E184)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D188" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D185+0.25*E185)/(0.75*D185+0.25*E185)+(1-w_cmp)*(0.75*D184+0.25*E184)/(0.75*D184+0.25*E184)</f>
@@ -55030,15 +55030,15 @@
       </c>
       <c r="E188" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E185+0.25*F185)/(0.75*D185+0.25*E185)+(1-w_cmp)*(0.75*E184+0.25*F184)/(0.75*D184+0.25*E184)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F188" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F185+0.25*G185)/(0.75*D185+0.25*E185)+(1-w_cmp)*(0.75*F184+0.25*G184)/(0.75*D184+0.25*E184)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G188" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G185+0.25*H185)/(0.75*D185+0.25*E185)+(1-w_cmp)*(0.75*G184+0.25*H184)/(0.75*D184+0.25*E184)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55142,15 +55142,15 @@
       </c>
       <c r="E193" s="16" t="n">
         <f aca="false">$D193*E188*E189*E190</f>
-        <v>46.5890443709581</v>
+        <v>46.419730464765</v>
       </c>
       <c r="F193" s="16" t="n">
         <f aca="false">$D193*F188*F189*F190</f>
-        <v>51.0159302111122</v>
+        <v>50.8322436327549</v>
       </c>
       <c r="G193" s="16" t="n">
         <f aca="false">$D193*G188*G189*G190</f>
-        <v>55.4526938548276</v>
+        <v>55.2555684787033</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55170,15 +55170,15 @@
       </c>
       <c r="E194" s="16" t="n">
         <f aca="false">E192+E193</f>
-        <v>167.774665866555</v>
+        <v>167.605351960362</v>
       </c>
       <c r="F194" s="16" t="n">
         <f aca="false">F192+F193</f>
-        <v>186.347244939634</v>
+        <v>186.163558361276</v>
       </c>
       <c r="G194" s="16" t="n">
         <f aca="false">G192+G193</f>
-        <v>203.043433564639</v>
+        <v>202.846308188514</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55226,15 +55226,15 @@
       </c>
       <c r="E196" s="16" t="n">
         <f aca="false">E194+E195</f>
-        <v>211.764665866555</v>
+        <v>211.595351960362</v>
       </c>
       <c r="F196" s="16" t="n">
         <f aca="false">F194+F195</f>
-        <v>232.976644939634</v>
+        <v>232.792958361276</v>
       </c>
       <c r="G196" s="16" t="n">
         <f aca="false">G194+G195</f>
-        <v>252.470597564639</v>
+        <v>252.273472188514</v>
       </c>
       <c r="J196" s="8" t="s">
         <v>557</v>
@@ -55257,15 +55257,15 @@
       </c>
       <c r="E197" s="11" t="n">
         <f aca="false">E194/E196</f>
-        <v>0.792269405190946</v>
+        <v>0.792103183777682</v>
       </c>
       <c r="F197" s="11" t="n">
         <f aca="false">F194/F196</f>
-        <v>0.799853757821596</v>
+        <v>0.799695831316191</v>
       </c>
       <c r="G197" s="11" t="n">
         <f aca="false">G194/G196</f>
-        <v>0.804226058492433</v>
+        <v>0.804073081599856</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55290,15 +55290,15 @@
       </c>
       <c r="E199" s="16" t="n">
         <f aca="false">$D199+v_s*(E194-$D194)</f>
-        <v>43.7107835905371</v>
+        <v>43.6598567726757</v>
       </c>
       <c r="F199" s="16" t="n">
         <f aca="false">$D199+v_s*(F194-$D194)+0*F194</f>
-        <v>49.2971076730535</v>
+        <v>49.2418577935255</v>
       </c>
       <c r="G199" s="16" t="n">
         <f aca="false">$D199+v_s*(G194-$D194)+0*G194</f>
-        <v>54.3190445960358</v>
+        <v>54.2597525487878</v>
       </c>
       <c r="J199" s="4" t="s">
         <v>560</v>
@@ -55352,15 +55352,15 @@
       </c>
       <c r="E201" s="16" t="n">
         <f aca="false">E199+E200</f>
-        <v>50.6974917482937</v>
+        <v>50.6465649304322</v>
       </c>
       <c r="F201" s="16" t="n">
         <f aca="false">F199+F200</f>
-        <v>56.9189764780319</v>
+        <v>56.8637265985039</v>
       </c>
       <c r="G201" s="16" t="n">
         <f aca="false">G199+G200</f>
-        <v>62.6141836870694</v>
+        <v>62.5548916398214</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55380,15 +55380,15 @@
       </c>
       <c r="E202" s="11" t="n">
         <f aca="false">E199/E194</f>
-        <v>0.260532681527162</v>
+        <v>0.260492020463649</v>
       </c>
       <c r="F202" s="11" t="n">
         <f aca="false">F199/F194</f>
-        <v>0.264544333290375</v>
+        <v>0.264508576366835</v>
       </c>
       <c r="G202" s="11" t="n">
         <f aca="false">G199/G194</f>
-        <v>0.267524261397714</v>
+        <v>0.267491940244541</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55408,15 +55408,15 @@
       </c>
       <c r="E203" s="11" t="n">
         <f aca="false">E201/E196</f>
-        <v>0.239404867383499</v>
+        <v>0.239355753617498</v>
       </c>
       <c r="F203" s="11" t="n">
         <f aca="false">F201/F196</f>
-        <v>0.244311941623076</v>
+        <v>0.244267382479224</v>
       </c>
       <c r="G203" s="11" t="n">
         <f aca="false">G201/G196</f>
-        <v>0.248005844209398</v>
+        <v>0.247964604035245</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55436,15 +55436,15 @@
       </c>
       <c r="E204" s="16" t="n">
         <f aca="false">E201*nioi</f>
-        <v>35.4882442238056</v>
+        <v>35.4525954513026</v>
       </c>
       <c r="F204" s="16" t="n">
         <f aca="false">F201*nioi</f>
-        <v>39.8432835346224</v>
+        <v>39.8046086189527</v>
       </c>
       <c r="G204" s="16" t="n">
         <f aca="false">G201*nioi</f>
-        <v>43.8299285809486</v>
+        <v>43.788424147875</v>
       </c>
       <c r="J204" s="8" t="s">
         <v>563</v>
@@ -55467,15 +55467,15 @@
       </c>
       <c r="E205" s="16" t="n">
         <f aca="false">E204*1000/shares</f>
-        <v>874.343636360638</v>
+        <v>873.465337699664</v>
       </c>
       <c r="F205" s="16" t="n">
         <f aca="false">F204*1000/shares</f>
-        <v>981.641165184529</v>
+        <v>980.6883097491</v>
       </c>
       <c r="G205" s="16" t="n">
         <f aca="false">G204*1000/shares</f>
-        <v>1079.86235935524</v>
+        <v>1078.83979152377</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55610,7 +55610,7 @@
       </c>
       <c r="D225" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E225" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -55671,7 +55671,7 @@
       </c>
       <c r="C228" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C225+0.25*D225)/(0.75*D225+0.25*E225)+(1-w_cmp)*(0.75*C224+0.25*D224)/(0.75*D224+0.25*E224)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D228" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D225+0.25*E225)/(0.75*D225+0.25*E225)+(1-w_cmp)*(0.75*D224+0.25*E224)/(0.75*D224+0.25*E224)</f>
@@ -55679,15 +55679,15 @@
       </c>
       <c r="E228" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E225+0.25*F225)/(0.75*D225+0.25*E225)+(1-w_cmp)*(0.75*E224+0.25*F224)/(0.75*D224+0.25*E224)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F228" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F225+0.25*G225)/(0.75*D225+0.25*E225)+(1-w_cmp)*(0.75*F224+0.25*G224)/(0.75*D224+0.25*E224)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G228" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G225+0.25*H225)/(0.75*D225+0.25*E225)+(1-w_cmp)*(0.75*G224+0.25*H224)/(0.75*D224+0.25*E224)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55791,15 +55791,15 @@
       </c>
       <c r="E233" s="16" t="n">
         <f aca="false">$D233*E228*E229*E230</f>
-        <v>46.8329660692354</v>
+        <v>46.6627657028004</v>
       </c>
       <c r="F233" s="16" t="n">
         <f aca="false">$D233*F228*F229*F230</f>
-        <v>51.5765448288167</v>
+        <v>51.3908397166314</v>
       </c>
       <c r="G233" s="16" t="n">
         <f aca="false">$D233*G228*G229*G230</f>
-        <v>56.0620641169686</v>
+        <v>55.8627725279198</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55819,15 +55819,15 @@
       </c>
       <c r="E234" s="16" t="n">
         <f aca="false">E232+E233</f>
-        <v>168.653067258526</v>
+        <v>168.482866892091</v>
       </c>
       <c r="F234" s="16" t="n">
         <f aca="false">F232+F233</f>
-        <v>188.395016862047</v>
+        <v>188.209311749862</v>
       </c>
       <c r="G234" s="16" t="n">
         <f aca="false">G232+G233</f>
-        <v>205.274680087327</v>
+        <v>205.075388498278</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55875,15 +55875,15 @@
       </c>
       <c r="E236" s="16" t="n">
         <f aca="false">E234+E235</f>
-        <v>212.643067258526</v>
+        <v>212.472866892091</v>
       </c>
       <c r="F236" s="16" t="n">
         <f aca="false">F234+F235</f>
-        <v>235.024416862047</v>
+        <v>234.838711749862</v>
       </c>
       <c r="G236" s="16" t="n">
         <f aca="false">G234+G235</f>
-        <v>254.701844087327</v>
+        <v>254.502552498278</v>
       </c>
       <c r="J236" s="8" t="s">
         <v>557</v>
@@ -55906,15 +55906,15 @@
       </c>
       <c r="E237" s="11" t="n">
         <f aca="false">E234/E236</f>
-        <v>0.793127513785728</v>
+        <v>0.792961799577255</v>
       </c>
       <c r="F237" s="11" t="n">
         <f aca="false">F234/F236</f>
-        <v>0.801597635587922</v>
+        <v>0.801440743510519</v>
       </c>
       <c r="G237" s="11" t="n">
         <f aca="false">G234/G236</f>
-        <v>0.805941083084371</v>
+        <v>0.805789122683418</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55939,15 +55939,15 @@
       </c>
       <c r="E239" s="16" t="n">
         <f aca="false">$D239+v_s*(E234-$D234)</f>
-        <v>43.974992176258</v>
+        <v>43.9237987258423</v>
       </c>
       <c r="F239" s="16" t="n">
         <f aca="false">$D239+v_s*(F234-$D234)+0*F234</f>
-        <v>49.913043540693</v>
+        <v>49.8571865196317</v>
       </c>
       <c r="G239" s="16" t="n">
         <f aca="false">$D239+v_s*(G234-$D234)+0*G234</f>
-        <v>54.9901665837081</v>
+        <v>54.9302229755013</v>
       </c>
       <c r="J239" s="4" t="s">
         <v>560</v>
@@ -56001,15 +56001,15 @@
       </c>
       <c r="E241" s="16" t="n">
         <f aca="false">E239+E240</f>
-        <v>50.9617003340145</v>
+        <v>50.9105068835988</v>
       </c>
       <c r="F241" s="16" t="n">
         <f aca="false">F239+F240</f>
-        <v>57.5349123456714</v>
+        <v>57.4790553246101</v>
       </c>
       <c r="G241" s="16" t="n">
         <f aca="false">G239+G240</f>
-        <v>63.2853056747417</v>
+        <v>63.2253620665349</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56029,15 +56029,15 @@
       </c>
       <c r="E242" s="11" t="n">
         <f aca="false">E239/E234</f>
-        <v>0.260742320854735</v>
+        <v>0.260701871567595</v>
       </c>
       <c r="F242" s="11" t="n">
         <f aca="false">F239/F234</f>
-        <v>0.264938236541798</v>
+        <v>0.264902868280471</v>
       </c>
       <c r="G242" s="11" t="n">
         <f aca="false">G239/G234</f>
-        <v>0.267885774126231</v>
+        <v>0.26785380428994</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56057,15 +56057,15 @@
       </c>
       <c r="E243" s="11" t="n">
         <f aca="false">E241/E236</f>
-        <v>0.239658414407917</v>
+        <v>0.239609450506707</v>
       </c>
       <c r="F243" s="11" t="n">
         <f aca="false">F241/F236</f>
-        <v>0.244803978726359</v>
+        <v>0.244759711447548</v>
       </c>
       <c r="G243" s="11" t="n">
         <f aca="false">G241/G236</f>
-        <v>0.248468187976856</v>
+        <v>0.248427221832923</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56085,15 +56085,15 @@
       </c>
       <c r="E244" s="16" t="n">
         <f aca="false">E241*nioi</f>
-        <v>35.6731902338101</v>
+        <v>35.6373548185192</v>
       </c>
       <c r="F244" s="16" t="n">
         <f aca="false">F241*nioi</f>
-        <v>40.27443864197</v>
+        <v>40.2353387272271</v>
       </c>
       <c r="G244" s="16" t="n">
         <f aca="false">G241*nioi</f>
-        <v>44.2997139723192</v>
+        <v>44.2577534465744</v>
       </c>
       <c r="J244" s="8" t="s">
         <v>563</v>
@@ -56116,15 +56116,15 @@
       </c>
       <c r="E245" s="16" t="n">
         <f aca="false">E244*1000/shares</f>
-        <v>878.900254205634</v>
+        <v>878.017357122352</v>
       </c>
       <c r="F245" s="16" t="n">
         <f aca="false">F244*1000/shares</f>
-        <v>992.263773674721</v>
+        <v>991.30044730044</v>
       </c>
       <c r="G245" s="16" t="n">
         <f aca="false">G244*1000/shares</f>
-        <v>1091.43672366613</v>
+        <v>1090.40291882552</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56259,7 +56259,7 @@
       </c>
       <c r="D265" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E265" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -56320,7 +56320,7 @@
       </c>
       <c r="C268" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C265+0.25*D265)/(0.75*D265+0.25*E265)+(1-w_cmp)*(0.75*C264+0.25*D264)/(0.75*D264+0.25*E264)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D268" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D265+0.25*E265)/(0.75*D265+0.25*E265)+(1-w_cmp)*(0.75*D264+0.25*E264)/(0.75*D264+0.25*E264)</f>
@@ -56328,15 +56328,15 @@
       </c>
       <c r="E268" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E265+0.25*F265)/(0.75*D265+0.25*E265)+(1-w_cmp)*(0.75*E264+0.25*F264)/(0.75*D264+0.25*E264)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F268" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F265+0.25*G265)/(0.75*D265+0.25*E265)+(1-w_cmp)*(0.75*F264+0.25*G264)/(0.75*D264+0.25*E264)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G268" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G265+0.25*H265)/(0.75*D265+0.25*E265)+(1-w_cmp)*(0.75*G264+0.25*H264)/(0.75*D264+0.25*E264)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56440,15 +56440,15 @@
       </c>
       <c r="E273" s="16" t="n">
         <f aca="false">$D273*E268*E269*E270</f>
-        <v>46.3451226726809</v>
+        <v>46.1766952267296</v>
       </c>
       <c r="F273" s="16" t="n">
         <f aca="false">$D273*F268*F269*F270</f>
-        <v>50.4553155934077</v>
+        <v>50.2736475488785</v>
       </c>
       <c r="G273" s="16" t="n">
         <f aca="false">$D273*G268*G269*G270</f>
-        <v>54.8433235926866</v>
+        <v>54.6483644294867</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56468,15 +56468,15 @@
       </c>
       <c r="E274" s="16" t="n">
         <f aca="false">E272+E273</f>
-        <v>166.896264474583</v>
+        <v>166.727837028632</v>
       </c>
       <c r="F274" s="16" t="n">
         <f aca="false">F272+F273</f>
-        <v>184.29947301722</v>
+        <v>184.117804972691</v>
       </c>
       <c r="G274" s="16" t="n">
         <f aca="false">G272+G273</f>
-        <v>200.81218704195</v>
+        <v>200.61722787875</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56524,15 +56524,15 @@
       </c>
       <c r="E276" s="16" t="n">
         <f aca="false">E274+E275</f>
-        <v>210.886264474583</v>
+        <v>210.717837028632</v>
       </c>
       <c r="F276" s="16" t="n">
         <f aca="false">F274+F275</f>
-        <v>230.92887301722</v>
+        <v>230.747204972691</v>
       </c>
       <c r="G276" s="16" t="n">
         <f aca="false">G274+G275</f>
-        <v>250.23935104195</v>
+        <v>250.04439187875</v>
       </c>
       <c r="J276" s="8" t="s">
         <v>557</v>
@@ -56555,15 +56555,15 @@
       </c>
       <c r="E277" s="11" t="n">
         <f aca="false">E274/E276</f>
-        <v>0.791404148062465</v>
+        <v>0.791237416726033</v>
       </c>
       <c r="F277" s="11" t="n">
         <f aca="false">F274/F276</f>
-        <v>0.798078952229924</v>
+        <v>0.797919979115159</v>
       </c>
       <c r="G277" s="11" t="n">
         <f aca="false">G274/G276</f>
-        <v>0.802480450040354</v>
+        <v>0.802326444402049</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56588,15 +56588,15 @@
       </c>
       <c r="E279" s="16" t="n">
         <f aca="false">$D279+v_s*(E274-$D274)</f>
-        <v>43.4465750048163</v>
+        <v>43.3959148195091</v>
       </c>
       <c r="F279" s="16" t="n">
         <f aca="false">$D279+v_s*(F274-$D274)+0*F274</f>
-        <v>48.681171805414</v>
+        <v>48.6265290674193</v>
       </c>
       <c r="G279" s="16" t="n">
         <f aca="false">$D279+v_s*(G274-$D274)+0*G274</f>
-        <v>53.6479226083635</v>
+        <v>53.5892821220743</v>
       </c>
       <c r="J279" s="4" t="s">
         <v>560</v>
@@ -56650,15 +56650,15 @@
       </c>
       <c r="E281" s="16" t="n">
         <f aca="false">E279+E280</f>
-        <v>50.4332831625728</v>
+        <v>50.3826229772656</v>
       </c>
       <c r="F281" s="16" t="n">
         <f aca="false">F279+F280</f>
-        <v>56.3030406103924</v>
+        <v>56.2483978723977</v>
       </c>
       <c r="G281" s="16" t="n">
         <f aca="false">G279+G280</f>
-        <v>61.9430616993972</v>
+        <v>61.8844212131079</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56678,15 +56678,15 @@
       </c>
       <c r="E282" s="11" t="n">
         <f aca="false">E279/E274</f>
-        <v>0.260320835469824</v>
+        <v>0.260279960400714</v>
       </c>
       <c r="F282" s="11" t="n">
         <f aca="false">F279/F274</f>
-        <v>0.264141676633365</v>
+        <v>0.264105522410675</v>
       </c>
       <c r="G282" s="11" t="n">
         <f aca="false">G279/G274</f>
-        <v>0.267154715053008</v>
+        <v>0.26712203477591</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56706,15 +56706,15 @@
       </c>
       <c r="E283" s="11" t="n">
         <f aca="false">E281/E276</f>
-        <v>0.239149208167852</v>
+        <v>0.239099943733855</v>
       </c>
       <c r="F283" s="11" t="n">
         <f aca="false">F281/F276</f>
-        <v>0.243811178198553</v>
+        <v>0.243766323752674</v>
       </c>
       <c r="G283" s="11" t="n">
         <f aca="false">G281/G276</f>
-        <v>0.247535255512284</v>
+        <v>0.247493738004396</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56734,15 +56734,15 @@
       </c>
       <c r="E284" s="16" t="n">
         <f aca="false">E281*nioi</f>
-        <v>35.303298213801</v>
+        <v>35.267836084086</v>
       </c>
       <c r="F284" s="16" t="n">
         <f aca="false">F281*nioi</f>
-        <v>39.4121284272747</v>
+        <v>39.3738785106784</v>
       </c>
       <c r="G284" s="16" t="n">
         <f aca="false">G281*nioi</f>
-        <v>43.360143189578</v>
+        <v>43.3190948491756</v>
       </c>
       <c r="J284" s="8" t="s">
         <v>563</v>
@@ -56765,15 +56765,15 @@
       </c>
       <c r="E285" s="16" t="n">
         <f aca="false">E284*1000/shares</f>
-        <v>869.787018515641</v>
+        <v>868.913318276976</v>
       </c>
       <c r="F285" s="16" t="n">
         <f aca="false">F284*1000/shares</f>
-        <v>971.018556694338</v>
+        <v>970.076172197759</v>
       </c>
       <c r="G285" s="16" t="n">
         <f aca="false">G284*1000/shares</f>
-        <v>1068.28799504435</v>
+        <v>1067.27666422202</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56908,7 +56908,7 @@
       </c>
       <c r="D305" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E305" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -56969,7 +56969,7 @@
       </c>
       <c r="C308" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C305+0.25*D305)/(0.75*D305+0.25*E305)+(1-w_cmp)*(0.75*C304+0.25*D304)/(0.75*D304+0.25*E304)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D308" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D305+0.25*E305)/(0.75*D305+0.25*E305)+(1-w_cmp)*(0.75*D304+0.25*E304)/(0.75*D304+0.25*E304)</f>
@@ -56977,15 +56977,15 @@
       </c>
       <c r="E308" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E305+0.25*F305)/(0.75*D305+0.25*E305)+(1-w_cmp)*(0.75*E304+0.25*F304)/(0.75*D304+0.25*E304)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F308" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F305+0.25*G305)/(0.75*D305+0.25*E305)+(1-w_cmp)*(0.75*F304+0.25*G304)/(0.75*D304+0.25*E304)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G308" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G305+0.25*H305)/(0.75*D305+0.25*E305)+(1-w_cmp)*(0.75*G304+0.25*H304)/(0.75*D304+0.25*E304)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57089,15 +57089,15 @@
       </c>
       <c r="E313" s="16" t="n">
         <f aca="false">$D313*E308*E309*E310</f>
-        <v>52.2689353451288</v>
+        <v>52.0789795790183</v>
       </c>
       <c r="F313" s="16" t="n">
         <f aca="false">$D313*F308*F309*F310</f>
-        <v>60.0658518969139</v>
+        <v>59.8495804153315</v>
       </c>
       <c r="G313" s="16" t="n">
         <f aca="false">$D313*G308*G309*G310</f>
-        <v>65.2896709436746</v>
+        <v>65.0575767017699</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57117,15 +57117,15 @@
       </c>
       <c r="E314" s="16" t="n">
         <f aca="false">E312+E313</f>
-        <v>175.639986896784</v>
+        <v>175.450031130673</v>
       </c>
       <c r="F314" s="16" t="n">
         <f aca="false">F312+F313</f>
-        <v>204.650589854736</v>
+        <v>204.434318373154</v>
       </c>
       <c r="G314" s="16" t="n">
         <f aca="false">G312+G313</f>
-        <v>222.972085163558</v>
+        <v>222.739990921654</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57173,15 +57173,15 @@
       </c>
       <c r="E316" s="16" t="n">
         <f aca="false">E314+E315</f>
-        <v>219.629986896784</v>
+        <v>219.440031130673</v>
       </c>
       <c r="F316" s="16" t="n">
         <f aca="false">F314+F315</f>
-        <v>251.279989854736</v>
+        <v>251.063718373154</v>
       </c>
       <c r="G316" s="16" t="n">
         <f aca="false">G314+G315</f>
-        <v>272.399249163558</v>
+        <v>272.167154921654</v>
       </c>
       <c r="J316" s="8" t="s">
         <v>557</v>
@@ -57204,15 +57204,15 @@
       </c>
       <c r="E317" s="11" t="n">
         <f aca="false">E314/E316</f>
-        <v>0.799708588879198</v>
+        <v>0.799535208898122</v>
       </c>
       <c r="F317" s="11" t="n">
         <f aca="false">F314/F316</f>
-        <v>0.814432498079309</v>
+        <v>0.814272646393713</v>
       </c>
       <c r="G317" s="11" t="n">
         <f aca="false">G314/G316</f>
-        <v>0.818548824375349</v>
+        <v>0.818394089418217</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57237,15 +57237,15 @@
       </c>
       <c r="E319" s="16" t="n">
         <f aca="false">$D319+v_s*(E314-$D314)</f>
-        <v>46.0765418471046</v>
+        <v>46.0194062997657</v>
       </c>
       <c r="F319" s="16" t="n">
         <f aca="false">$D319+v_s*(F314-$D314)+0*F314</f>
-        <v>54.8024505814087</v>
+        <v>54.7373997028436</v>
       </c>
       <c r="G319" s="16" t="n">
         <f aca="false">$D319+v_s*(G314-$D314)+0*G314</f>
-        <v>60.3132528274868</v>
+        <v>60.2434427247615</v>
       </c>
       <c r="J319" s="4" t="s">
         <v>560</v>
@@ -57299,15 +57299,15 @@
       </c>
       <c r="E321" s="16" t="n">
         <f aca="false">E319+E320</f>
-        <v>53.0632500048611</v>
+        <v>53.0061144575222</v>
       </c>
       <c r="F321" s="16" t="n">
         <f aca="false">F319+F320</f>
-        <v>62.4243193863871</v>
+        <v>62.359268507822</v>
       </c>
       <c r="G321" s="16" t="n">
         <f aca="false">G319+G320</f>
-        <v>68.6083919185204</v>
+        <v>68.5385818157951</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57327,15 +57327,15 @@
       </c>
       <c r="E322" s="11" t="n">
         <f aca="false">E319/E314</f>
-        <v>0.262335147372688</v>
+        <v>0.262293520287215</v>
       </c>
       <c r="F322" s="11" t="n">
         <f aca="false">F319/F314</f>
-        <v>0.267785451389651</v>
+        <v>0.267750542758342</v>
       </c>
       <c r="G322" s="11" t="n">
         <f aca="false">G319/G314</f>
-        <v>0.270496877594542</v>
+        <v>0.270465319117085</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57355,15 +57355,15 @@
       </c>
       <c r="E323" s="11" t="n">
         <f aca="false">E321/E316</f>
-        <v>0.241602937534202</v>
+        <v>0.241551708612172</v>
       </c>
       <c r="F323" s="11" t="n">
         <f aca="false">F321/F316</f>
-        <v>0.248425349835753</v>
+        <v>0.248380247500111</v>
       </c>
       <c r="G323" s="11" t="n">
         <f aca="false">G321/G316</f>
-        <v>0.251867037553123</v>
+        <v>0.251825323432303</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57383,15 +57383,15 @@
       </c>
       <c r="E324" s="16" t="n">
         <f aca="false">E321*nioi</f>
-        <v>37.1442750034028</v>
+        <v>37.1042801202656</v>
       </c>
       <c r="F324" s="16" t="n">
         <f aca="false">F321*nioi</f>
-        <v>43.697023570471</v>
+        <v>43.6514879554754</v>
       </c>
       <c r="G324" s="16" t="n">
         <f aca="false">G321*nioi</f>
-        <v>48.0258743429643</v>
+        <v>47.9770072710566</v>
       </c>
       <c r="J324" s="8" t="s">
         <v>563</v>
@@ -57414,15 +57414,15 @@
       </c>
       <c r="E325" s="16" t="n">
         <f aca="false">E324*1000/shares</f>
-        <v>915.144188921841</v>
+        <v>914.15881271282</v>
       </c>
       <c r="F325" s="16" t="n">
         <f aca="false">F324*1000/shares</f>
-        <v>1076.58790459725</v>
+        <v>1075.46601829179</v>
       </c>
       <c r="G325" s="16" t="n">
         <f aca="false">G324*1000/shares</f>
-        <v>1183.24021181805</v>
+        <v>1182.03624655337</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57557,7 +57557,7 @@
       </c>
       <c r="D345" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E345" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -57618,7 +57618,7 @@
       </c>
       <c r="C348" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C345+0.25*D345)/(0.75*D345+0.25*E345)+(1-w_cmp)*(0.75*C344+0.25*D344)/(0.75*D344+0.25*E344)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D348" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D345+0.25*E345)/(0.75*D345+0.25*E345)+(1-w_cmp)*(0.75*D344+0.25*E344)/(0.75*D344+0.25*E344)</f>
@@ -57626,15 +57626,15 @@
       </c>
       <c r="E348" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E345+0.25*F345)/(0.75*D345+0.25*E345)+(1-w_cmp)*(0.75*E344+0.25*F344)/(0.75*D344+0.25*E344)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F348" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F345+0.25*G345)/(0.75*D345+0.25*E345)+(1-w_cmp)*(0.75*F344+0.25*G344)/(0.75*D344+0.25*E344)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G348" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G345+0.25*H345)/(0.75*D345+0.25*E345)+(1-w_cmp)*(0.75*G344+0.25*H344)/(0.75*D344+0.25*E344)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57738,15 +57738,15 @@
       </c>
       <c r="E353" s="16" t="n">
         <f aca="false">$D353*E348*E349*E350</f>
-        <v>45.2997439657783</v>
+        <v>45.1351156351492</v>
       </c>
       <c r="F353" s="16" t="n">
         <f aca="false">$D353*F348*F349*F350</f>
-        <v>52.057071643992</v>
+        <v>51.869636359954</v>
       </c>
       <c r="G353" s="16" t="n">
         <f aca="false">$D353*G348*G349*G350</f>
-        <v>56.584381484518</v>
+        <v>56.3832331415339</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57766,15 +57766,15 @@
       </c>
       <c r="E354" s="16" t="n">
         <f aca="false">E352+E353</f>
-        <v>175.720569891813</v>
+        <v>175.555941561184</v>
       </c>
       <c r="F354" s="16" t="n">
         <f aca="false">F352+F353</f>
-        <v>204.903794627975</v>
+        <v>204.716359343937</v>
       </c>
       <c r="G354" s="16" t="n">
         <f aca="false">G352+G353</f>
-        <v>223.277219374109</v>
+        <v>223.076071031125</v>
       </c>
     </row>
     <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57822,15 +57822,15 @@
       </c>
       <c r="E356" s="16" t="n">
         <f aca="false">E354+E355</f>
-        <v>219.710569891813</v>
+        <v>219.545941561184</v>
       </c>
       <c r="F356" s="16" t="n">
         <f aca="false">F354+F355</f>
-        <v>251.533194627975</v>
+        <v>251.345759343937</v>
       </c>
       <c r="G356" s="16" t="n">
         <f aca="false">G354+G355</f>
-        <v>272.704383374109</v>
+        <v>272.503235031125</v>
       </c>
       <c r="J356" s="8" t="s">
         <v>557</v>
@@ -57853,15 +57853,15 @@
       </c>
       <c r="E357" s="11" t="n">
         <f aca="false">E354/E356</f>
-        <v>0.799782049531523</v>
+        <v>0.799631914454039</v>
       </c>
       <c r="F357" s="11" t="n">
         <f aca="false">F354/F356</f>
-        <v>0.814619298780957</v>
+        <v>0.814481055412623</v>
       </c>
       <c r="G357" s="11" t="n">
         <f aca="false">G354/G356</f>
-        <v>0.818751853606279</v>
+        <v>0.818618065233778</v>
       </c>
     </row>
     <row r="358" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57886,15 +57886,15 @@
       </c>
       <c r="E359" s="16" t="n">
         <f aca="false">$D359+v_s*(E354-$D354)</f>
-        <v>46.1007798769445</v>
+        <v>46.0512624025841</v>
       </c>
       <c r="F359" s="16" t="n">
         <f aca="false">$D359+v_s*(F354-$D354)+0*F354</f>
-        <v>54.8786103822091</v>
+        <v>54.8222329541193</v>
       </c>
       <c r="G359" s="16" t="n">
         <f aca="false">$D359+v_s*(G354-$D354)+0*G354</f>
-        <v>60.4050321426855</v>
+        <v>60.3445300536569</v>
       </c>
       <c r="J359" s="4" t="s">
         <v>560</v>
@@ -57948,15 +57948,15 @@
       </c>
       <c r="E361" s="16" t="n">
         <f aca="false">E359+E360</f>
-        <v>53.087488034701</v>
+        <v>53.0379705603406</v>
       </c>
       <c r="F361" s="16" t="n">
         <f aca="false">F359+F360</f>
-        <v>62.5004791871876</v>
+        <v>62.4441017590977</v>
       </c>
       <c r="G361" s="16" t="n">
         <f aca="false">G359+G360</f>
-        <v>68.7001712337191</v>
+        <v>68.6396691446905</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57976,15 +57976,15 @@
       </c>
       <c r="E362" s="11" t="n">
         <f aca="false">E359/E354</f>
-        <v>0.262352779218321</v>
+        <v>0.26231674070988</v>
       </c>
       <c r="F362" s="11" t="n">
         <f aca="false">F359/F354</f>
-        <v>0.267826227824854</v>
+        <v>0.267796052693641</v>
       </c>
       <c r="G362" s="11" t="n">
         <f aca="false">G359/G354</f>
-        <v>0.270538267683613</v>
+        <v>0.270510995530476</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58004,15 +58004,15 @@
       </c>
       <c r="E363" s="11" t="n">
         <f aca="false">E361/E356</f>
-        <v>0.241624643096787</v>
+        <v>0.241580282391873</v>
       </c>
       <c r="F363" s="11" t="n">
         <f aca="false">F361/F356</f>
-        <v>0.24847805586705</v>
+        <v>0.2484390503428</v>
       </c>
       <c r="G363" s="11" t="n">
         <f aca="false">G361/G356</f>
-        <v>0.251921771053723</v>
+        <v>0.251885703804032</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58032,15 +58032,15 @@
       </c>
       <c r="E364" s="16" t="n">
         <f aca="false">E361*nioi</f>
-        <v>37.1612416242907</v>
+        <v>37.1265793922384</v>
       </c>
       <c r="F364" s="16" t="n">
         <f aca="false">F361*nioi</f>
-        <v>43.7503354310313</v>
+        <v>43.7108712313684</v>
       </c>
       <c r="G364" s="16" t="n">
         <f aca="false">G361*nioi</f>
-        <v>48.0901198636034</v>
+        <v>48.0477684012834</v>
       </c>
       <c r="J364" s="8" t="s">
         <v>563</v>
@@ -58063,15 +58063,15 @@
       </c>
       <c r="E365" s="16" t="n">
         <f aca="false">E364*1000/shares</f>
-        <v>915.562205009374</v>
+        <v>914.70821229489</v>
       </c>
       <c r="F365" s="16" t="n">
         <f aca="false">F364*1000/shares</f>
-        <v>1077.90137859527</v>
+        <v>1076.92907713054</v>
       </c>
       <c r="G365" s="16" t="n">
         <f aca="false">G364*1000/shares</f>
-        <v>1184.8230644884</v>
+        <v>1183.77962792567</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58206,7 +58206,7 @@
       </c>
       <c r="D385" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E385" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -58267,7 +58267,7 @@
       </c>
       <c r="C388" s="19" t="n">
         <f aca="false">w_cmp_lo*(0.75*C385+0.25*D385)/(0.75*D385+0.25*E385)+(1-w_cmp_lo)*(0.75*C384+0.25*D384)/(0.75*D384+0.25*E384)</f>
-        <v>0.890473789600864</v>
+        <v>0.88972301757891</v>
       </c>
       <c r="D388" s="19" t="n">
         <f aca="false">w_cmp_lo*(0.75*D385+0.25*E385)/(0.75*D385+0.25*E385)+(1-w_cmp_lo)*(0.75*D384+0.25*E384)/(0.75*D384+0.25*E384)</f>
@@ -58275,15 +58275,15 @@
       </c>
       <c r="E388" s="19" t="n">
         <f aca="false">w_cmp_lo*(0.75*E385+0.25*F385)/(0.75*D385+0.25*E385)+(1-w_cmp_lo)*(0.75*E384+0.25*F384)/(0.75*D384+0.25*E384)</f>
-        <v>1.13988363164374</v>
+        <v>1.13779975510256</v>
       </c>
       <c r="F388" s="19" t="n">
         <f aca="false">w_cmp_lo*(0.75*F385+0.25*G385)/(0.75*D385+0.25*E385)+(1-w_cmp_lo)*(0.75*F384+0.25*G384)/(0.75*D384+0.25*E384)</f>
-        <v>1.27331764573142</v>
+        <v>1.27101418116868</v>
       </c>
       <c r="G388" s="19" t="n">
         <f aca="false">w_cmp_lo*(0.75*G385+0.25*H385)/(0.75*D385+0.25*E385)+(1-w_cmp_lo)*(0.75*G384+0.25*H384)/(0.75*D384+0.25*E384)</f>
-        <v>1.34597022224822</v>
+        <v>1.34357023230853</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58387,15 +58387,15 @@
       </c>
       <c r="E393" s="16" t="n">
         <f aca="false">$D393*E388*E389*E390</f>
-        <v>48.4895098064929</v>
+        <v>48.400863782308</v>
       </c>
       <c r="F393" s="16" t="n">
         <f aca="false">$D393*F388*F389*F390</f>
-        <v>55.7906291117218</v>
+        <v>55.6897024203167</v>
       </c>
       <c r="G393" s="16" t="n">
         <f aca="false">$D393*G388*G389*G390</f>
-        <v>60.7431315258259</v>
+        <v>60.6348208796038</v>
       </c>
     </row>
     <row r="394" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58415,15 +58415,15 @@
       </c>
       <c r="E394" s="16" t="n">
         <f aca="false">E392+E393</f>
-        <v>175.385448545338</v>
+        <v>175.296802521153</v>
       </c>
       <c r="F394" s="16" t="n">
         <f aca="false">F392+F393</f>
-        <v>204.506359582624</v>
+        <v>204.405432891219</v>
       </c>
       <c r="G394" s="16" t="n">
         <f aca="false">G392+G393</f>
-        <v>222.930757580563</v>
+        <v>222.822446934341</v>
       </c>
     </row>
     <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58471,15 +58471,15 @@
       </c>
       <c r="E396" s="16" t="n">
         <f aca="false">E394+E395</f>
-        <v>219.375448545338</v>
+        <v>219.286802521153</v>
       </c>
       <c r="F396" s="16" t="n">
         <f aca="false">F394+F395</f>
-        <v>251.135759582624</v>
+        <v>251.034832891219</v>
       </c>
       <c r="G396" s="16" t="n">
         <f aca="false">G394+G395</f>
-        <v>272.357921580563</v>
+        <v>272.249610934341</v>
       </c>
       <c r="J396" s="8" t="s">
         <v>557</v>
@@ -58502,15 +58502,15 @@
       </c>
       <c r="E397" s="11" t="n">
         <f aca="false">E394/E396</f>
-        <v>0.799476193477008</v>
+        <v>0.799395132336992</v>
       </c>
       <c r="F397" s="11" t="n">
         <f aca="false">F394/F396</f>
-        <v>0.814325924442239</v>
+        <v>0.814251275558218</v>
       </c>
       <c r="G397" s="11" t="n">
         <f aca="false">G394/G396</f>
-        <v>0.818521290979306</v>
+        <v>0.818449092248949</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58535,15 +58535,15 @@
       </c>
       <c r="E399" s="16" t="n">
         <f aca="false">$D399+v_s*(E394-$D394)</f>
-        <v>45.9999809280739</v>
+        <v>45.9733176726491</v>
       </c>
       <c r="F399" s="16" t="n">
         <f aca="false">$D399+v_s*(F394-$D394)+0*F394</f>
-        <v>54.759068505104</v>
+        <v>54.7287114284402</v>
       </c>
       <c r="G399" s="16" t="n">
         <f aca="false">$D399+v_s*(G394-$D394)+0*G394</f>
-        <v>60.3008221752199</v>
+        <v>60.2682441272815</v>
       </c>
       <c r="J399" s="4" t="s">
         <v>560</v>
@@ -58597,15 +58597,15 @@
       </c>
       <c r="E401" s="16" t="n">
         <f aca="false">E399+E400</f>
-        <v>52.9866890858304</v>
+        <v>52.9600258304056</v>
       </c>
       <c r="F401" s="16" t="n">
         <f aca="false">F399+F400</f>
-        <v>62.3809373100824</v>
+        <v>62.3505802334186</v>
       </c>
       <c r="G401" s="16" t="n">
         <f aca="false">G399+G400</f>
-        <v>68.5959612662536</v>
+        <v>68.5633832183151</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58625,15 +58625,15 @@
       </c>
       <c r="E402" s="11" t="n">
         <f aca="false">E399/E394</f>
-        <v>0.262279347058731</v>
+        <v>0.262259875887363</v>
       </c>
       <c r="F402" s="11" t="n">
         <f aca="false">F399/F394</f>
-        <v>0.267762179214678</v>
+        <v>0.267745874727145</v>
       </c>
       <c r="G402" s="11" t="n">
         <f aca="false">G399/G394</f>
-        <v>0.270491262980741</v>
+        <v>0.270476538411952</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58653,15 +58653,15 @@
       </c>
       <c r="E403" s="11" t="n">
         <f aca="false">E401/E396</f>
-        <v>0.241534271210298</v>
+        <v>0.241510319916754</v>
       </c>
       <c r="F403" s="11" t="n">
         <f aca="false">F401/F396</f>
-        <v>0.248395279962346</v>
+        <v>0.24837421769447</v>
       </c>
       <c r="G403" s="11" t="n">
         <f aca="false">G401/G396</f>
-        <v>0.251859614980807</v>
+        <v>0.251840151333956</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58681,15 +58681,15 @@
       </c>
       <c r="E404" s="16" t="n">
         <f aca="false">E401*nioi</f>
-        <v>37.0906823600813</v>
+        <v>37.0720180812839</v>
       </c>
       <c r="F404" s="16" t="n">
         <f aca="false">F401*nioi</f>
-        <v>43.6666561170577</v>
+        <v>43.6454061633931</v>
       </c>
       <c r="G404" s="16" t="n">
         <f aca="false">G401*nioi</f>
-        <v>48.0171728863775</v>
+        <v>47.9943682528206</v>
       </c>
       <c r="J404" s="8" t="s">
         <v>563</v>
@@ -58712,15 +58712,15 @@
       </c>
       <c r="E405" s="16" t="n">
         <f aca="false">E404*1000/shares</f>
-        <v>913.823797122562</v>
+        <v>913.363954891686</v>
       </c>
       <c r="F405" s="16" t="n">
         <f aca="false">F404*1000/shares</f>
-        <v>1075.83972473585</v>
+        <v>1075.31617779331</v>
       </c>
       <c r="G405" s="16" t="n">
         <f aca="false">G404*1000/shares</f>
-        <v>1183.02582918628</v>
+        <v>1182.46397872943</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58855,7 +58855,7 @@
       </c>
       <c r="D425" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E425" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -58916,7 +58916,7 @@
       </c>
       <c r="C428" s="19" t="n">
         <f aca="false">w_cmp_hi*(0.75*C425+0.25*D425)/(0.75*D425+0.25*E425)+(1-w_cmp_hi)*(0.75*C424+0.25*D424)/(0.75*D424+0.25*E424)</f>
-        <v>0.856031030936512</v>
+        <v>0.853403328859675</v>
       </c>
       <c r="D428" s="19" t="n">
         <f aca="false">w_cmp_hi*(0.75*D425+0.25*E425)/(0.75*D425+0.25*E425)+(1-w_cmp_hi)*(0.75*D424+0.25*E424)/(0.75*D424+0.25*E424)</f>
@@ -58924,15 +58924,15 @@
       </c>
       <c r="E428" s="19" t="n">
         <f aca="false">w_cmp_hi*(0.75*E425+0.25*F425)/(0.75*D425+0.25*E425)+(1-w_cmp_hi)*(0.75*E424+0.25*F424)/(0.75*D424+0.25*E424)</f>
-        <v>1.15721066383541</v>
+        <v>1.14991709594131</v>
       </c>
       <c r="F428" s="19" t="n">
         <f aca="false">w_cmp_hi*(0.75*F425+0.25*G425)/(0.75*D425+0.25*E425)+(1-w_cmp_hi)*(0.75*F424+0.25*G424)/(0.75*D424+0.25*E424)</f>
-        <v>1.28877077867208</v>
+        <v>1.28070865270252</v>
       </c>
       <c r="G428" s="19" t="n">
         <f aca="false">w_cmp_hi*(0.75*G425+0.25*H425)/(0.75*D425+0.25*E425)+(1-w_cmp_hi)*(0.75*G424+0.25*H424)/(0.75*D424+0.25*E424)</f>
-        <v>1.35671120934044</v>
+        <v>1.34831124455151</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59036,15 +59036,15 @@
       </c>
       <c r="E433" s="16" t="n">
         <f aca="false">$D433*E428*E429*E430</f>
-        <v>49.2265844288945</v>
+        <v>48.9163233442474</v>
       </c>
       <c r="F433" s="16" t="n">
         <f aca="false">$D433*F428*F429*F430</f>
-        <v>56.4677107585497</v>
+        <v>56.1144673386319</v>
       </c>
       <c r="G433" s="16" t="n">
         <f aca="false">$D433*G428*G429*G430</f>
-        <v>61.2278682465018</v>
+        <v>60.8487809847241</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59064,15 +59064,15 @@
       </c>
       <c r="E434" s="16" t="n">
         <f aca="false">E432+E433</f>
-        <v>176.122523167739</v>
+        <v>175.812262083092</v>
       </c>
       <c r="F434" s="16" t="n">
         <f aca="false">F432+F433</f>
-        <v>205.183441229452</v>
+        <v>204.830197809535</v>
       </c>
       <c r="G434" s="16" t="n">
         <f aca="false">G432+G433</f>
-        <v>223.415494301239</v>
+        <v>223.036407039462</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59120,15 +59120,15 @@
       </c>
       <c r="E436" s="16" t="n">
         <f aca="false">E434+E435</f>
-        <v>220.112523167739</v>
+        <v>219.802262083092</v>
       </c>
       <c r="F436" s="16" t="n">
         <f aca="false">F434+F435</f>
-        <v>251.812841229452</v>
+        <v>251.459597809535</v>
       </c>
       <c r="G436" s="16" t="n">
         <f aca="false">G434+G435</f>
-        <v>272.842658301239</v>
+        <v>272.463571039462</v>
       </c>
       <c r="J436" s="8" t="s">
         <v>557</v>
@@ -59151,15 +59151,15 @@
       </c>
       <c r="E437" s="11" t="n">
         <f aca="false">E434/E436</f>
-        <v>0.800147672804255</v>
+        <v>0.799865571977733</v>
       </c>
       <c r="F437" s="11" t="n">
         <f aca="false">F434/F436</f>
-        <v>0.814825170264009</v>
+        <v>0.814565041834995</v>
       </c>
       <c r="G437" s="11" t="n">
         <f aca="false">G434/G436</f>
-        <v>0.818843709016247</v>
+        <v>0.818591660487187</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59184,15 +59184,15 @@
       </c>
       <c r="E439" s="16" t="n">
         <f aca="false">$D439+v_s*(E434-$D434)</f>
-        <v>46.2216807629505</v>
+        <v>46.1283593689636</v>
       </c>
       <c r="F439" s="16" t="n">
         <f aca="false">$D439+v_s*(F434-$D434)+0*F434</f>
-        <v>54.9627234468663</v>
+        <v>54.8564736785432</v>
       </c>
       <c r="G439" s="16" t="n">
         <f aca="false">$D439+v_s*(G434-$D434)+0*G434</f>
-        <v>60.4466229498855</v>
+        <v>60.3325997821008</v>
       </c>
       <c r="J439" s="4" t="s">
         <v>560</v>
@@ -59246,15 +59246,15 @@
       </c>
       <c r="E441" s="16" t="n">
         <f aca="false">E439+E440</f>
-        <v>53.208388920707</v>
+        <v>53.1150675267201</v>
       </c>
       <c r="F441" s="16" t="n">
         <f aca="false">F439+F440</f>
-        <v>62.5845922518448</v>
+        <v>62.4783424835216</v>
       </c>
       <c r="G441" s="16" t="n">
         <f aca="false">G439+G440</f>
-        <v>68.7417620409191</v>
+        <v>68.6277388731344</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59274,15 +59274,15 @@
       </c>
       <c r="E442" s="11" t="n">
         <f aca="false">E439/E434</f>
-        <v>0.262440487063253</v>
+        <v>0.262372822136618</v>
       </c>
       <c r="F442" s="11" t="n">
         <f aca="false">F439/F434</f>
-        <v>0.267871145534608</v>
+        <v>0.267814386087508</v>
       </c>
       <c r="G442" s="11" t="n">
         <f aca="false">G439/G434</f>
-        <v>0.270556986832718</v>
+        <v>0.270505611989285</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59302,15 +59302,15 @@
       </c>
       <c r="E443" s="11" t="n">
         <f aca="false">E441/E436</f>
-        <v>0.241732674520109</v>
+        <v>0.241649321637286</v>
       </c>
       <c r="F443" s="11" t="n">
         <f aca="false">F441/F436</f>
-        <v>0.248536142741099</v>
+        <v>0.248462747207785</v>
       </c>
       <c r="G443" s="11" t="n">
         <f aca="false">G441/G436</f>
-        <v>0.251946533833514</v>
+        <v>0.25187858549793</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59330,15 +59330,15 @@
       </c>
       <c r="E444" s="16" t="n">
         <f aca="false">E441*nioi</f>
-        <v>37.2458722444949</v>
+        <v>37.1805472687041</v>
       </c>
       <c r="F444" s="16" t="n">
         <f aca="false">F441*nioi</f>
-        <v>43.8092145762913</v>
+        <v>43.7348397384652</v>
       </c>
       <c r="G444" s="16" t="n">
         <f aca="false">G441*nioi</f>
-        <v>48.1192334286434</v>
+        <v>48.0394172111941</v>
       </c>
       <c r="J444" s="8" t="s">
         <v>563</v>
@@ -59361,15 +59361,15 @@
       </c>
       <c r="E445" s="16" t="n">
         <f aca="false">E444*1000/shares</f>
-        <v>917.647296730175</v>
+        <v>916.037848922109</v>
       </c>
       <c r="F445" s="16" t="n">
         <f aca="false">F444*1000/shares</f>
-        <v>1079.35201688686</v>
+        <v>1077.51960258796</v>
       </c>
       <c r="G445" s="16" t="n">
         <f aca="false">G444*1000/shares</f>
-        <v>1185.54035160364</v>
+        <v>1183.57387500466</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59504,7 +59504,7 @@
       </c>
       <c r="D465" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E465" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -59565,7 +59565,7 @@
       </c>
       <c r="C468" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C465+0.25*D465)/(0.75*D465+0.25*E465)+(1-w_cmp)*(0.75*C464+0.25*D464)/(0.75*D464+0.25*E464)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D468" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D465+0.25*E465)/(0.75*D465+0.25*E465)+(1-w_cmp)*(0.75*D464+0.25*E464)/(0.75*D464+0.25*E464)</f>
@@ -59573,15 +59573,15 @@
       </c>
       <c r="E468" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E465+0.25*F465)/(0.75*D465+0.25*E465)+(1-w_cmp)*(0.75*E464+0.25*F464)/(0.75*D464+0.25*E464)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F468" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F465+0.25*G465)/(0.75*D465+0.25*E465)+(1-w_cmp)*(0.75*F464+0.25*G464)/(0.75*D464+0.25*E464)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G468" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G465+0.25*H465)/(0.75*D465+0.25*E465)+(1-w_cmp)*(0.75*G464+0.25*H464)/(0.75*D464+0.25*E464)</f>
-        <v>1.31650995165798</v>
+        <v>1.31182997127558</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59685,15 +59685,15 @@
       </c>
       <c r="E473" s="16" t="n">
         <f aca="false">$D473*E468*E469*E470</f>
-        <v>48.7843396554535</v>
+        <v>48.6070476070838</v>
       </c>
       <c r="F473" s="16" t="n">
         <f aca="false">$D473*F468*F469*F470</f>
-        <v>56.061461770453</v>
+        <v>55.8596083876428</v>
       </c>
       <c r="G473" s="16" t="n">
         <f aca="false">$D473*G468*G469*G470</f>
-        <v>59.4136005587439</v>
+        <v>59.2023947986106</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59713,15 +59713,15 @@
       </c>
       <c r="E474" s="16" t="n">
         <f aca="false">E472+E473</f>
-        <v>175.680278394298</v>
+        <v>175.502986345929</v>
       </c>
       <c r="F474" s="16" t="n">
         <f aca="false">F472+F473</f>
-        <v>204.777192241356</v>
+        <v>204.575338858545</v>
       </c>
       <c r="G474" s="16" t="n">
         <f aca="false">G472+G473</f>
-        <v>217.546535962113</v>
+        <v>217.33533020198</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59769,15 +59769,15 @@
       </c>
       <c r="E476" s="16" t="n">
         <f aca="false">E474+E475</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="F476" s="16" t="n">
         <f aca="false">F474+F475</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G476" s="16" t="n">
         <f aca="false">G474+G475</f>
-        <v>266.973699962113</v>
+        <v>266.76249420198</v>
       </c>
       <c r="J476" s="8" t="s">
         <v>557</v>
@@ -59800,15 +59800,15 @@
       </c>
       <c r="E477" s="11" t="n">
         <f aca="false">E474/E476</f>
-        <v>0.799745325942366</v>
+        <v>0.799583573341746</v>
       </c>
       <c r="F477" s="11" t="n">
         <f aca="false">F474/F476</f>
-        <v>0.814525945464331</v>
+        <v>0.814376909401151</v>
       </c>
       <c r="G477" s="11" t="n">
         <f aca="false">G474/G476</f>
-        <v>0.814861299045508</v>
+        <v>0.814714717869686</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59833,15 +59833,15 @@
       </c>
       <c r="E479" s="16" t="n">
         <f aca="false">$D479+v_s*(E474-$D474)</f>
-        <v>46.0886608620245</v>
+        <v>46.0353343511749</v>
       </c>
       <c r="F479" s="16" t="n">
         <f aca="false">$D479+v_s*(F474-$D474)+0*F474</f>
-        <v>54.8405304818089</v>
+        <v>54.7798163284814</v>
       </c>
       <c r="G479" s="16" t="n">
         <f aca="false">$D479+v_s*(G474-$D474)+0*G474</f>
-        <v>58.6813375159055</v>
+        <v>58.6178103224255</v>
       </c>
       <c r="J479" s="4" t="s">
         <v>560</v>
@@ -59895,15 +59895,15 @@
       </c>
       <c r="E481" s="16" t="n">
         <f aca="false">E479+E480</f>
-        <v>53.0753690197811</v>
+        <v>53.0220425089314</v>
       </c>
       <c r="F481" s="16" t="n">
         <f aca="false">F479+F480</f>
-        <v>62.4623992867873</v>
+        <v>62.4016851334598</v>
       </c>
       <c r="G481" s="16" t="n">
         <f aca="false">G479+G480</f>
-        <v>66.9764766069391</v>
+        <v>66.9129494134591</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59923,15 +59923,15 @@
       </c>
       <c r="E482" s="11" t="n">
         <f aca="false">E479/E474</f>
-        <v>0.262343965317397</v>
+        <v>0.262305134001743</v>
       </c>
       <c r="F482" s="11" t="n">
         <f aca="false">F479/F474</f>
-        <v>0.267805852212157</v>
+        <v>0.267773313411736</v>
       </c>
       <c r="G482" s="11" t="n">
         <f aca="false">G479/G474</f>
-        <v>0.269741539465953</v>
+        <v>0.269711373056324</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59951,15 +59951,15 @@
       </c>
       <c r="E483" s="11" t="n">
         <f aca="false">E481/E476</f>
-        <v>0.24161379230609</v>
+        <v>0.241565998948899</v>
       </c>
       <c r="F483" s="11" t="n">
         <f aca="false">F481/F476</f>
-        <v>0.248451716122154</v>
+        <v>0.248409665426728</v>
       </c>
       <c r="G483" s="11" t="n">
         <f aca="false">G481/G476</f>
-        <v>0.25087293848212</v>
+        <v>0.250833422493028</v>
       </c>
     </row>
     <row r="484" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59979,15 +59979,15 @@
       </c>
       <c r="E484" s="16" t="n">
         <f aca="false">E481*nioi</f>
-        <v>37.1527583138467</v>
+        <v>37.115429756252</v>
       </c>
       <c r="F484" s="16" t="n">
         <f aca="false">F481*nioi</f>
-        <v>43.7236795007511</v>
+        <v>43.6811795934219</v>
       </c>
       <c r="G484" s="16" t="n">
         <f aca="false">G481*nioi</f>
-        <v>46.8835336248574</v>
+        <v>46.8390645894214</v>
       </c>
       <c r="J484" s="8" t="s">
         <v>563</v>
@@ -60010,15 +60010,15 @@
       </c>
       <c r="E485" s="16" t="n">
         <f aca="false">E484*1000/shares</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="F485" s="16" t="n">
         <f aca="false">F484*1000/shares</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="G485" s="16" t="n">
         <f aca="false">G484*1000/shares</f>
-        <v>1155.09572737601</v>
+        <v>1154.00011898514</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60153,7 +60153,7 @@
       </c>
       <c r="D505" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E505" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -60214,7 +60214,7 @@
       </c>
       <c r="C508" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C505+0.25*D505)/(0.75*D505+0.25*E505)+(1-w_cmp)*(0.75*C504+0.25*D504)/(0.75*D504+0.25*E504)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D508" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D505+0.25*E505)/(0.75*D505+0.25*E505)+(1-w_cmp)*(0.75*D504+0.25*E504)/(0.75*D504+0.25*E504)</f>
@@ -60222,15 +60222,15 @@
       </c>
       <c r="E508" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E505+0.25*F505)/(0.75*D505+0.25*E505)+(1-w_cmp)*(0.75*E504+0.25*F504)/(0.75*D504+0.25*E504)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F508" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F505+0.25*G505)/(0.75*D505+0.25*E505)+(1-w_cmp)*(0.75*F504+0.25*G504)/(0.75*D504+0.25*E504)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G508" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G505+0.25*H505)/(0.75*D505+0.25*E505)+(1-w_cmp)*(0.75*G504+0.25*H504)/(0.75*D504+0.25*E504)</f>
-        <v>1.38402328251224</v>
+        <v>1.37910330313586</v>
       </c>
     </row>
     <row r="509" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60334,15 +60334,15 @@
       </c>
       <c r="E513" s="16" t="n">
         <f aca="false">$D513*E508*E509*E510</f>
-        <v>48.7843396554535</v>
+        <v>48.6070476070838</v>
       </c>
       <c r="F513" s="16" t="n">
         <f aca="false">$D513*F508*F509*F510</f>
-        <v>56.061461770453</v>
+        <v>55.8596083876428</v>
       </c>
       <c r="G513" s="16" t="n">
         <f aca="false">$D513*G508*G509*G510</f>
-        <v>62.4604518694487</v>
+        <v>62.2384150446932</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60362,15 +60362,15 @@
       </c>
       <c r="E514" s="16" t="n">
         <f aca="false">E512+E513</f>
-        <v>175.680278394298</v>
+        <v>175.502986345929</v>
       </c>
       <c r="F514" s="16" t="n">
         <f aca="false">F512+F513</f>
-        <v>204.777192241356</v>
+        <v>204.575338858545</v>
       </c>
       <c r="G514" s="16" t="n">
         <f aca="false">G512+G513</f>
-        <v>228.702768575554</v>
+        <v>228.480731750799</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60418,15 +60418,15 @@
       </c>
       <c r="E516" s="16" t="n">
         <f aca="false">E514+E515</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="F516" s="16" t="n">
         <f aca="false">F514+F515</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G516" s="16" t="n">
         <f aca="false">G514+G515</f>
-        <v>278.129932575554</v>
+        <v>277.907895750799</v>
       </c>
       <c r="J516" s="8" t="s">
         <v>557</v>
@@ -60449,15 +60449,15 @@
       </c>
       <c r="E517" s="11" t="n">
         <f aca="false">E514/E516</f>
-        <v>0.799745325942366</v>
+        <v>0.799583573341746</v>
       </c>
       <c r="F517" s="11" t="n">
         <f aca="false">F514/F516</f>
-        <v>0.814525945464331</v>
+        <v>0.814376909401151</v>
       </c>
       <c r="G517" s="11" t="n">
         <f aca="false">G514/G516</f>
-        <v>0.822287505906711</v>
+        <v>0.822145521031466</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60482,15 +60482,15 @@
       </c>
       <c r="E519" s="16" t="n">
         <f aca="false">$D519+v_s*(E514-$D514)</f>
-        <v>46.0886608620245</v>
+        <v>46.0353343511749</v>
       </c>
       <c r="F519" s="16" t="n">
         <f aca="false">$D519+v_s*(F514-$D514)+0*F514</f>
-        <v>54.8405304818089</v>
+        <v>54.7798163284814</v>
       </c>
       <c r="G519" s="16" t="n">
         <f aca="false">$D519+v_s*(G514-$D514)+0*G514</f>
-        <v>62.0369474542668</v>
+        <v>61.9701624559929</v>
       </c>
       <c r="J519" s="4" t="s">
         <v>560</v>
@@ -60544,15 +60544,15 @@
       </c>
       <c r="E521" s="16" t="n">
         <f aca="false">E519+E520</f>
-        <v>53.0753690197811</v>
+        <v>53.0220425089314</v>
       </c>
       <c r="F521" s="16" t="n">
         <f aca="false">F519+F520</f>
-        <v>62.4623992867873</v>
+        <v>62.4016851334598</v>
       </c>
       <c r="G521" s="16" t="n">
         <f aca="false">G519+G520</f>
-        <v>70.3320865453004</v>
+        <v>70.2653015470266</v>
       </c>
     </row>
     <row r="522" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60572,15 +60572,15 @@
       </c>
       <c r="E522" s="11" t="n">
         <f aca="false">E519/E514</f>
-        <v>0.262343965317397</v>
+        <v>0.262305134001743</v>
       </c>
       <c r="F522" s="11" t="n">
         <f aca="false">F519/F514</f>
-        <v>0.267805852212157</v>
+        <v>0.267773313411736</v>
       </c>
       <c r="G522" s="11" t="n">
         <f aca="false">G519/G514</f>
-        <v>0.271255778146701</v>
+        <v>0.271227083269249</v>
       </c>
     </row>
     <row r="523" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60600,15 +60600,15 @@
       </c>
       <c r="E523" s="11" t="n">
         <f aca="false">E521/E516</f>
-        <v>0.24161379230609</v>
+        <v>0.241565998948899</v>
       </c>
       <c r="F523" s="11" t="n">
         <f aca="false">F521/F516</f>
-        <v>0.248451716122154</v>
+        <v>0.248409665426728</v>
       </c>
       <c r="G523" s="11" t="n">
         <f aca="false">G521/G516</f>
-        <v>0.252874927534794</v>
+        <v>0.252836650636345</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60628,15 +60628,15 @@
       </c>
       <c r="E524" s="16" t="n">
         <f aca="false">E521*nioi</f>
-        <v>37.1527583138467</v>
+        <v>37.115429756252</v>
       </c>
       <c r="F524" s="16" t="n">
         <f aca="false">F521*nioi</f>
-        <v>43.7236795007511</v>
+        <v>43.6811795934219</v>
       </c>
       <c r="G524" s="16" t="n">
         <f aca="false">G521*nioi</f>
-        <v>49.2324605817103</v>
+        <v>49.1857110829186</v>
       </c>
       <c r="J524" s="8" t="s">
         <v>563</v>
@@ -60659,15 +60659,15 @@
       </c>
       <c r="E525" s="16" t="n">
         <f aca="false">E524*1000/shares</f>
-        <v>915.353196965608</v>
+        <v>914.433512503855</v>
       </c>
       <c r="F525" s="16" t="n">
         <f aca="false">F524*1000/shares</f>
-        <v>1077.24464159626</v>
+        <v>1076.19754771117</v>
       </c>
       <c r="G525" s="16" t="n">
         <f aca="false">G524*1000/shares</f>
-        <v>1212.96754893044</v>
+        <v>1211.81575549389</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60802,7 +60802,7 @@
       </c>
       <c r="D545" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E545" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -60863,7 +60863,7 @@
       </c>
       <c r="C548" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C545+0.25*D545)/(0.75*D545+0.25*E545)+(1-w_cmp)*(0.75*C544+0.25*D544)/(0.75*D544+0.25*E544)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D548" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D545+0.25*E545)/(0.75*D545+0.25*E545)+(1-w_cmp)*(0.75*D544+0.25*E544)/(0.75*D544+0.25*E544)</f>
@@ -60871,15 +60871,15 @@
       </c>
       <c r="E548" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E545+0.25*F545)/(0.75*D545+0.25*E545)+(1-w_cmp)*(0.75*E544+0.25*F544)/(0.75*D544+0.25*E544)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F548" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F545+0.25*G545)/(0.75*D545+0.25*E545)+(1-w_cmp)*(0.75*F544+0.25*G544)/(0.75*D544+0.25*E544)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G548" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G545+0.25*H545)/(0.75*D545+0.25*E545)+(1-w_cmp)*(0.75*G544+0.25*H544)/(0.75*D544+0.25*E544)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="549" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60983,15 +60983,15 @@
       </c>
       <c r="E553" s="16" t="n">
         <f aca="false">$D553*E548*E549*E550</f>
-        <v>48.7843396554535</v>
+        <v>48.6070476070838</v>
       </c>
       <c r="F553" s="16" t="n">
         <f aca="false">$D553*F548*F549*F550</f>
-        <v>56.061461770453</v>
+        <v>55.8596083876428</v>
       </c>
       <c r="G553" s="16" t="n">
         <f aca="false">$D553*G548*G549*G550</f>
-        <v>60.9370262140963</v>
+        <v>60.7204049216519</v>
       </c>
     </row>
     <row r="554" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61011,15 +61011,15 @@
       </c>
       <c r="E554" s="16" t="n">
         <f aca="false">E552+E553</f>
-        <v>175.680278394298</v>
+        <v>175.502986345929</v>
       </c>
       <c r="F554" s="16" t="n">
         <f aca="false">F552+F553</f>
-        <v>204.777192241356</v>
+        <v>204.575338858545</v>
       </c>
       <c r="G554" s="16" t="n">
         <f aca="false">G552+G553</f>
-        <v>223.124652268834</v>
+        <v>222.908030976389</v>
       </c>
     </row>
     <row r="555" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61067,15 +61067,15 @@
       </c>
       <c r="E556" s="16" t="n">
         <f aca="false">E554+E555</f>
-        <v>218.840278394298</v>
+        <v>218.662986345929</v>
       </c>
       <c r="F556" s="16" t="n">
         <f aca="false">F554+F555</f>
-        <v>249.663592241356</v>
+        <v>249.461738858545</v>
       </c>
       <c r="G556" s="16" t="n">
         <f aca="false">G554+G555</f>
-        <v>269.806508268834</v>
+        <v>269.589886976389</v>
       </c>
       <c r="J556" s="8" t="s">
         <v>557</v>
@@ -61098,15 +61098,15 @@
       </c>
       <c r="E557" s="11" t="n">
         <f aca="false">E554/E556</f>
-        <v>0.802778536397967</v>
+        <v>0.802618629145949</v>
       </c>
       <c r="F557" s="11" t="n">
         <f aca="false">F554/F556</f>
-        <v>0.820212472323128</v>
+        <v>0.820066996224009</v>
       </c>
       <c r="G557" s="11" t="n">
         <f aca="false">G554/G556</f>
-        <v>0.826980244844626</v>
+        <v>0.826841219737266</v>
       </c>
     </row>
     <row r="558" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61131,15 +61131,15 @@
       </c>
       <c r="E559" s="16" t="n">
         <f aca="false">$D559+v_s*(E554-$D554)</f>
-        <v>46.0886608620245</v>
+        <v>46.0353343511749</v>
       </c>
       <c r="F559" s="16" t="n">
         <f aca="false">$D559+v_s*(F554-$D554)+0*F554</f>
-        <v>54.8405304818089</v>
+        <v>54.7798163284814</v>
       </c>
       <c r="G559" s="16" t="n">
         <f aca="false">$D559+v_s*(G554-$D554)+0*G554</f>
-        <v>60.3591424850862</v>
+        <v>60.2939863892092</v>
       </c>
       <c r="J559" s="4" t="s">
         <v>560</v>
@@ -61193,15 +61193,15 @@
       </c>
       <c r="E561" s="16" t="n">
         <f aca="false">E559+E560</f>
-        <v>52.8756329671956</v>
+        <v>52.8223064563459</v>
       </c>
       <c r="F561" s="16" t="n">
         <f aca="false">F559+F560</f>
-        <v>62.0429535763578</v>
+        <v>61.9822394230303</v>
       </c>
       <c r="G561" s="16" t="n">
         <f aca="false">G559+G560</f>
-        <v>67.993634608588</v>
+        <v>67.928478512711</v>
       </c>
     </row>
     <row r="562" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61221,15 +61221,15 @@
       </c>
       <c r="E562" s="11" t="n">
         <f aca="false">E559/E554</f>
-        <v>0.262343965317397</v>
+        <v>0.262305134001743</v>
       </c>
       <c r="F562" s="11" t="n">
         <f aca="false">F559/F554</f>
-        <v>0.267805852212157</v>
+        <v>0.267773313411736</v>
       </c>
       <c r="G562" s="11" t="n">
         <f aca="false">G559/G554</f>
-        <v>0.270517586789836</v>
+        <v>0.270488174540448</v>
       </c>
     </row>
     <row r="563" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61249,15 +61249,15 @@
       </c>
       <c r="E563" s="11" t="n">
         <f aca="false">E561/E556</f>
-        <v>0.241617463453991</v>
+        <v>0.241569491659554</v>
       </c>
       <c r="F563" s="11" t="n">
         <f aca="false">F561/F556</f>
-        <v>0.248506211976552</v>
+        <v>0.248463911566722</v>
       </c>
       <c r="G563" s="11" t="n">
         <f aca="false">G561/G556</f>
-        <v>0.252008874970649</v>
+        <v>0.251969683561091</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61277,15 +61277,15 @@
       </c>
       <c r="E564" s="16" t="n">
         <f aca="false">E561*nioi</f>
-        <v>37.0129430770369</v>
+        <v>36.9756145194421</v>
       </c>
       <c r="F564" s="16" t="n">
         <f aca="false">F561*nioi</f>
-        <v>43.4300675034505</v>
+        <v>43.3875675961212</v>
       </c>
       <c r="G564" s="16" t="n">
         <f aca="false">G561*nioi</f>
-        <v>47.5955442260116</v>
+        <v>47.5499349588977</v>
       </c>
       <c r="J564" s="8" t="s">
         <v>563</v>
@@ -61308,15 +61308,15 @@
       </c>
       <c r="E565" s="16" t="n">
         <f aca="false">E564*1000/shares</f>
-        <v>911.908491113157</v>
+        <v>910.988806651404</v>
       </c>
       <c r="F565" s="16" t="n">
         <f aca="false">F564*1000/shares</f>
-        <v>1070.01075930611</v>
+        <v>1068.96366542102</v>
       </c>
       <c r="G565" s="16" t="n">
         <f aca="false">G564*1000/shares</f>
-        <v>1172.63792907566</v>
+        <v>1171.51422816195</v>
       </c>
     </row>
     <row r="566" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61451,7 +61451,7 @@
       </c>
       <c r="D585" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E585" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -61512,7 +61512,7 @@
       </c>
       <c r="C588" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C585+0.25*D585)/(0.75*D585+0.25*E585)+(1-w_cmp)*(0.75*C584+0.25*D584)/(0.75*D584+0.25*E584)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D588" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D585+0.25*E585)/(0.75*D585+0.25*E585)+(1-w_cmp)*(0.75*D584+0.25*E584)/(0.75*D584+0.25*E584)</f>
@@ -61520,15 +61520,15 @@
       </c>
       <c r="E588" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E585+0.25*F585)/(0.75*D585+0.25*E585)+(1-w_cmp)*(0.75*E584+0.25*F584)/(0.75*D584+0.25*E584)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F588" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F585+0.25*G585)/(0.75*D585+0.25*E585)+(1-w_cmp)*(0.75*F584+0.25*G584)/(0.75*D584+0.25*E584)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G588" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G585+0.25*H585)/(0.75*D585+0.25*E585)+(1-w_cmp)*(0.75*G584+0.25*H584)/(0.75*D584+0.25*E584)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61632,15 +61632,15 @@
       </c>
       <c r="E593" s="16" t="n">
         <f aca="false">$D593*E588*E589*E590</f>
-        <v>48.7843396554535</v>
+        <v>48.6070476070838</v>
       </c>
       <c r="F593" s="16" t="n">
         <f aca="false">$D593*F588*F589*F590</f>
-        <v>56.061461770453</v>
+        <v>55.8596083876428</v>
       </c>
       <c r="G593" s="16" t="n">
         <f aca="false">$D593*G588*G589*G590</f>
-        <v>60.9370262140963</v>
+        <v>60.7204049216519</v>
       </c>
     </row>
     <row r="594" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61660,15 +61660,15 @@
       </c>
       <c r="E594" s="16" t="n">
         <f aca="false">E592+E593</f>
-        <v>175.680278394298</v>
+        <v>175.502986345929</v>
       </c>
       <c r="F594" s="16" t="n">
         <f aca="false">F592+F593</f>
-        <v>204.777192241356</v>
+        <v>204.575338858545</v>
       </c>
       <c r="G594" s="16" t="n">
         <f aca="false">G592+G593</f>
-        <v>223.124652268834</v>
+        <v>222.908030976389</v>
       </c>
     </row>
     <row r="595" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61716,15 +61716,15 @@
       </c>
       <c r="E596" s="16" t="n">
         <f aca="false">E594+E595</f>
-        <v>220.500278394298</v>
+        <v>220.322986345929</v>
       </c>
       <c r="F596" s="16" t="n">
         <f aca="false">F594+F595</f>
-        <v>253.182792241356</v>
+        <v>252.980938858545</v>
       </c>
       <c r="G596" s="16" t="n">
         <f aca="false">G594+G595</f>
-        <v>275.402700268834</v>
+        <v>275.186078976389</v>
       </c>
       <c r="J596" s="8" t="s">
         <v>557</v>
@@ -61747,15 +61747,15 @@
       </c>
       <c r="E597" s="11" t="n">
         <f aca="false">E594/E596</f>
-        <v>0.796734950511705</v>
+        <v>0.796571384841216</v>
       </c>
       <c r="F597" s="11" t="n">
         <f aca="false">F594/F596</f>
-        <v>0.808811651173135</v>
+        <v>0.808659102071457</v>
       </c>
       <c r="G597" s="11" t="n">
         <f aca="false">G594/G596</f>
-        <v>0.810175978852172</v>
+        <v>0.810026552962058</v>
       </c>
     </row>
     <row r="598" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61780,15 +61780,15 @@
       </c>
       <c r="E599" s="16" t="n">
         <f aca="false">$D599+v_s*(E594-$D594)</f>
-        <v>46.0886608620245</v>
+        <v>46.0353343511749</v>
       </c>
       <c r="F599" s="16" t="n">
         <f aca="false">$D599+v_s*(F594-$D594)+0*F594</f>
-        <v>54.8405304818089</v>
+        <v>54.7798163284814</v>
       </c>
       <c r="G599" s="16" t="n">
         <f aca="false">$D599+v_s*(G594-$D594)+0*G594</f>
-        <v>60.3591424850862</v>
+        <v>60.2939863892092</v>
       </c>
       <c r="J599" s="4" t="s">
         <v>560</v>
@@ -61842,15 +61842,15 @@
       </c>
       <c r="E601" s="16" t="n">
         <f aca="false">E599+E600</f>
-        <v>53.2751050723666</v>
+        <v>53.2217785615169</v>
       </c>
       <c r="F601" s="16" t="n">
         <f aca="false">F599+F600</f>
-        <v>62.8898344393203</v>
+        <v>62.8291202859928</v>
       </c>
       <c r="G601" s="16" t="n">
         <f aca="false">G599+G600</f>
-        <v>69.3403349695405</v>
+        <v>69.2751788736635</v>
       </c>
     </row>
     <row r="602" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61870,15 +61870,15 @@
       </c>
       <c r="E602" s="11" t="n">
         <f aca="false">E599/E594</f>
-        <v>0.262343965317397</v>
+        <v>0.262305134001743</v>
       </c>
       <c r="F602" s="11" t="n">
         <f aca="false">F599/F594</f>
-        <v>0.267805852212157</v>
+        <v>0.267773313411736</v>
       </c>
       <c r="G602" s="11" t="n">
         <f aca="false">G599/G594</f>
-        <v>0.270517586789836</v>
+        <v>0.270488174540448</v>
       </c>
     </row>
     <row r="603" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61898,15 +61898,15 @@
       </c>
       <c r="E603" s="11" t="n">
         <f aca="false">E601/E596</f>
-        <v>0.241610148795822</v>
+        <v>0.241562532553701</v>
       </c>
       <c r="F603" s="11" t="n">
         <f aca="false">F601/F596</f>
-        <v>0.248396954163332</v>
+        <v>0.248355155014757</v>
       </c>
       <c r="G603" s="11" t="n">
         <f aca="false">G601/G596</f>
-        <v>0.25177797785517</v>
+        <v>0.251739401685386</v>
       </c>
     </row>
     <row r="604" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -61926,15 +61926,15 @@
       </c>
       <c r="E604" s="16" t="n">
         <f aca="false">E601*nioi</f>
-        <v>37.2925735506566</v>
+        <v>37.2552449930618</v>
       </c>
       <c r="F604" s="16" t="n">
         <f aca="false">F601*nioi</f>
-        <v>44.0228841075242</v>
+        <v>43.980384200195</v>
       </c>
       <c r="G604" s="16" t="n">
         <f aca="false">G601*nioi</f>
-        <v>48.5382344786784</v>
+        <v>48.4926252115645</v>
       </c>
       <c r="J604" s="8" t="s">
         <v>563</v>
@@ -61957,15 +61957,15 @@
       </c>
       <c r="E605" s="16" t="n">
         <f aca="false">E604*1000/shares</f>
-        <v>918.797902818058</v>
+        <v>917.878218356306</v>
       </c>
       <c r="F605" s="16" t="n">
         <f aca="false">F604*1000/shares</f>
-        <v>1084.6163121205</v>
+        <v>1083.56921823541</v>
       </c>
       <c r="G605" s="16" t="n">
         <f aca="false">G604*1000/shares</f>
-        <v>1195.86351381522</v>
+        <v>1194.73981290152</v>
       </c>
     </row>
     <row r="606" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62100,7 +62100,7 @@
       </c>
       <c r="D625" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E625" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -62161,7 +62161,7 @@
       </c>
       <c r="C628" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C625+0.25*D625)/(0.75*D625+0.25*E625)+(1-w_cmp)*(0.75*C624+0.25*D624)/(0.75*D624+0.25*E624)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D628" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D625+0.25*E625)/(0.75*D625+0.25*E625)+(1-w_cmp)*(0.75*D624+0.25*E624)/(0.75*D624+0.25*E624)</f>
@@ -62169,15 +62169,15 @@
       </c>
       <c r="E628" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E625+0.25*F625)/(0.75*D625+0.25*E625)+(1-w_cmp)*(0.75*E624+0.25*F624)/(0.75*D624+0.25*E624)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F628" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F625+0.25*G625)/(0.75*D625+0.25*E625)+(1-w_cmp)*(0.75*F624+0.25*G624)/(0.75*D624+0.25*E624)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G628" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G625+0.25*H625)/(0.75*D625+0.25*E625)+(1-w_cmp)*(0.75*G624+0.25*H624)/(0.75*D624+0.25*E624)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="629" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62281,15 +62281,15 @@
       </c>
       <c r="E633" s="16" t="n">
         <f aca="false">$D633*E628*E629*E630</f>
-        <v>48.7843396554535</v>
+        <v>48.6070476070838</v>
       </c>
       <c r="F633" s="16" t="n">
         <f aca="false">$D633*F628*F629*F630</f>
-        <v>56.061461770453</v>
+        <v>55.8596083876428</v>
       </c>
       <c r="G633" s="16" t="n">
         <f aca="false">$D633*G628*G629*G630</f>
-        <v>60.9370262140963</v>
+        <v>60.7204049216519</v>
       </c>
     </row>
     <row r="634" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62309,15 +62309,15 @@
       </c>
       <c r="E634" s="16" t="n">
         <f aca="false">E632+E633</f>
-        <v>175.680278394298</v>
+        <v>175.502986345929</v>
       </c>
       <c r="F634" s="16" t="n">
         <f aca="false">F632+F633</f>
-        <v>204.777192241356</v>
+        <v>204.575338858545</v>
       </c>
       <c r="G634" s="16" t="n">
         <f aca="false">G632+G633</f>
-        <v>223.124652268834</v>
+        <v>222.908030976389</v>
       </c>
     </row>
     <row r="635" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62365,15 +62365,15 @@
       </c>
       <c r="E636" s="16" t="n">
         <f aca="false">E634+E635</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="F636" s="16" t="n">
         <f aca="false">F634+F635</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G636" s="16" t="n">
         <f aca="false">G634+G635</f>
-        <v>272.551816268834</v>
+        <v>272.335194976389</v>
       </c>
       <c r="J636" s="8" t="s">
         <v>557</v>
@@ -62396,15 +62396,15 @@
       </c>
       <c r="E637" s="11" t="n">
         <f aca="false">E634/E636</f>
-        <v>0.799745325942366</v>
+        <v>0.799583573341746</v>
       </c>
       <c r="F637" s="11" t="n">
         <f aca="false">F634/F636</f>
-        <v>0.814525945464331</v>
+        <v>0.814376909401151</v>
       </c>
       <c r="G637" s="11" t="n">
         <f aca="false">G634/G636</f>
-        <v>0.818650395815939</v>
+        <v>0.818506146426336</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62429,15 +62429,15 @@
       </c>
       <c r="E639" s="16" t="n">
         <f aca="false">$D639+v_s2*(E634-$D634)</f>
-        <v>44.3134994788425</v>
+        <v>44.2713411329559</v>
       </c>
       <c r="F639" s="16" t="n">
         <f aca="false">$D639+v_s2*(F634-$D634)+0*F634</f>
-        <v>51.2324660623844</v>
+        <v>51.1844672671245</v>
       </c>
       <c r="G639" s="16" t="n">
         <f aca="false">$D639+v_s2*(G634-$D634)+0*G634</f>
-        <v>55.5953157958735</v>
+        <v>55.5438053335756</v>
       </c>
       <c r="J639" s="4" t="s">
         <v>560</v>
@@ -62491,15 +62491,15 @@
       </c>
       <c r="E641" s="16" t="n">
         <f aca="false">E639+E640</f>
-        <v>51.3002076365991</v>
+        <v>51.2580492907124</v>
       </c>
       <c r="F641" s="16" t="n">
         <f aca="false">F639+F640</f>
-        <v>58.8543348673628</v>
+        <v>58.806336072103</v>
       </c>
       <c r="G641" s="16" t="n">
         <f aca="false">G639+G640</f>
-        <v>63.8904548869072</v>
+        <v>63.8389444246092</v>
       </c>
     </row>
     <row r="642" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62519,15 +62519,15 @@
       </c>
       <c r="E642" s="11" t="n">
         <f aca="false">E639/E634</f>
-        <v>0.25223946525964</v>
+        <v>0.252254061624308</v>
       </c>
       <c r="F642" s="11" t="n">
         <f aca="false">F639/F634</f>
-        <v>0.25018638795477</v>
+        <v>0.250198619015933</v>
       </c>
       <c r="G642" s="11" t="n">
         <f aca="false">G639/G634</f>
-        <v>0.249167069754753</v>
+        <v>0.249178125571702</v>
       </c>
     </row>
     <row r="643" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62547,15 +62547,15 @@
       </c>
       <c r="E643" s="11" t="n">
         <f aca="false">E641/E636</f>
-        <v>0.233532765613915</v>
+        <v>0.233529326581433</v>
       </c>
       <c r="F643" s="11" t="n">
         <f aca="false">F641/F636</f>
-        <v>0.234100205339331</v>
+        <v>0.234097240121004</v>
       </c>
       <c r="G643" s="11" t="n">
         <f aca="false">G641/G636</f>
-        <v>0.234415810400942</v>
+        <v>0.234413126184972</v>
       </c>
     </row>
     <row r="644" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62575,15 +62575,15 @@
       </c>
       <c r="E644" s="16" t="n">
         <f aca="false">E641*nioi</f>
-        <v>35.9101453456194</v>
+        <v>35.8806345034987</v>
       </c>
       <c r="F644" s="16" t="n">
         <f aca="false">F641*nioi</f>
-        <v>41.198034407154</v>
+        <v>41.1644352504721</v>
       </c>
       <c r="G644" s="16" t="n">
         <f aca="false">G641*nioi</f>
-        <v>44.723318420835</v>
+        <v>44.6872610972265</v>
       </c>
       <c r="J644" s="8" t="s">
         <v>563</v>
@@ -62606,15 +62606,15 @@
       </c>
       <c r="E645" s="16" t="n">
         <f aca="false">E644*1000/shares</f>
-        <v>884.738249255683</v>
+        <v>884.011174203756</v>
       </c>
       <c r="F645" s="16" t="n">
         <f aca="false">F644*1000/shares</f>
-        <v>1015.01891689244</v>
+        <v>1014.19111575789</v>
       </c>
       <c r="G645" s="16" t="n">
         <f aca="false">G644*1000/shares</f>
-        <v>1101.87330236972</v>
+        <v>1100.98493800763</v>
       </c>
     </row>
     <row r="646" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62749,7 +62749,7 @@
       </c>
       <c r="D665" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E665" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -62810,7 +62810,7 @@
       </c>
       <c r="C668" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C665+0.25*D665)/(0.75*D665+0.25*E665)+(1-w_cmp)*(0.75*C664+0.25*D664)/(0.75*D664+0.25*E664)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D668" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D665+0.25*E665)/(0.75*D665+0.25*E665)+(1-w_cmp)*(0.75*D664+0.25*E664)/(0.75*D664+0.25*E664)</f>
@@ -62818,15 +62818,15 @@
       </c>
       <c r="E668" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E665+0.25*F665)/(0.75*D665+0.25*E665)+(1-w_cmp)*(0.75*E664+0.25*F664)/(0.75*D664+0.25*E664)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F668" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F665+0.25*G665)/(0.75*D665+0.25*E665)+(1-w_cmp)*(0.75*F664+0.25*G664)/(0.75*D664+0.25*E664)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G668" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G665+0.25*H665)/(0.75*D665+0.25*E665)+(1-w_cmp)*(0.75*G664+0.25*H664)/(0.75*D664+0.25*E664)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="669" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62930,15 +62930,15 @@
       </c>
       <c r="E673" s="16" t="n">
         <f aca="false">$D673*E668*E669*E670</f>
-        <v>48.7843396554535</v>
+        <v>48.6070476070838</v>
       </c>
       <c r="F673" s="16" t="n">
         <f aca="false">$D673*F668*F669*F670</f>
-        <v>56.061461770453</v>
+        <v>55.8596083876428</v>
       </c>
       <c r="G673" s="16" t="n">
         <f aca="false">$D673*G668*G669*G670</f>
-        <v>60.9370262140963</v>
+        <v>60.7204049216519</v>
       </c>
     </row>
     <row r="674" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -62958,15 +62958,15 @@
       </c>
       <c r="E674" s="16" t="n">
         <f aca="false">E672+E673</f>
-        <v>175.680278394298</v>
+        <v>175.502986345929</v>
       </c>
       <c r="F674" s="16" t="n">
         <f aca="false">F672+F673</f>
-        <v>204.777192241356</v>
+        <v>204.575338858545</v>
       </c>
       <c r="G674" s="16" t="n">
         <f aca="false">G672+G673</f>
-        <v>223.124652268834</v>
+        <v>222.908030976389</v>
       </c>
     </row>
     <row r="675" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63014,15 +63014,15 @@
       </c>
       <c r="E676" s="16" t="n">
         <f aca="false">E674+E675</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="F676" s="16" t="n">
         <f aca="false">F674+F675</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G676" s="16" t="n">
         <f aca="false">G674+G675</f>
-        <v>272.551816268834</v>
+        <v>272.335194976389</v>
       </c>
       <c r="J676" s="8" t="s">
         <v>557</v>
@@ -63045,15 +63045,15 @@
       </c>
       <c r="E677" s="11" t="n">
         <f aca="false">E674/E676</f>
-        <v>0.799745325942366</v>
+        <v>0.799583573341746</v>
       </c>
       <c r="F677" s="11" t="n">
         <f aca="false">F674/F676</f>
-        <v>0.814525945464331</v>
+        <v>0.814376909401151</v>
       </c>
       <c r="G677" s="11" t="n">
         <f aca="false">G674/G676</f>
-        <v>0.818650395815939</v>
+        <v>0.818506146426336</v>
       </c>
     </row>
     <row r="678" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63078,15 +63078,15 @@
       </c>
       <c r="E679" s="16" t="n">
         <f aca="false">$D679+v_s*(E674-$D674)</f>
-        <v>46.0886608620245</v>
+        <v>46.0353343511749</v>
       </c>
       <c r="F679" s="16" t="n">
         <f aca="false">$D679+v_s*(F674-$D674)+0*F674</f>
-        <v>54.8405304818089</v>
+        <v>54.7798163284814</v>
       </c>
       <c r="G679" s="16" t="n">
         <f aca="false">$D679+v_s*(G674-$D674)+0*G674</f>
-        <v>60.3591424850862</v>
+        <v>60.2939863892092</v>
       </c>
       <c r="J679" s="4" t="s">
         <v>560</v>
@@ -63140,15 +63140,15 @@
       </c>
       <c r="E681" s="16" t="n">
         <f aca="false">E679+E680</f>
-        <v>53.0753690197811</v>
+        <v>53.0220425089314</v>
       </c>
       <c r="F681" s="16" t="n">
         <f aca="false">F679+F680</f>
-        <v>62.4623992867873</v>
+        <v>62.4016851334598</v>
       </c>
       <c r="G681" s="16" t="n">
         <f aca="false">G679+G680</f>
-        <v>68.6542815761198</v>
+        <v>68.5891254802428</v>
       </c>
     </row>
     <row r="682" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63168,15 +63168,15 @@
       </c>
       <c r="E682" s="11" t="n">
         <f aca="false">E679/E674</f>
-        <v>0.262343965317397</v>
+        <v>0.262305134001743</v>
       </c>
       <c r="F682" s="11" t="n">
         <f aca="false">F679/F674</f>
-        <v>0.267805852212157</v>
+        <v>0.267773313411736</v>
       </c>
       <c r="G682" s="11" t="n">
         <f aca="false">G679/G674</f>
-        <v>0.270517586789836</v>
+        <v>0.270488174540448</v>
       </c>
     </row>
     <row r="683" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63196,15 +63196,15 @@
       </c>
       <c r="E683" s="11" t="n">
         <f aca="false">E681/E676</f>
-        <v>0.24161379230609</v>
+        <v>0.241565998948899</v>
       </c>
       <c r="F683" s="11" t="n">
         <f aca="false">F681/F676</f>
-        <v>0.248451716122154</v>
+        <v>0.248409665426728</v>
       </c>
       <c r="G683" s="11" t="n">
         <f aca="false">G681/G676</f>
-        <v>0.251894419622587</v>
+        <v>0.251855532246537</v>
       </c>
     </row>
     <row r="684" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63224,15 +63224,15 @@
       </c>
       <c r="E684" s="16" t="n">
         <f aca="false">E681*nioi_lo</f>
-        <v>36.0912509334511</v>
+        <v>36.0549889060734</v>
       </c>
       <c r="F684" s="16" t="n">
         <f aca="false">F681*nioi_lo</f>
-        <v>42.4744315150154</v>
+        <v>42.4331458907527</v>
       </c>
       <c r="G684" s="16" t="n">
         <f aca="false">G681*nioi_lo</f>
-        <v>46.6849114717615</v>
+        <v>46.6406053265651</v>
       </c>
       <c r="J684" s="8" t="s">
         <v>563</v>
@@ -63255,15 +63255,15 @@
       </c>
       <c r="E685" s="16" t="n">
         <f aca="false">E684*1000/shares</f>
-        <v>889.200248480876</v>
+        <v>888.306840718031</v>
       </c>
       <c r="F685" s="16" t="n">
         <f aca="false">F684*1000/shares</f>
-        <v>1046.46622326493</v>
+        <v>1045.44904634799</v>
       </c>
       <c r="G685" s="16" t="n">
         <f aca="false">G684*1000/shares</f>
-        <v>1150.20216277742</v>
+        <v>1149.1105676041</v>
       </c>
     </row>
     <row r="686" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63398,7 +63398,7 @@
       </c>
       <c r="D705" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E705" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -63459,7 +63459,7 @@
       </c>
       <c r="C708" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C705+0.25*D705)/(0.75*D705+0.25*E705)+(1-w_cmp)*(0.75*C704+0.25*D704)/(0.75*D704+0.25*E704)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D708" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D705+0.25*E705)/(0.75*D705+0.25*E705)+(1-w_cmp)*(0.75*D704+0.25*E704)/(0.75*D704+0.25*E704)</f>
@@ -63467,15 +63467,15 @@
       </c>
       <c r="E708" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E705+0.25*F705)/(0.75*D705+0.25*E705)+(1-w_cmp)*(0.75*E704+0.25*F704)/(0.75*D704+0.25*E704)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F708" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F705+0.25*G705)/(0.75*D705+0.25*E705)+(1-w_cmp)*(0.75*F704+0.25*G704)/(0.75*D704+0.25*E704)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G708" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G705+0.25*H705)/(0.75*D705+0.25*E705)+(1-w_cmp)*(0.75*G704+0.25*H704)/(0.75*D704+0.25*E704)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="709" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63579,15 +63579,15 @@
       </c>
       <c r="E713" s="16" t="n">
         <f aca="false">$D713*E708*E709*E710</f>
-        <v>48.7843396554535</v>
+        <v>48.6070476070838</v>
       </c>
       <c r="F713" s="16" t="n">
         <f aca="false">$D713*F708*F709*F710</f>
-        <v>56.061461770453</v>
+        <v>55.8596083876428</v>
       </c>
       <c r="G713" s="16" t="n">
         <f aca="false">$D713*G708*G709*G710</f>
-        <v>60.9370262140963</v>
+        <v>60.7204049216519</v>
       </c>
     </row>
     <row r="714" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63607,15 +63607,15 @@
       </c>
       <c r="E714" s="16" t="n">
         <f aca="false">E712+E713</f>
-        <v>175.680278394298</v>
+        <v>175.502986345929</v>
       </c>
       <c r="F714" s="16" t="n">
         <f aca="false">F712+F713</f>
-        <v>204.777192241356</v>
+        <v>204.575338858545</v>
       </c>
       <c r="G714" s="16" t="n">
         <f aca="false">G712+G713</f>
-        <v>223.124652268834</v>
+        <v>222.908030976389</v>
       </c>
     </row>
     <row r="715" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63663,15 +63663,15 @@
       </c>
       <c r="E716" s="16" t="n">
         <f aca="false">E714+E715</f>
-        <v>219.670278394298</v>
+        <v>219.492986345929</v>
       </c>
       <c r="F716" s="16" t="n">
         <f aca="false">F714+F715</f>
-        <v>251.406592241356</v>
+        <v>251.204738858545</v>
       </c>
       <c r="G716" s="16" t="n">
         <f aca="false">G714+G715</f>
-        <v>272.551816268834</v>
+        <v>272.335194976389</v>
       </c>
       <c r="J716" s="8" t="s">
         <v>557</v>
@@ -63694,15 +63694,15 @@
       </c>
       <c r="E717" s="11" t="n">
         <f aca="false">E714/E716</f>
-        <v>0.799745325942366</v>
+        <v>0.799583573341746</v>
       </c>
       <c r="F717" s="11" t="n">
         <f aca="false">F714/F716</f>
-        <v>0.814525945464331</v>
+        <v>0.814376909401151</v>
       </c>
       <c r="G717" s="11" t="n">
         <f aca="false">G714/G716</f>
-        <v>0.818650395815939</v>
+        <v>0.818506146426336</v>
       </c>
     </row>
     <row r="718" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63727,15 +63727,15 @@
       </c>
       <c r="E719" s="16" t="n">
         <f aca="false">$D719+v_s*(E714-$D714)</f>
-        <v>46.0886608620245</v>
+        <v>46.0353343511749</v>
       </c>
       <c r="F719" s="16" t="n">
         <f aca="false">$D719+v_s*(F714-$D714)+0*F714</f>
-        <v>54.8405304818089</v>
+        <v>54.7798163284814</v>
       </c>
       <c r="G719" s="16" t="n">
         <f aca="false">$D719+v_s*(G714-$D714)+0*G714</f>
-        <v>60.3591424850862</v>
+        <v>60.2939863892092</v>
       </c>
       <c r="J719" s="4" t="s">
         <v>560</v>
@@ -63789,15 +63789,15 @@
       </c>
       <c r="E721" s="16" t="n">
         <f aca="false">E719+E720</f>
-        <v>53.0753690197811</v>
+        <v>53.0220425089314</v>
       </c>
       <c r="F721" s="16" t="n">
         <f aca="false">F719+F720</f>
-        <v>62.4623992867873</v>
+        <v>62.4016851334598</v>
       </c>
       <c r="G721" s="16" t="n">
         <f aca="false">G719+G720</f>
-        <v>68.6542815761198</v>
+        <v>68.5891254802428</v>
       </c>
     </row>
     <row r="722" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63817,15 +63817,15 @@
       </c>
       <c r="E722" s="11" t="n">
         <f aca="false">E719/E714</f>
-        <v>0.262343965317397</v>
+        <v>0.262305134001743</v>
       </c>
       <c r="F722" s="11" t="n">
         <f aca="false">F719/F714</f>
-        <v>0.267805852212157</v>
+        <v>0.267773313411736</v>
       </c>
       <c r="G722" s="11" t="n">
         <f aca="false">G719/G714</f>
-        <v>0.270517586789836</v>
+        <v>0.270488174540448</v>
       </c>
     </row>
     <row r="723" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63845,15 +63845,15 @@
       </c>
       <c r="E723" s="11" t="n">
         <f aca="false">E721/E716</f>
-        <v>0.24161379230609</v>
+        <v>0.241565998948899</v>
       </c>
       <c r="F723" s="11" t="n">
         <f aca="false">F721/F716</f>
-        <v>0.248451716122154</v>
+        <v>0.248409665426728</v>
       </c>
       <c r="G723" s="11" t="n">
         <f aca="false">G721/G716</f>
-        <v>0.251894419622587</v>
+        <v>0.251855532246537</v>
       </c>
     </row>
     <row r="724" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -63873,15 +63873,15 @@
       </c>
       <c r="E724" s="16" t="n">
         <f aca="false">E721*nioi_hi</f>
-        <v>38.9184763228515</v>
+        <v>38.8793736922299</v>
       </c>
       <c r="F724" s="16" t="n">
         <f aca="false">F721*nioi_hi</f>
-        <v>45.8016864057096</v>
+        <v>45.7571666523405</v>
       </c>
       <c r="G724" s="16" t="n">
         <f aca="false">G721*nioi_hi</f>
-        <v>50.3419963219997</v>
+        <v>50.2942194337462</v>
       </c>
       <c r="J724" s="8" t="s">
         <v>563</v>
@@ -63904,15 +63904,15 @@
       </c>
       <c r="E725" s="16" t="n">
         <f aca="false">E724*1000/shares</f>
-        <v>958.85617488259</v>
+        <v>957.892781595694</v>
       </c>
       <c r="F725" s="16" t="n">
         <f aca="false">F724*1000/shares</f>
-        <v>1128.44165495667</v>
+        <v>1127.34479699985</v>
       </c>
       <c r="G725" s="16" t="n">
         <f aca="false">G724*1000/shares</f>
-        <v>1240.30379886489</v>
+        <v>1239.12669306202</v>
       </c>
     </row>
     <row r="726" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64047,7 +64047,7 @@
       </c>
       <c r="D745" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E745" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -64108,7 +64108,7 @@
       </c>
       <c r="C748" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C745+0.25*D745)/(0.75*D745+0.25*E745)+(1-w_cmp)*(0.75*C744+0.25*D744)/(0.75*D744+0.25*E744)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D748" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D745+0.25*E745)/(0.75*D745+0.25*E745)+(1-w_cmp)*(0.75*D744+0.25*E744)/(0.75*D744+0.25*E744)</f>
@@ -64116,15 +64116,15 @@
       </c>
       <c r="E748" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E745+0.25*F745)/(0.75*D745+0.25*E745)+(1-w_cmp)*(0.75*E744+0.25*F744)/(0.75*D744+0.25*E744)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F748" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F745+0.25*G745)/(0.75*D745+0.25*E745)+(1-w_cmp)*(0.75*F744+0.25*G744)/(0.75*D744+0.25*E744)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G748" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G745+0.25*H745)/(0.75*D745+0.25*E745)+(1-w_cmp)*(0.75*G744+0.25*H744)/(0.75*D744+0.25*E744)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="749" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64228,15 +64228,15 @@
       </c>
       <c r="E753" s="16" t="n">
         <f aca="false">$D753*E748*E749*E750</f>
-        <v>47.3208094657899</v>
+        <v>47.1488361788712</v>
       </c>
       <c r="F753" s="16" t="n">
         <f aca="false">$D753*F748*F749*F750</f>
-        <v>54.3796179173394</v>
+        <v>54.1838201360135</v>
       </c>
       <c r="G753" s="16" t="n">
         <f aca="false">$D753*G748*G749*G750</f>
-        <v>59.1089154276734</v>
+        <v>58.8987927740024</v>
       </c>
     </row>
     <row r="754" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64256,15 +64256,15 @@
       </c>
       <c r="E754" s="16" t="n">
         <f aca="false">E752+E753</f>
-        <v>170.409870042469</v>
+        <v>170.237896755551</v>
       </c>
       <c r="F754" s="16" t="n">
         <f aca="false">F752+F753</f>
-        <v>198.633876474115</v>
+        <v>198.438078692789</v>
       </c>
       <c r="G754" s="16" t="n">
         <f aca="false">G752+G753</f>
-        <v>216.430912700769</v>
+        <v>216.220790047098</v>
       </c>
     </row>
     <row r="755" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64312,15 +64312,15 @@
       </c>
       <c r="E756" s="16" t="n">
         <f aca="false">E754+E755</f>
-        <v>213.080170042469</v>
+        <v>212.908196755551</v>
       </c>
       <c r="F756" s="16" t="n">
         <f aca="false">F754+F755</f>
-        <v>243.864394474115</v>
+        <v>243.668596692789</v>
       </c>
       <c r="G756" s="16" t="n">
         <f aca="false">G754+G755</f>
-        <v>264.375261780769</v>
+        <v>264.165139127098</v>
       </c>
       <c r="J756" s="8" t="s">
         <v>557</v>
@@ -64343,15 +64343,15 @@
       </c>
       <c r="E757" s="11" t="n">
         <f aca="false">E754/E756</f>
-        <v>0.799745325942366</v>
+        <v>0.799583573341746</v>
       </c>
       <c r="F757" s="11" t="n">
         <f aca="false">F754/F756</f>
-        <v>0.814525945464331</v>
+        <v>0.814376909401151</v>
       </c>
       <c r="G757" s="11" t="n">
         <f aca="false">G754/G756</f>
-        <v>0.818650395815939</v>
+        <v>0.818506146426336</v>
       </c>
     </row>
     <row r="758" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64376,15 +64376,15 @@
       </c>
       <c r="E759" s="16" t="n">
         <f aca="false">$D759+v_s*(E754-$D754)</f>
-        <v>44.5034093476996</v>
+        <v>44.4516826321754</v>
       </c>
       <c r="F759" s="16" t="n">
         <f aca="false">$D759+v_s*(F754-$D754)+0*F754</f>
-        <v>52.9927228788905</v>
+        <v>52.9338301501628</v>
       </c>
       <c r="G759" s="16" t="n">
         <f aca="false">$D759+v_s*(G754-$D754)+0*G754</f>
-        <v>58.3457765220694</v>
+        <v>58.2825751090687</v>
       </c>
       <c r="J759" s="4" t="s">
         <v>560</v>
@@ -64438,15 +64438,15 @@
       </c>
       <c r="E761" s="16" t="n">
         <f aca="false">E759+E760</f>
-        <v>51.1725371818452</v>
+        <v>51.120810466321</v>
       </c>
       <c r="F761" s="16" t="n">
         <f aca="false">F759+F760</f>
-        <v>60.2779565408413</v>
+        <v>60.2190638121136</v>
       </c>
       <c r="G761" s="16" t="n">
         <f aca="false">G759+G760</f>
-        <v>66.2840823614937</v>
+        <v>66.2208809484931</v>
       </c>
     </row>
     <row r="762" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64466,15 +64466,15 @@
       </c>
       <c r="E762" s="11" t="n">
         <f aca="false">E759/E754</f>
-        <v>0.261155115819339</v>
+        <v>0.261115083535159</v>
       </c>
       <c r="F762" s="11" t="n">
         <f aca="false">F759/F754</f>
-        <v>0.26678592705105</v>
+        <v>0.266752381895977</v>
       </c>
       <c r="G762" s="11" t="n">
         <f aca="false">G759/G754</f>
-        <v>0.269581529708451</v>
+        <v>0.269551207801865</v>
       </c>
     </row>
     <row r="763" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64494,15 +64494,15 @@
       </c>
       <c r="E763" s="11" t="n">
         <f aca="false">E761/E756</f>
-        <v>0.240156262178906</v>
+        <v>0.240107291524408</v>
       </c>
       <c r="F763" s="11" t="n">
         <f aca="false">F761/F756</f>
-        <v>0.247178177326086</v>
+        <v>0.247135103289638</v>
       </c>
       <c r="G763" s="11" t="n">
         <f aca="false">G761/G756</f>
-        <v>0.250719685022797</v>
+        <v>0.250679863237489</v>
       </c>
     </row>
     <row r="764" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64522,15 +64522,15 @@
       </c>
       <c r="E764" s="16" t="n">
         <f aca="false">E761*nioi</f>
-        <v>35.8207760272916</v>
+        <v>35.7845673264247</v>
       </c>
       <c r="F764" s="16" t="n">
         <f aca="false">F761*nioi</f>
-        <v>42.1945695785889</v>
+        <v>42.1533446684795</v>
       </c>
       <c r="G764" s="16" t="n">
         <f aca="false">G761*nioi</f>
-        <v>46.3988576530456</v>
+        <v>46.3546166639452</v>
       </c>
       <c r="J764" s="8" t="s">
         <v>563</v>
@@ -64553,15 +64553,15 @@
       </c>
       <c r="E765" s="16" t="n">
         <f aca="false">E764*1000/shares</f>
-        <v>882.53640759023</v>
+        <v>881.644313662331</v>
       </c>
       <c r="F765" s="16" t="n">
         <f aca="false">F764*1000/shares</f>
-        <v>1039.57110888196</v>
+        <v>1038.55542781342</v>
       </c>
       <c r="G765" s="16" t="n">
         <f aca="false">G764*1000/shares</f>
-        <v>1143.15449554222</v>
+        <v>1142.06450565592</v>
       </c>
     </row>
     <row r="766" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64696,7 +64696,7 @@
       </c>
       <c r="D785" s="16" t="n">
         <f aca="false">wfeA_26</f>
-        <v>156.157050570127</v>
+        <v>160.0450143593</v>
       </c>
       <c r="E785" s="16" t="n">
         <f aca="false">wfeA_27</f>
@@ -64757,7 +64757,7 @@
       </c>
       <c r="C788" s="19" t="n">
         <f aca="false">w_cmp*(0.75*C785+0.25*D785)/(0.75*D785+0.25*E785)+(1-w_cmp)*(0.75*C784+0.25*D784)/(0.75*D784+0.25*E784)</f>
-        <v>0.876696686135123</v>
+        <v>0.875195142091216</v>
       </c>
       <c r="D788" s="19" t="n">
         <f aca="false">w_cmp*(0.75*D785+0.25*E785)/(0.75*D785+0.25*E785)+(1-w_cmp)*(0.75*D784+0.25*E784)/(0.75*D784+0.25*E784)</f>
@@ -64765,15 +64765,15 @@
       </c>
       <c r="E788" s="19" t="n">
         <f aca="false">w_cmp*(0.75*E785+0.25*F785)/(0.75*D785+0.25*E785)+(1-w_cmp)*(0.75*E784+0.25*F784)/(0.75*D784+0.25*E784)</f>
-        <v>1.14681444452041</v>
+        <v>1.14264669143806</v>
       </c>
       <c r="F788" s="19" t="n">
         <f aca="false">w_cmp*(0.75*F785+0.25*G785)/(0.75*D785+0.25*E785)+(1-w_cmp)*(0.75*F784+0.25*G784)/(0.75*D784+0.25*E784)</f>
-        <v>1.27949889890768</v>
+        <v>1.27489196978222</v>
       </c>
       <c r="G788" s="19" t="n">
         <f aca="false">w_cmp*(0.75*G785+0.25*H785)/(0.75*D785+0.25*E785)+(1-w_cmp)*(0.75*G784+0.25*H784)/(0.75*D784+0.25*E784)</f>
-        <v>1.35026661708511</v>
+        <v>1.34546663720572</v>
       </c>
     </row>
     <row r="789" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64877,15 +64877,15 @@
       </c>
       <c r="E793" s="16" t="n">
         <f aca="false">$D793*E788*E789*E790</f>
-        <v>51.2235566382262</v>
+        <v>51.0373999874379</v>
       </c>
       <c r="F793" s="16" t="n">
         <f aca="false">$D793*F788*F789*F790</f>
-        <v>58.8645348589756</v>
+        <v>58.6525888070249</v>
       </c>
       <c r="G793" s="16" t="n">
         <f aca="false">$D793*G788*G789*G790</f>
-        <v>63.9838775248011</v>
+        <v>63.7564251677345</v>
       </c>
     </row>
     <row r="794" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64905,15 +64905,15 @@
       </c>
       <c r="E794" s="16" t="n">
         <f aca="false">E792+E793</f>
-        <v>184.464292314013</v>
+        <v>184.278135663225</v>
       </c>
       <c r="F794" s="16" t="n">
         <f aca="false">F792+F793</f>
-        <v>215.016051853423</v>
+        <v>214.804105801473</v>
       </c>
       <c r="G794" s="16" t="n">
         <f aca="false">G792+G793</f>
-        <v>234.280884882275</v>
+        <v>234.053432525209</v>
       </c>
     </row>
     <row r="795" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -64961,15 +64961,15 @@
       </c>
       <c r="E796" s="16" t="n">
         <f aca="false">E794+E795</f>
-        <v>230.653792314013</v>
+        <v>230.467635663225</v>
       </c>
       <c r="F796" s="16" t="n">
         <f aca="false">F794+F795</f>
-        <v>263.976921853423</v>
+        <v>263.764975801473</v>
       </c>
       <c r="G796" s="16" t="n">
         <f aca="false">G794+G795</f>
-        <v>286.179407082275</v>
+        <v>285.951954725209</v>
       </c>
       <c r="J796" s="8" t="s">
         <v>557</v>
@@ -64992,15 +64992,15 @@
       </c>
       <c r="E797" s="11" t="n">
         <f aca="false">E794/E796</f>
-        <v>0.799745325942366</v>
+        <v>0.799583573341746</v>
       </c>
       <c r="F797" s="11" t="n">
         <f aca="false">F794/F796</f>
-        <v>0.814525945464331</v>
+        <v>0.814376909401151</v>
       </c>
       <c r="G797" s="11" t="n">
         <f aca="false">G794/G796</f>
-        <v>0.818650395815939</v>
+        <v>0.818506146426336</v>
       </c>
     </row>
     <row r="798" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65025,15 +65025,15 @@
       </c>
       <c r="E799" s="16" t="n">
         <f aca="false">$D799+v_s*(E794-$D794)</f>
-        <v>48.7307467192328</v>
+        <v>48.6747538828406</v>
       </c>
       <c r="F799" s="16" t="n">
         <f aca="false">$D799+v_s*(F794-$D794)+0*F794</f>
-        <v>57.9202098200064</v>
+        <v>57.8564599590125</v>
       </c>
       <c r="G799" s="16" t="n">
         <f aca="false">$D799+v_s*(G794-$D794)+0*G794</f>
-        <v>63.7147524234474</v>
+        <v>63.6463385227767</v>
       </c>
       <c r="J799" s="4" t="s">
         <v>560</v>
@@ -65087,15 +65087,15 @@
       </c>
       <c r="E801" s="16" t="n">
         <f aca="false">E799+E800</f>
-        <v>56.2467554163409</v>
+        <v>56.1907625799487</v>
       </c>
       <c r="F801" s="16" t="n">
         <f aca="false">F799+F800</f>
-        <v>66.1031371966975</v>
+        <v>66.0393873357036</v>
       </c>
       <c r="G801" s="16" t="n">
         <f aca="false">G799+G800</f>
-        <v>72.6046136004965</v>
+        <v>72.5361996998257</v>
       </c>
     </row>
     <row r="802" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65115,15 +65115,15 @@
       </c>
       <c r="E802" s="11" t="n">
         <f aca="false">E799/E794</f>
-        <v>0.264174416131868</v>
+        <v>0.264137433926483</v>
       </c>
       <c r="F802" s="11" t="n">
         <f aca="false">F799/F794</f>
-        <v>0.269376213174497</v>
+        <v>0.269345223840763</v>
       </c>
       <c r="G802" s="11" t="n">
         <f aca="false">G799/G794</f>
-        <v>0.271958817534191</v>
+        <v>0.271930805868107</v>
       </c>
     </row>
     <row r="803" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65143,15 +65143,15 @@
       </c>
       <c r="E803" s="11" t="n">
         <f aca="false">E801/E796</f>
-        <v>0.243857925993977</v>
+        <v>0.243811945300895</v>
       </c>
       <c r="F803" s="11" t="n">
         <f aca="false">F801/F796</f>
-        <v>0.250412561570068</v>
+        <v>0.250372086494946</v>
       </c>
       <c r="G803" s="11" t="n">
         <f aca="false">G801/G796</f>
-        <v>0.253703137974645</v>
+        <v>0.253665689292213</v>
       </c>
     </row>
     <row r="804" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65171,15 +65171,15 @@
       </c>
       <c r="E804" s="16" t="n">
         <f aca="false">E801*nioi</f>
-        <v>39.3727287914386</v>
+        <v>39.3335338059641</v>
       </c>
       <c r="F804" s="16" t="n">
         <f aca="false">F801*nioi</f>
-        <v>46.2721960376882</v>
+        <v>46.2275711349925</v>
       </c>
       <c r="G804" s="16" t="n">
         <f aca="false">G801*nioi</f>
-        <v>50.8232295203476</v>
+        <v>50.775339789878</v>
       </c>
       <c r="J804" s="8" t="s">
         <v>563</v>
@@ -65202,15 +65202,15 @@
       </c>
       <c r="E805" s="16" t="n">
         <f aca="false">E804*1000/shares</f>
-        <v>970.047845924569</v>
+        <v>969.082177239729</v>
       </c>
       <c r="F805" s="16" t="n">
         <f aca="false">F804*1000/shares</f>
-        <v>1140.03386278675</v>
+        <v>1138.93441420741</v>
       </c>
       <c r="G805" s="16" t="n">
         <f aca="false">G804*1000/shares</f>
-        <v>1252.16020917157</v>
+        <v>1250.98032321218</v>
       </c>
     </row>
     <row r="806" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65259,15 +65259,15 @@
       </c>
       <c r="C825" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>10189.1593268613</v>
+        <v>10179.867022387</v>
       </c>
       <c r="D825" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>15852.7564080399</v>
+        <v>15836.8594040909</v>
       </c>
       <c r="E825" s="13" t="n">
         <f aca="false">tp_w_dcf*C825+(1-tp_w_dcf)*D825</f>
-        <v>13020.9578674506</v>
+        <v>13008.3632132389</v>
       </c>
       <c r="F825" s="11" t="n">
         <f aca="false">E825/E$825-1</f>
@@ -65283,19 +65283,19 @@
       </c>
       <c r="C826" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!B9*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!B10*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*MAX(0,Val!C8*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!C9*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!C10*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*MAX(0,Val!D8*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^1+Val!D9*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^2+Val!D10*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
-        <v>8827.7576437299</v>
+        <v>8819.68072255395</v>
       </c>
       <c r="D826" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>15852.7564080399</v>
+        <v>15836.8594040909</v>
       </c>
       <c r="E826" s="13" t="n">
         <f aca="false">tp_w_dcf*C826+(1-tp_w_dcf)*D826</f>
-        <v>12340.2570258849</v>
+        <v>12328.2700633224</v>
       </c>
       <c r="F826" s="11" t="n">
         <f aca="false">E826/E$825-1</f>
-        <v>-0.052277324640401</v>
+        <v>-0.0522812239148107</v>
       </c>
     </row>
     <row r="827" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65307,19 +65307,19 @@
       </c>
       <c r="C827" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!B9*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!B10*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*MAX(0,Val!C8*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!C9*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!C10*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*MAX(0,Val!D8*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^1+Val!D9*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^2+Val!D10*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
-        <v>12094.759804592</v>
+        <v>12083.7671843284</v>
       </c>
       <c r="D827" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>15852.7564080399</v>
+        <v>15836.8594040909</v>
       </c>
       <c r="E827" s="13" t="n">
         <f aca="false">tp_w_dcf*C827+(1-tp_w_dcf)*D827</f>
-        <v>13973.758106316</v>
+        <v>13960.3132942096</v>
       </c>
       <c r="F827" s="11" t="n">
         <f aca="false">E827/E$825-1</f>
-        <v>0.0731743584891802</v>
+        <v>0.0731798509440342</v>
       </c>
     </row>
     <row r="828" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65331,19 +65331,19 @@
       </c>
       <c r="C828" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>10532.0294294108</v>
+        <v>10522.4532113213</v>
       </c>
       <c r="D828" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>15852.7564080399</v>
+        <v>15836.8594040909</v>
       </c>
       <c r="E828" s="13" t="n">
         <f aca="false">tp_w_dcf*C828+(1-tp_w_dcf)*D828</f>
-        <v>13192.3929187254</v>
+        <v>13179.6563077061</v>
       </c>
       <c r="F828" s="11" t="n">
         <f aca="false">E828/E$825-1</f>
-        <v>0.0131660860145548</v>
+        <v>0.0131679206414557</v>
       </c>
     </row>
     <row r="829" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65355,19 +65355,19 @@
       </c>
       <c r="C829" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>10018.4615898444</v>
+        <v>10009.2998014373</v>
       </c>
       <c r="D829" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>15852.7564080399</v>
+        <v>15836.8594040909</v>
       </c>
       <c r="E829" s="13" t="n">
         <f aca="false">tp_w_dcf*C829+(1-tp_w_dcf)*D829</f>
-        <v>12935.6089989422</v>
+        <v>12923.0796027641</v>
       </c>
       <c r="F829" s="11" t="n">
         <f aca="false">E829/E$825-1</f>
-        <v>-0.0065547304105632</v>
+        <v>-0.00655606005742881</v>
       </c>
     </row>
     <row r="830" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65379,19 +65379,19 @@
       </c>
       <c r="C830" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>10189.1593268613</v>
+        <v>10179.867022387</v>
       </c>
       <c r="D830" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>15852.7564080399</v>
+        <v>15836.8594040909</v>
       </c>
       <c r="E830" s="13" t="n">
         <f aca="false">0.3*C830+(1-0.3)*D830</f>
-        <v>14153.6772836863</v>
+        <v>14139.7616895797</v>
       </c>
       <c r="F830" s="11" t="n">
         <f aca="false">E830/E$825-1</f>
-        <v>0.0869920191560762</v>
+        <v>0.0869746991065961</v>
       </c>
     </row>
     <row r="831" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -65403,19 +65403,19 @@
       </c>
       <c r="C831" s="13" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!B9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!B10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!C9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!C10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D8*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^1+Val!D9*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^2+Val!D10*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>10189.1593268613</v>
+        <v>10179.867022387</v>
       </c>
       <c r="D831" s="13" t="n">
         <f aca="false">tp_comp_adj</f>
-        <v>15852.7564080399</v>
+        <v>15836.8594040909</v>
       </c>
       <c r="E831" s="13" t="n">
         <f aca="false">0.7*C831+(1-0.7)*D831</f>
-        <v>11888.2384512149</v>
+        <v>11876.9647368982</v>
       </c>
       <c r="F831" s="11" t="n">
         <f aca="false">E831/E$825-1</f>
-        <v>-0.0869920191560762</v>
+        <v>-0.0869746991065959</v>
       </c>
     </row>
   </sheetData>
